--- a/outputs/plan/plan_prodazh_08.2026-03.2027.xlsx
+++ b/outputs/plan/plan_prodazh_08.2026-03.2027.xlsx
@@ -532,44 +532,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>551392965</t>
+          <t>868516027</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]</t>
+          <t>Celimax Dual Barrier Creamy Toner</t>
         </is>
       </c>
       <c r="D3">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(2499*$B$1,0)</f>
         <v/>
       </c>
       <c r="E3">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(2024*$B$1,0)</f>
         <v/>
       </c>
       <c r="F3">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(2024*$B$1,0)</f>
         <v/>
       </c>
       <c r="G3">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(2024*$B$1,0)</f>
         <v/>
       </c>
       <c r="H3">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(2457*$B$1,0)</f>
         <v/>
       </c>
       <c r="I3">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(2520*$B$1,0)</f>
         <v/>
       </c>
       <c r="J3">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(2047*$B$1,0)</f>
         <v/>
       </c>
       <c r="K3">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(2220*$B$1,0)</f>
         <v/>
       </c>
       <c r="L3">
@@ -585,44 +585,44 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>551607905</t>
+          <t>551465879</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / </t>
+          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]</t>
         </is>
       </c>
       <c r="D4">
-        <f>ROUND(197*$B$1,0)</f>
+        <f>ROUND(549*$B$1,0)</f>
         <v/>
       </c>
       <c r="E4">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(445*$B$1,0)</f>
         <v/>
       </c>
       <c r="F4">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(445*$B$1,0)</f>
         <v/>
       </c>
       <c r="G4">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(445*$B$1,0)</f>
         <v/>
       </c>
       <c r="H4">
-        <f>ROUND(193*$B$1,0)</f>
+        <f>ROUND(540*$B$1,0)</f>
         <v/>
       </c>
       <c r="I4">
-        <f>ROUND(198*$B$1,0)</f>
+        <f>ROUND(554*$B$1,0)</f>
         <v/>
       </c>
       <c r="J4">
-        <f>ROUND(161*$B$1,0)</f>
+        <f>ROUND(450*$B$1,0)</f>
         <v/>
       </c>
       <c r="K4">
-        <f>ROUND(175*$B$1,0)</f>
+        <f>ROUND(488*$B$1,0)</f>
         <v/>
       </c>
       <c r="L4">
@@ -638,44 +638,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>551600265</t>
+          <t>551607905</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30m</t>
+          <t xml:space="preserve">CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD [170ml / </t>
         </is>
       </c>
       <c r="D5">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(197*$B$1,0)</f>
         <v/>
       </c>
       <c r="E5">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="F5">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="G5">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="H5">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(193*$B$1,0)</f>
         <v/>
       </c>
       <c r="I5">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(198*$B$1,0)</f>
         <v/>
       </c>
       <c r="J5">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(161*$B$1,0)</f>
         <v/>
       </c>
       <c r="K5">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(175*$B$1,0)</f>
         <v/>
       </c>
       <c r="L5">
@@ -691,44 +691,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>551447345</t>
+          <t>551540924</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
         </is>
       </c>
       <c r="D6">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="E6">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(136*$B$1,0)</f>
         <v/>
       </c>
       <c r="F6">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(136*$B$1,0)</f>
         <v/>
       </c>
       <c r="G6">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(136*$B$1,0)</f>
         <v/>
       </c>
       <c r="H6">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(165*$B$1,0)</f>
         <v/>
       </c>
       <c r="I6">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(170*$B$1,0)</f>
         <v/>
       </c>
       <c r="J6">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(138*$B$1,0)</f>
         <v/>
       </c>
       <c r="K6">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(149*$B$1,0)</f>
         <v/>
       </c>
       <c r="L6">
@@ -744,44 +744,44 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>551540924</t>
+          <t>551616449</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
+          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml</t>
         </is>
       </c>
       <c r="D7">
-        <f>ROUND(168*$B$1,0)</f>
+        <f>ROUND(49*$B$1,0)</f>
         <v/>
       </c>
       <c r="E7">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(40*$B$1,0)</f>
         <v/>
       </c>
       <c r="F7">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(40*$B$1,0)</f>
         <v/>
       </c>
       <c r="G7">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(40*$B$1,0)</f>
         <v/>
       </c>
       <c r="H7">
-        <f>ROUND(165*$B$1,0)</f>
+        <f>ROUND(48*$B$1,0)</f>
         <v/>
       </c>
       <c r="I7">
-        <f>ROUND(170*$B$1,0)</f>
+        <f>ROUND(50*$B$1,0)</f>
         <v/>
       </c>
       <c r="J7">
-        <f>ROUND(138*$B$1,0)</f>
+        <f>ROUND(40*$B$1,0)</f>
         <v/>
       </c>
       <c r="K7">
-        <f>ROUND(149*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="L7">
@@ -797,44 +797,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>551490295</t>
+          <t>551387355</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_10ml [10ml]</t>
+          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15m</t>
         </is>
       </c>
       <c r="D8">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(37*$B$1,0)</f>
         <v/>
       </c>
       <c r="E8">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="F8">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="G8">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="H8">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(37*$B$1,0)</f>
         <v/>
       </c>
       <c r="I8">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="J8">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="K8">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="L8">
@@ -850,44 +850,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>551482493</t>
+          <t>551490295</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_10ml [10ml]</t>
         </is>
       </c>
       <c r="D9">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="E9">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="F9">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="G9">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="H9">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="I9">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="J9">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="K9">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="L9">
@@ -956,44 +956,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>551616449</t>
+          <t>551600265</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30m</t>
         </is>
       </c>
       <c r="D11">
-        <f>ROUND(49*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="E11">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="F11">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="G11">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="H11">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="I11">
-        <f>ROUND(50*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="J11">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="K11">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="L11">
@@ -1009,44 +1009,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>551387355</t>
+          <t>551447345</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINAL SHOT TIGHTENING BOOSTER [15m</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
         </is>
       </c>
       <c r="D12">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="E12">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="F12">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="G12">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="H12">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="I12">
-        <f>ROUND(38*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="J12">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="K12">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="L12">
@@ -1062,44 +1062,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>551465879</t>
+          <t>551482493</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CELIMAX THE VITA-A RETINOL SHOT TIGHTENING SERUM [30ml]</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]</t>
         </is>
       </c>
       <c r="D13">
-        <f>ROUND(549*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="E13">
-        <f>ROUND(445*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="F13">
-        <f>ROUND(445*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="G13">
-        <f>ROUND(445*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="H13">
-        <f>ROUND(540*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="I13">
-        <f>ROUND(554*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="J13">
-        <f>ROUND(450*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="K13">
-        <f>ROUND(488*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="L13">
@@ -1115,44 +1115,44 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>868516027</t>
+          <t>551392965</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Celimax Dual Barrier Creamy Toner</t>
+          <t>CELIMAX DUAL BARRIER SKIN WEARABLE CREAM [50ml]</t>
         </is>
       </c>
       <c r="D14">
-        <f>ROUND(2499*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="E14">
-        <f>ROUND(2024*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F14">
-        <f>ROUND(2024*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G14">
-        <f>ROUND(2024*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H14">
-        <f>ROUND(2457*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="I14">
-        <f>ROUND(2520*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="J14">
-        <f>ROUND(2047*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="K14">
-        <f>ROUND(2220*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="L14">
@@ -1221,44 +1221,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>207481251</t>
+          <t>204258828</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COSRX Advanced Snail 96 Mucin Power Essence [100ml]</t>
+          <t>COSRX_Salicylic_Acid_Cleanser</t>
         </is>
       </c>
       <c r="D16">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(69*$B$1,0)</f>
         <v/>
       </c>
       <c r="E16">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="F16">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="G16">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="H16">
-        <f>ROUND(65*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="I16">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(69*$B$1,0)</f>
         <v/>
       </c>
       <c r="J16">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="K16">
-        <f>ROUND(59*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="L16">
@@ -1274,44 +1274,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>204258828</t>
+          <t>207481251</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COSRX_Salicylic_Acid_Cleanser</t>
+          <t>COSRX Advanced Snail 96 Mucin Power Essence [100ml]</t>
         </is>
       </c>
       <c r="D17">
-        <f>ROUND(69*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="E17">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="F17">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="G17">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="H17">
-        <f>ROUND(68*$B$1,0)</f>
+        <f>ROUND(65*$B$1,0)</f>
         <v/>
       </c>
       <c r="I17">
-        <f>ROUND(69*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="J17">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="K17">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(59*$B$1,0)</f>
         <v/>
       </c>
       <c r="L17">
@@ -1327,44 +1327,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>214304289</t>
+          <t>214305722</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DEOPROCE - REAL FRESH VEGAN CALMING TONER [200ml]</t>
+          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
         </is>
       </c>
       <c r="D18">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(161*$B$1,0)</f>
         <v/>
       </c>
       <c r="E18">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="F18">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="G18">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="H18">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(158*$B$1,0)</f>
         <v/>
       </c>
       <c r="I18">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="J18">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(132*$B$1,0)</f>
         <v/>
       </c>
       <c r="K18">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(143*$B$1,0)</f>
         <v/>
       </c>
       <c r="L18">
@@ -1380,44 +1380,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>214304883</t>
+          <t>214305705</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g]</t>
+          <t>DEOPROCE SHAMPOO - ARGAN SILKY MOISTURE [1000ml]</t>
         </is>
       </c>
       <c r="D19">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(120*$B$1,0)</f>
         <v/>
       </c>
       <c r="E19">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="F19">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="G19">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="H19">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(118*$B$1,0)</f>
         <v/>
       </c>
       <c r="I19">
-        <f>ROUND(35*$B$1,0)</f>
+        <f>ROUND(121*$B$1,0)</f>
         <v/>
       </c>
       <c r="J19">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(98*$B$1,0)</f>
         <v/>
       </c>
       <c r="K19">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(107*$B$1,0)</f>
         <v/>
       </c>
       <c r="L19">
@@ -1433,44 +1433,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>214305705</t>
+          <t>608841921</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - ARGAN SILKY MOISTURE [1000ml]</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[200ml]</t>
         </is>
       </c>
       <c r="D20">
-        <f>ROUND(120*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="E20">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="F20">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="G20">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="H20">
-        <f>ROUND(118*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="I20">
-        <f>ROUND(121*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="J20">
-        <f>ROUND(98*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="K20">
-        <f>ROUND(107*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="L20">
@@ -1486,44 +1486,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>608841921</t>
+          <t>608837066</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[200ml]</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] без колпачка</t>
         </is>
       </c>
       <c r="D21">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="E21">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="F21">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="G21">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="H21">
-        <f>ROUND(81*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="I21">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="J21">
-        <f>ROUND(68*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="K21">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(50*$B$1,0)</f>
         <v/>
       </c>
       <c r="L21">
@@ -1539,44 +1539,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>608837066</t>
+          <t>608624295</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] без колпачка</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] с колпачком</t>
         </is>
       </c>
       <c r="D22">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="E22">
-        <f>ROUND(46*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="F22">
-        <f>ROUND(46*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="G22">
-        <f>ROUND(46*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="H22">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(43*$B$1,0)</f>
         <v/>
       </c>
       <c r="I22">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="J22">
-        <f>ROUND(46*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="K22">
-        <f>ROUND(50*$B$1,0)</f>
+        <f>ROUND(39*$B$1,0)</f>
         <v/>
       </c>
       <c r="L22">
@@ -1592,44 +1592,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>608624295</t>
+          <t>214304883</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] с колпачком</t>
+          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g]</t>
         </is>
       </c>
       <c r="D23">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="E23">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="F23">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="G23">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="H23">
-        <f>ROUND(43*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="I23">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="J23">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="K23">
-        <f>ROUND(39*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="L23">
@@ -1645,44 +1645,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>214305722</t>
+          <t>214304289</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
+          <t>DEOPROCE - REAL FRESH VEGAN CALMING TONER [200ml]</t>
         </is>
       </c>
       <c r="D24">
-        <f>ROUND(161*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="E24">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F24">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G24">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H24">
-        <f>ROUND(158*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="I24">
-        <f>ROUND(162*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="J24">
-        <f>ROUND(132*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="K24">
-        <f>ROUND(143*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="L24">
@@ -1698,44 +1698,44 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>212719009</t>
+          <t>199425671</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DR. JART - Cicapair Tiger Grass Color Correcting Treatm</t>
+          <t>Dr.Jart_Teatreatment_Soothing_Spot</t>
         </is>
       </c>
       <c r="D25">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(71*$B$1,0)</f>
         <v/>
       </c>
       <c r="E25">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="F25">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="G25">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="H25">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(70*$B$1,0)</f>
         <v/>
       </c>
       <c r="I25">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(71*$B$1,0)</f>
         <v/>
       </c>
       <c r="J25">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(58*$B$1,0)</f>
         <v/>
       </c>
       <c r="K25">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="L25">
@@ -1804,44 +1804,44 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>199425671</t>
+          <t>212719009</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dr.Jart_Teatreatment_Soothing_Spot</t>
+          <t>DR. JART - Cicapair Tiger Grass Color Correcting Treatm</t>
         </is>
       </c>
       <c r="D27">
-        <f>ROUND(71*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="E27">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="F27">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="G27">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="H27">
-        <f>ROUND(70*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="I27">
-        <f>ROUND(71*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="J27">
-        <f>ROUND(58*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="K27">
-        <f>ROUND(63*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="L27">
@@ -2016,44 +2016,44 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>207796563</t>
+          <t>207796439</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream</t>
+          <t>ELIZAVECCA - Natural 90% Olive Cleansing Oil</t>
         </is>
       </c>
       <c r="D31">
+        <f>ROUND(196*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E31">
         <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
-      <c r="E31">
-        <f>ROUND(129*$B$1,0)</f>
-        <v/>
-      </c>
       <c r="F31">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="G31">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="H31">
-        <f>ROUND(156*$B$1,0)</f>
+        <f>ROUND(192*$B$1,0)</f>
         <v/>
       </c>
       <c r="I31">
+        <f>ROUND(197*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J31">
         <f>ROUND(160*$B$1,0)</f>
         <v/>
       </c>
-      <c r="J31">
-        <f>ROUND(130*$B$1,0)</f>
-        <v/>
-      </c>
       <c r="K31">
-        <f>ROUND(141*$B$1,0)</f>
+        <f>ROUND(174*$B$1,0)</f>
         <v/>
       </c>
       <c r="L31">
@@ -2069,44 +2069,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>207796350</t>
+          <t>207796563</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - CER-100  [100ml]</t>
+          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream</t>
         </is>
       </c>
       <c r="D32">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="E32">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(129*$B$1,0)</f>
         <v/>
       </c>
       <c r="F32">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(129*$B$1,0)</f>
         <v/>
       </c>
       <c r="G32">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(129*$B$1,0)</f>
         <v/>
       </c>
       <c r="H32">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(156*$B$1,0)</f>
         <v/>
       </c>
       <c r="I32">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(160*$B$1,0)</f>
         <v/>
       </c>
       <c r="J32">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="K32">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(141*$B$1,0)</f>
         <v/>
       </c>
       <c r="L32">
@@ -2122,44 +2122,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>207796439</t>
+          <t>154163936</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Natural 90% Olive Cleansing Oil</t>
+          <t>Elizavecca Hell-Pore Control Hyaluronic Acid 97%</t>
         </is>
       </c>
       <c r="D33">
-        <f>ROUND(196*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="E33">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(129*$B$1,0)</f>
         <v/>
       </c>
       <c r="F33">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(129*$B$1,0)</f>
         <v/>
       </c>
       <c r="G33">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(129*$B$1,0)</f>
         <v/>
       </c>
       <c r="H33">
-        <f>ROUND(192*$B$1,0)</f>
+        <f>ROUND(156*$B$1,0)</f>
         <v/>
       </c>
       <c r="I33">
-        <f>ROUND(197*$B$1,0)</f>
+        <f>ROUND(160*$B$1,0)</f>
         <v/>
       </c>
       <c r="J33">
-        <f>ROUND(160*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="K33">
-        <f>ROUND(174*$B$1,0)</f>
+        <f>ROUND(141*$B$1,0)</f>
         <v/>
       </c>
       <c r="L33">
@@ -2281,44 +2281,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>154163936</t>
+          <t>207796350</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Elizavecca Hell-Pore Control Hyaluronic Acid 97%</t>
+          <t>ELIZAVECCA - CER-100  [100ml]</t>
         </is>
       </c>
       <c r="D36">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="E36">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="F36">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="G36">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="H36">
-        <f>ROUND(156*$B$1,0)</f>
+        <f>ROUND(32*$B$1,0)</f>
         <v/>
       </c>
       <c r="I36">
-        <f>ROUND(160*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="J36">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="K36">
-        <f>ROUND(141*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="L36">
@@ -2440,44 +2440,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>150925321</t>
+          <t>238415286</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Collagen_Enough_Moisture_Foundation_13</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N</t>
         </is>
       </c>
       <c r="D39">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(2426*$B$1,0)</f>
         <v/>
       </c>
       <c r="E39">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(1965*$B$1,0)</f>
         <v/>
       </c>
       <c r="F39">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(1965*$B$1,0)</f>
         <v/>
       </c>
       <c r="G39">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(1965*$B$1,0)</f>
         <v/>
       </c>
       <c r="H39">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(2385*$B$1,0)</f>
         <v/>
       </c>
       <c r="I39">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(2446*$B$1,0)</f>
         <v/>
       </c>
       <c r="J39">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(1987*$B$1,0)</f>
         <v/>
       </c>
       <c r="K39">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(2155*$B$1,0)</f>
         <v/>
       </c>
       <c r="L39">
@@ -2493,44 +2493,44 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>150925322</t>
+          <t>238358954</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Collagen_Enough_Moisture_Foundation_21</t>
+          <t>ENOUGH - Collagen 3in1 Sun Cream SPF50 PA++ [50ml] N</t>
         </is>
       </c>
       <c r="D40">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(980*$B$1,0)</f>
         <v/>
       </c>
       <c r="E40">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(794*$B$1,0)</f>
         <v/>
       </c>
       <c r="F40">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(794*$B$1,0)</f>
         <v/>
       </c>
       <c r="G40">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(794*$B$1,0)</f>
         <v/>
       </c>
       <c r="H40">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(964*$B$1,0)</f>
         <v/>
       </c>
       <c r="I40">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(988*$B$1,0)</f>
         <v/>
       </c>
       <c r="J40">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(803*$B$1,0)</f>
         <v/>
       </c>
       <c r="K40">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(871*$B$1,0)</f>
         <v/>
       </c>
       <c r="L40">
@@ -2546,44 +2546,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>611747838</t>
+          <t>238358009</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Collagen_Enough_Moisture_Foundation_23</t>
+          <t>ENOUGH - Collagen Moisture Sun Cream SPF50+ PA++++ [50m</t>
         </is>
       </c>
       <c r="D41">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(730*$B$1,0)</f>
         <v/>
       </c>
       <c r="E41">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(592*$B$1,0)</f>
         <v/>
       </c>
       <c r="F41">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(592*$B$1,0)</f>
         <v/>
       </c>
       <c r="G41">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(592*$B$1,0)</f>
         <v/>
       </c>
       <c r="H41">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(718*$B$1,0)</f>
         <v/>
       </c>
       <c r="I41">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(736*$B$1,0)</f>
         <v/>
       </c>
       <c r="J41">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(598*$B$1,0)</f>
         <v/>
       </c>
       <c r="K41">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(649*$B$1,0)</f>
         <v/>
       </c>
       <c r="L41">
@@ -2599,44 +2599,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>238358954</t>
+          <t>207796789</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen 3in1 Sun Cream SPF50 PA++ [50ml] N</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13]</t>
         </is>
       </c>
       <c r="D42">
-        <f>ROUND(980*$B$1,0)</f>
+        <f>ROUND(442*$B$1,0)</f>
         <v/>
       </c>
       <c r="E42">
-        <f>ROUND(794*$B$1,0)</f>
+        <f>ROUND(358*$B$1,0)</f>
         <v/>
       </c>
       <c r="F42">
-        <f>ROUND(794*$B$1,0)</f>
+        <f>ROUND(358*$B$1,0)</f>
         <v/>
       </c>
       <c r="G42">
-        <f>ROUND(794*$B$1,0)</f>
+        <f>ROUND(358*$B$1,0)</f>
         <v/>
       </c>
       <c r="H42">
-        <f>ROUND(964*$B$1,0)</f>
+        <f>ROUND(435*$B$1,0)</f>
         <v/>
       </c>
       <c r="I42">
-        <f>ROUND(988*$B$1,0)</f>
+        <f>ROUND(446*$B$1,0)</f>
         <v/>
       </c>
       <c r="J42">
-        <f>ROUND(803*$B$1,0)</f>
+        <f>ROUND(362*$B$1,0)</f>
         <v/>
       </c>
       <c r="K42">
-        <f>ROUND(871*$B$1,0)</f>
+        <f>ROUND(393*$B$1,0)</f>
         <v/>
       </c>
       <c r="L42">
@@ -2652,44 +2652,44 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>238415286</t>
+          <t>333318356</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N</t>
+          <t>ENOUGH - Collagen Moisture Sun Cream SPF50+ PA++++ [50m</t>
         </is>
       </c>
       <c r="D43">
-        <f>ROUND(2426*$B$1,0)</f>
+        <f>ROUND(307*$B$1,0)</f>
         <v/>
       </c>
       <c r="E43">
-        <f>ROUND(1965*$B$1,0)</f>
+        <f>ROUND(249*$B$1,0)</f>
         <v/>
       </c>
       <c r="F43">
-        <f>ROUND(1965*$B$1,0)</f>
+        <f>ROUND(249*$B$1,0)</f>
         <v/>
       </c>
       <c r="G43">
-        <f>ROUND(1965*$B$1,0)</f>
+        <f>ROUND(249*$B$1,0)</f>
         <v/>
       </c>
       <c r="H43">
-        <f>ROUND(2385*$B$1,0)</f>
+        <f>ROUND(302*$B$1,0)</f>
         <v/>
       </c>
       <c r="I43">
-        <f>ROUND(2446*$B$1,0)</f>
+        <f>ROUND(310*$B$1,0)</f>
         <v/>
       </c>
       <c r="J43">
-        <f>ROUND(1987*$B$1,0)</f>
+        <f>ROUND(252*$B$1,0)</f>
         <v/>
       </c>
       <c r="K43">
-        <f>ROUND(2155*$B$1,0)</f>
+        <f>ROUND(273*$B$1,0)</f>
         <v/>
       </c>
       <c r="L43">
@@ -2705,44 +2705,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>149197341</t>
+          <t>170198835</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N 1</t>
+          <t>Enough Collagen Foundation Cover Up Ultra X10 13 тон</t>
         </is>
       </c>
       <c r="D44">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(307*$B$1,0)</f>
         <v/>
       </c>
       <c r="E44">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(249*$B$1,0)</f>
         <v/>
       </c>
       <c r="F44">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(249*$B$1,0)</f>
         <v/>
       </c>
       <c r="G44">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(249*$B$1,0)</f>
         <v/>
       </c>
       <c r="H44">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(302*$B$1,0)</f>
         <v/>
       </c>
       <c r="I44">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(310*$B$1,0)</f>
         <v/>
       </c>
       <c r="J44">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(252*$B$1,0)</f>
         <v/>
       </c>
       <c r="K44">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(273*$B$1,0)</f>
         <v/>
       </c>
       <c r="L44">
@@ -2758,44 +2758,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>238358009</t>
+          <t>207796898</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Sun Cream SPF50+ PA++++ [50m</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21]</t>
         </is>
       </c>
       <c r="D45">
-        <f>ROUND(730*$B$1,0)</f>
+        <f>ROUND(307*$B$1,0)</f>
         <v/>
       </c>
       <c r="E45">
-        <f>ROUND(592*$B$1,0)</f>
+        <f>ROUND(248*$B$1,0)</f>
         <v/>
       </c>
       <c r="F45">
-        <f>ROUND(592*$B$1,0)</f>
+        <f>ROUND(248*$B$1,0)</f>
         <v/>
       </c>
       <c r="G45">
-        <f>ROUND(592*$B$1,0)</f>
+        <f>ROUND(248*$B$1,0)</f>
         <v/>
       </c>
       <c r="H45">
-        <f>ROUND(718*$B$1,0)</f>
+        <f>ROUND(302*$B$1,0)</f>
         <v/>
       </c>
       <c r="I45">
-        <f>ROUND(736*$B$1,0)</f>
+        <f>ROUND(309*$B$1,0)</f>
         <v/>
       </c>
       <c r="J45">
-        <f>ROUND(598*$B$1,0)</f>
+        <f>ROUND(251*$B$1,0)</f>
         <v/>
       </c>
       <c r="K45">
-        <f>ROUND(649*$B$1,0)</f>
+        <f>ROUND(272*$B$1,0)</f>
         <v/>
       </c>
       <c r="L45">
@@ -2811,44 +2811,44 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>333318356</t>
+          <t>238416010</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Sun Cream SPF50+ PA++++ [50m</t>
+          <t>Enough Collagen Whitening Moisture Cream 3in1 50 N</t>
         </is>
       </c>
       <c r="D46">
-        <f>ROUND(307*$B$1,0)</f>
+        <f>ROUND(191*$B$1,0)</f>
         <v/>
       </c>
       <c r="E46">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(155*$B$1,0)</f>
         <v/>
       </c>
       <c r="F46">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(155*$B$1,0)</f>
         <v/>
       </c>
       <c r="G46">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(155*$B$1,0)</f>
         <v/>
       </c>
       <c r="H46">
-        <f>ROUND(302*$B$1,0)</f>
+        <f>ROUND(188*$B$1,0)</f>
         <v/>
       </c>
       <c r="I46">
-        <f>ROUND(310*$B$1,0)</f>
+        <f>ROUND(193*$B$1,0)</f>
         <v/>
       </c>
       <c r="J46">
-        <f>ROUND(252*$B$1,0)</f>
+        <f>ROUND(157*$B$1,0)</f>
         <v/>
       </c>
       <c r="K46">
-        <f>ROUND(273*$B$1,0)</f>
+        <f>ROUND(170*$B$1,0)</f>
         <v/>
       </c>
       <c r="L46">
@@ -2864,44 +2864,44 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>207796789</t>
+          <t>170198180</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13]</t>
+          <t>Enough Rich Gold Double Wea Radiance Foundation 13 тон</t>
         </is>
       </c>
       <c r="D47">
-        <f>ROUND(442*$B$1,0)</f>
+        <f>ROUND(156*$B$1,0)</f>
         <v/>
       </c>
       <c r="E47">
-        <f>ROUND(358*$B$1,0)</f>
+        <f>ROUND(126*$B$1,0)</f>
         <v/>
       </c>
       <c r="F47">
-        <f>ROUND(358*$B$1,0)</f>
+        <f>ROUND(126*$B$1,0)</f>
         <v/>
       </c>
       <c r="G47">
-        <f>ROUND(358*$B$1,0)</f>
+        <f>ROUND(126*$B$1,0)</f>
         <v/>
       </c>
       <c r="H47">
-        <f>ROUND(435*$B$1,0)</f>
+        <f>ROUND(153*$B$1,0)</f>
         <v/>
       </c>
       <c r="I47">
-        <f>ROUND(446*$B$1,0)</f>
+        <f>ROUND(157*$B$1,0)</f>
         <v/>
       </c>
       <c r="J47">
-        <f>ROUND(362*$B$1,0)</f>
+        <f>ROUND(128*$B$1,0)</f>
         <v/>
       </c>
       <c r="K47">
-        <f>ROUND(393*$B$1,0)</f>
+        <f>ROUND(139*$B$1,0)</f>
         <v/>
       </c>
       <c r="L47">
@@ -2917,44 +2917,44 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>207796898</t>
+          <t>170198876</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21]</t>
+          <t>Enough Collagen Foundation Cover Up Ultra X10 21 тон</t>
         </is>
       </c>
       <c r="D48">
-        <f>ROUND(307*$B$1,0)</f>
+        <f>ROUND(122*$B$1,0)</f>
         <v/>
       </c>
       <c r="E48">
-        <f>ROUND(248*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="F48">
-        <f>ROUND(248*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="G48">
-        <f>ROUND(248*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="H48">
-        <f>ROUND(302*$B$1,0)</f>
+        <f>ROUND(120*$B$1,0)</f>
         <v/>
       </c>
       <c r="I48">
-        <f>ROUND(309*$B$1,0)</f>
+        <f>ROUND(123*$B$1,0)</f>
         <v/>
       </c>
       <c r="J48">
-        <f>ROUND(251*$B$1,0)</f>
+        <f>ROUND(100*$B$1,0)</f>
         <v/>
       </c>
       <c r="K48">
-        <f>ROUND(272*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="L48">
@@ -2970,44 +2970,44 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>151132051</t>
+          <t>170198738</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ENOUGH COLLAGEN 3IN1 13</t>
+          <t>Enough 8 Peptide Full Cover Perfect Foundation 13 тон</t>
         </is>
       </c>
       <c r="D49">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="E49">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="F49">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="G49">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="H49">
-        <f>ROUND(101*$B$1,0)</f>
+        <f>ROUND(110*$B$1,0)</f>
         <v/>
       </c>
       <c r="I49">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="J49">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(91*$B$1,0)</f>
         <v/>
       </c>
       <c r="K49">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="L49">
@@ -3023,44 +3023,44 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>151132052</t>
+          <t>170198109</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ENOUGH COLLAGEN 3IN1 21</t>
+          <t>Enough Rich Gold Double Wea Radiance Foundation 21 тон</t>
         </is>
       </c>
       <c r="D50">
-        <f>ROUND(39*$B$1,0)</f>
+        <f>ROUND(106*$B$1,0)</f>
         <v/>
       </c>
       <c r="E50">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(86*$B$1,0)</f>
         <v/>
       </c>
       <c r="F50">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(86*$B$1,0)</f>
         <v/>
       </c>
       <c r="G50">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(86*$B$1,0)</f>
         <v/>
       </c>
       <c r="H50">
-        <f>ROUND(38*$B$1,0)</f>
+        <f>ROUND(104*$B$1,0)</f>
         <v/>
       </c>
       <c r="I50">
-        <f>ROUND(39*$B$1,0)</f>
+        <f>ROUND(107*$B$1,0)</f>
         <v/>
       </c>
       <c r="J50">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="K50">
-        <f>ROUND(35*$B$1,0)</f>
+        <f>ROUND(94*$B$1,0)</f>
         <v/>
       </c>
       <c r="L50">
@@ -3076,44 +3076,44 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>611717011</t>
+          <t>170198337</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #01</t>
+          <t>Enough 8 Peptide Full Cover Perfect Foundation 21 тон</t>
         </is>
       </c>
       <c r="D51">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="E51">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="F51">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="G51">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="H51">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(103*$B$1,0)</f>
         <v/>
       </c>
       <c r="I51">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="J51">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(86*$B$1,0)</f>
         <v/>
       </c>
       <c r="K51">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="L51">
@@ -3129,44 +3129,44 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>611744611</t>
+          <t>150925322</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02</t>
+          <t>Collagen_Enough_Moisture_Foundation_21</t>
         </is>
       </c>
       <c r="D52">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(104*$B$1,0)</f>
         <v/>
       </c>
       <c r="E52">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="F52">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="G52">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="H52">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="I52">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="J52">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="K52">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="L52">
@@ -3182,44 +3182,44 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>165002270</t>
+          <t>151132051</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ BB</t>
+          <t>ENOUGH COLLAGEN 3IN1 13</t>
         </is>
       </c>
       <c r="D53">
-        <f>ROUND(70*$B$1,0)</f>
+        <f>ROUND(103*$B$1,0)</f>
         <v/>
       </c>
       <c r="E53">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="F53">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="G53">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="H53">
-        <f>ROUND(68*$B$1,0)</f>
+        <f>ROUND(101*$B$1,0)</f>
         <v/>
       </c>
       <c r="I53">
-        <f>ROUND(70*$B$1,0)</f>
+        <f>ROUND(104*$B$1,0)</f>
         <v/>
       </c>
       <c r="J53">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="K53">
-        <f>ROUND(62*$B$1,0)</f>
+        <f>ROUND(91*$B$1,0)</f>
         <v/>
       </c>
       <c r="L53">
@@ -3235,16 +3235,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>238413828</t>
+          <t>150925321</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ N</t>
+          <t>Collagen_Enough_Moisture_Foundation_13</t>
         </is>
       </c>
       <c r="D54">
-        <f>ROUND(101*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="E54">
@@ -3260,19 +3260,19 @@
         <v/>
       </c>
       <c r="H54">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(100*$B$1,0)</f>
         <v/>
       </c>
       <c r="I54">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(103*$B$1,0)</f>
         <v/>
       </c>
       <c r="J54">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="K54">
-        <f>ROUND(89*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="L54">
@@ -3288,44 +3288,44 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>170198738</t>
+          <t>238413828</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide Full Cover Perfect Foundation 13 тон</t>
+          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ N</t>
         </is>
       </c>
       <c r="D55">
-        <f>ROUND(112*$B$1,0)</f>
+        <f>ROUND(101*$B$1,0)</f>
         <v/>
       </c>
       <c r="E55">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="F55">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="G55">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="H55">
-        <f>ROUND(110*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="I55">
-        <f>ROUND(112*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="J55">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="K55">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(89*$B$1,0)</f>
         <v/>
       </c>
       <c r="L55">
@@ -3341,44 +3341,44 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>170198337</t>
+          <t>212889027</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide Full Cover Perfect Foundation 21 тон</t>
+          <t>Enoughcollagenwhiteningcovertip</t>
         </is>
       </c>
       <c r="D56">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(78*$B$1,0)</f>
         <v/>
       </c>
       <c r="E56">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="F56">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="G56">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="H56">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(77*$B$1,0)</f>
         <v/>
       </c>
       <c r="I56">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(79*$B$1,0)</f>
         <v/>
       </c>
       <c r="J56">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(64*$B$1,0)</f>
         <v/>
       </c>
       <c r="K56">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(69*$B$1,0)</f>
         <v/>
       </c>
       <c r="L56">
@@ -3394,44 +3394,44 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>170198835</t>
+          <t>212889025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Enough Collagen Foundation Cover Up Ultra X10 13 тон</t>
+          <t>Enoughcollagenwhiteningcovertip01</t>
         </is>
       </c>
       <c r="D57">
-        <f>ROUND(307*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="E57">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="F57">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="G57">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="H57">
-        <f>ROUND(302*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="I57">
-        <f>ROUND(310*$B$1,0)</f>
+        <f>ROUND(76*$B$1,0)</f>
         <v/>
       </c>
       <c r="J57">
-        <f>ROUND(252*$B$1,0)</f>
+        <f>ROUND(62*$B$1,0)</f>
         <v/>
       </c>
       <c r="K57">
-        <f>ROUND(273*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="L57">
@@ -3447,44 +3447,44 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>170198876</t>
+          <t>165002270</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Enough Collagen Foundation Cover Up Ultra X10 21 тон</t>
+          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ BB</t>
         </is>
       </c>
       <c r="D58">
-        <f>ROUND(122*$B$1,0)</f>
+        <f>ROUND(70*$B$1,0)</f>
         <v/>
       </c>
       <c r="E58">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="F58">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="G58">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="H58">
-        <f>ROUND(120*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="I58">
-        <f>ROUND(123*$B$1,0)</f>
+        <f>ROUND(70*$B$1,0)</f>
         <v/>
       </c>
       <c r="J58">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="K58">
-        <f>ROUND(108*$B$1,0)</f>
+        <f>ROUND(62*$B$1,0)</f>
         <v/>
       </c>
       <c r="L58">
@@ -3500,44 +3500,44 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>238416010</t>
+          <t>212889028</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Enough Collagen Whitening Moisture Cream 3in1 50 N</t>
+          <t>Enoughcollagenwhiteningcovertip03</t>
         </is>
       </c>
       <c r="D59">
-        <f>ROUND(191*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="E59">
-        <f>ROUND(155*$B$1,0)</f>
+        <f>ROUND(43*$B$1,0)</f>
         <v/>
       </c>
       <c r="F59">
-        <f>ROUND(155*$B$1,0)</f>
+        <f>ROUND(43*$B$1,0)</f>
         <v/>
       </c>
       <c r="G59">
-        <f>ROUND(155*$B$1,0)</f>
+        <f>ROUND(43*$B$1,0)</f>
         <v/>
       </c>
       <c r="H59">
-        <f>ROUND(188*$B$1,0)</f>
+        <f>ROUND(53*$B$1,0)</f>
         <v/>
       </c>
       <c r="I59">
-        <f>ROUND(193*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="J59">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="K59">
-        <f>ROUND(170*$B$1,0)</f>
+        <f>ROUND(48*$B$1,0)</f>
         <v/>
       </c>
       <c r="L59">
@@ -3553,44 +3553,44 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>170198180</t>
+          <t>611747838</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Enough Rich Gold Double Wea Radiance Foundation 13 тон</t>
+          <t>Collagen_Enough_Moisture_Foundation_23</t>
         </is>
       </c>
       <c r="D60">
-        <f>ROUND(156*$B$1,0)</f>
+        <f>ROUND(41*$B$1,0)</f>
         <v/>
       </c>
       <c r="E60">
-        <f>ROUND(126*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="F60">
-        <f>ROUND(126*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="G60">
-        <f>ROUND(126*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="H60">
-        <f>ROUND(153*$B$1,0)</f>
+        <f>ROUND(40*$B$1,0)</f>
         <v/>
       </c>
       <c r="I60">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(41*$B$1,0)</f>
         <v/>
       </c>
       <c r="J60">
-        <f>ROUND(128*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="K60">
-        <f>ROUND(139*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="L60">
@@ -3606,44 +3606,44 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>170198109</t>
+          <t>151132052</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Enough Rich Gold Double Wea Radiance Foundation 21 тон</t>
+          <t>ENOUGH COLLAGEN 3IN1 21</t>
         </is>
       </c>
       <c r="D61">
-        <f>ROUND(106*$B$1,0)</f>
+        <f>ROUND(39*$B$1,0)</f>
         <v/>
       </c>
       <c r="E61">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="F61">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="G61">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="H61">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="I61">
-        <f>ROUND(107*$B$1,0)</f>
+        <f>ROUND(39*$B$1,0)</f>
         <v/>
       </c>
       <c r="J61">
-        <f>ROUND(87*$B$1,0)</f>
+        <f>ROUND(32*$B$1,0)</f>
         <v/>
       </c>
       <c r="K61">
-        <f>ROUND(94*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="L61">
@@ -3659,44 +3659,44 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>212889027</t>
+          <t>149197341</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N 1</t>
         </is>
       </c>
       <c r="D62">
-        <f>ROUND(78*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="E62">
-        <f>ROUND(63*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="F62">
-        <f>ROUND(63*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="G62">
-        <f>ROUND(63*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="H62">
-        <f>ROUND(77*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="I62">
-        <f>ROUND(79*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="J62">
-        <f>ROUND(64*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="K62">
-        <f>ROUND(69*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="L62">
@@ -3712,44 +3712,44 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>212889025</t>
+          <t>611717011</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip01</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #01</t>
         </is>
       </c>
       <c r="D63">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="E63">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="F63">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="G63">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="H63">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="I63">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="J63">
-        <f>ROUND(62*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="K63">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="L63">
@@ -3765,44 +3765,44 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>212889028</t>
+          <t>611744611</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip03</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02</t>
         </is>
       </c>
       <c r="D64">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="E64">
-        <f>ROUND(43*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F64">
-        <f>ROUND(43*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G64">
-        <f>ROUND(43*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H64">
-        <f>ROUND(53*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="I64">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="J64">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="K64">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="L64">
@@ -3818,44 +3818,44 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>307073881</t>
+          <t>151313163</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ETUDE Baking Powder BB Deep Cleansing Foam 160 мл N</t>
+          <t>Etude Baking Powder Crunch Pore Scrub</t>
         </is>
       </c>
       <c r="D65">
-        <f>ROUND(242*$B$1,0)</f>
+        <f>ROUND(1572*$B$1,0)</f>
         <v/>
       </c>
       <c r="E65">
-        <f>ROUND(196*$B$1,0)</f>
+        <f>ROUND(1273*$B$1,0)</f>
         <v/>
       </c>
       <c r="F65">
-        <f>ROUND(196*$B$1,0)</f>
+        <f>ROUND(1273*$B$1,0)</f>
         <v/>
       </c>
       <c r="G65">
-        <f>ROUND(196*$B$1,0)</f>
+        <f>ROUND(1273*$B$1,0)</f>
         <v/>
       </c>
       <c r="H65">
-        <f>ROUND(237*$B$1,0)</f>
+        <f>ROUND(1545*$B$1,0)</f>
         <v/>
       </c>
       <c r="I65">
-        <f>ROUND(244*$B$1,0)</f>
+        <f>ROUND(1585*$B$1,0)</f>
         <v/>
       </c>
       <c r="J65">
-        <f>ROUND(198*$B$1,0)</f>
+        <f>ROUND(1287*$B$1,0)</f>
         <v/>
       </c>
       <c r="K65">
-        <f>ROUND(215*$B$1,0)</f>
+        <f>ROUND(1396*$B$1,0)</f>
         <v/>
       </c>
       <c r="L65">
@@ -3871,44 +3871,44 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>151313163</t>
+          <t>169198316</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Etude Baking Powder Crunch Pore Scrub</t>
+          <t>Etude House Baking Powder Pore Cleansing Foam 160 ml бе</t>
         </is>
       </c>
       <c r="D66">
-        <f>ROUND(1572*$B$1,0)</f>
+        <f>ROUND(282*$B$1,0)</f>
         <v/>
       </c>
       <c r="E66">
-        <f>ROUND(1273*$B$1,0)</f>
+        <f>ROUND(228*$B$1,0)</f>
         <v/>
       </c>
       <c r="F66">
-        <f>ROUND(1273*$B$1,0)</f>
+        <f>ROUND(228*$B$1,0)</f>
         <v/>
       </c>
       <c r="G66">
-        <f>ROUND(1273*$B$1,0)</f>
+        <f>ROUND(228*$B$1,0)</f>
         <v/>
       </c>
       <c r="H66">
-        <f>ROUND(1545*$B$1,0)</f>
+        <f>ROUND(277*$B$1,0)</f>
         <v/>
       </c>
       <c r="I66">
-        <f>ROUND(1585*$B$1,0)</f>
+        <f>ROUND(284*$B$1,0)</f>
         <v/>
       </c>
       <c r="J66">
-        <f>ROUND(1287*$B$1,0)</f>
+        <f>ROUND(231*$B$1,0)</f>
         <v/>
       </c>
       <c r="K66">
-        <f>ROUND(1396*$B$1,0)</f>
+        <f>ROUND(250*$B$1,0)</f>
         <v/>
       </c>
       <c r="L66">
@@ -3924,44 +3924,44 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>149971127</t>
+          <t>307073881</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Etude Baking Powder Crunch Pore Scrub 1</t>
+          <t>ETUDE Baking Powder BB Deep Cleansing Foam 160 мл N</t>
         </is>
       </c>
       <c r="D67">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(242*$B$1,0)</f>
         <v/>
       </c>
       <c r="E67">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(196*$B$1,0)</f>
         <v/>
       </c>
       <c r="F67">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(196*$B$1,0)</f>
         <v/>
       </c>
       <c r="G67">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(196*$B$1,0)</f>
         <v/>
       </c>
       <c r="H67">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(237*$B$1,0)</f>
         <v/>
       </c>
       <c r="I67">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(244*$B$1,0)</f>
         <v/>
       </c>
       <c r="J67">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(198*$B$1,0)</f>
         <v/>
       </c>
       <c r="K67">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(215*$B$1,0)</f>
         <v/>
       </c>
       <c r="L67">
@@ -4030,44 +4030,44 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>169198316</t>
+          <t>149971127</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Etude House Baking Powder Pore Cleansing Foam 160 ml бе</t>
+          <t>Etude Baking Powder Crunch Pore Scrub 1</t>
         </is>
       </c>
       <c r="D69">
-        <f>ROUND(282*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="E69">
-        <f>ROUND(228*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="F69">
-        <f>ROUND(228*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="G69">
-        <f>ROUND(228*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="H69">
-        <f>ROUND(277*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="I69">
-        <f>ROUND(284*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="J69">
-        <f>ROUND(231*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="K69">
-        <f>ROUND(250*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="L69">
@@ -4083,44 +4083,44 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>207472742</t>
+          <t>168956391</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
+          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE</t>
         </is>
       </c>
       <c r="D70">
-        <f>ROUND(1789*$B$1,0)</f>
+        <f>ROUND(2528*$B$1,0)</f>
         <v/>
       </c>
       <c r="E70">
-        <f>ROUND(1449*$B$1,0)</f>
+        <f>ROUND(2047*$B$1,0)</f>
         <v/>
       </c>
       <c r="F70">
-        <f>ROUND(1449*$B$1,0)</f>
+        <f>ROUND(2047*$B$1,0)</f>
         <v/>
       </c>
       <c r="G70">
-        <f>ROUND(1449*$B$1,0)</f>
+        <f>ROUND(2047*$B$1,0)</f>
         <v/>
       </c>
       <c r="H70">
-        <f>ROUND(1758*$B$1,0)</f>
+        <f>ROUND(2485*$B$1,0)</f>
         <v/>
       </c>
       <c r="I70">
-        <f>ROUND(1803*$B$1,0)</f>
+        <f>ROUND(2549*$B$1,0)</f>
         <v/>
       </c>
       <c r="J70">
-        <f>ROUND(1465*$B$1,0)</f>
+        <f>ROUND(2070*$B$1,0)</f>
         <v/>
       </c>
       <c r="K70">
-        <f>ROUND(1589*$B$1,0)</f>
+        <f>ROUND(2246*$B$1,0)</f>
         <v/>
       </c>
       <c r="L70">
@@ -4136,44 +4136,44 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>710417367</t>
+          <t>207472742</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] 11</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
         </is>
       </c>
       <c r="D71">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(1789*$B$1,0)</f>
         <v/>
       </c>
       <c r="E71">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(1449*$B$1,0)</f>
         <v/>
       </c>
       <c r="F71">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(1449*$B$1,0)</f>
         <v/>
       </c>
       <c r="G71">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(1449*$B$1,0)</f>
         <v/>
       </c>
       <c r="H71">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(1758*$B$1,0)</f>
         <v/>
       </c>
       <c r="I71">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(1803*$B$1,0)</f>
         <v/>
       </c>
       <c r="J71">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(1465*$B$1,0)</f>
         <v/>
       </c>
       <c r="K71">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(1589*$B$1,0)</f>
         <v/>
       </c>
       <c r="L71">
@@ -4189,44 +4189,44 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>207476777</t>
+          <t>207476309</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
+          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditi</t>
         </is>
       </c>
       <c r="D72">
-        <f>ROUND(101*$B$1,0)</f>
+        <f>ROUND(568*$B$1,0)</f>
         <v/>
       </c>
       <c r="E72">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(460*$B$1,0)</f>
         <v/>
       </c>
       <c r="F72">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(460*$B$1,0)</f>
         <v/>
       </c>
       <c r="G72">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(460*$B$1,0)</f>
         <v/>
       </c>
       <c r="H72">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(558*$B$1,0)</f>
         <v/>
       </c>
       <c r="I72">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(572*$B$1,0)</f>
         <v/>
       </c>
       <c r="J72">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(465*$B$1,0)</f>
         <v/>
       </c>
       <c r="K72">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(504*$B$1,0)</f>
         <v/>
       </c>
       <c r="L72">
@@ -4242,44 +4242,44 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>207477077</t>
+          <t>169076150</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE CREAM</t>
         </is>
       </c>
       <c r="D73">
-        <f>ROUND(217*$B$1,0)</f>
+        <f>ROUND(516*$B$1,0)</f>
         <v/>
       </c>
       <c r="E73">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(418*$B$1,0)</f>
         <v/>
       </c>
       <c r="F73">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(418*$B$1,0)</f>
         <v/>
       </c>
       <c r="G73">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(418*$B$1,0)</f>
         <v/>
       </c>
       <c r="H73">
-        <f>ROUND(213*$B$1,0)</f>
+        <f>ROUND(507*$B$1,0)</f>
         <v/>
       </c>
       <c r="I73">
-        <f>ROUND(219*$B$1,0)</f>
+        <f>ROUND(520*$B$1,0)</f>
         <v/>
       </c>
       <c r="J73">
-        <f>ROUND(178*$B$1,0)</f>
+        <f>ROUND(422*$B$1,0)</f>
         <v/>
       </c>
       <c r="K73">
-        <f>ROUND(193*$B$1,0)</f>
+        <f>ROUND(458*$B$1,0)</f>
         <v/>
       </c>
       <c r="L73">
@@ -4295,44 +4295,44 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>212885914</t>
+          <t>207469760</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARMSTAY - Collagen Water Full Moist Rolling Eye Serum </t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
         </is>
       </c>
       <c r="D74">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(504*$B$1,0)</f>
         <v/>
       </c>
       <c r="E74">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(408*$B$1,0)</f>
         <v/>
       </c>
       <c r="F74">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(408*$B$1,0)</f>
         <v/>
       </c>
       <c r="G74">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(408*$B$1,0)</f>
         <v/>
       </c>
       <c r="H74">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(495*$B$1,0)</f>
         <v/>
       </c>
       <c r="I74">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(508*$B$1,0)</f>
         <v/>
       </c>
       <c r="J74">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(413*$B$1,0)</f>
         <v/>
       </c>
       <c r="K74">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(447*$B$1,0)</f>
         <v/>
       </c>
       <c r="L74">
@@ -4401,44 +4401,44 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>208708607</t>
+          <t>419630142</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [5</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
         </is>
       </c>
       <c r="D76">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(219*$B$1,0)</f>
         <v/>
       </c>
       <c r="E76">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(177*$B$1,0)</f>
         <v/>
       </c>
       <c r="F76">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(177*$B$1,0)</f>
         <v/>
       </c>
       <c r="G76">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(177*$B$1,0)</f>
         <v/>
       </c>
       <c r="H76">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(215*$B$1,0)</f>
         <v/>
       </c>
       <c r="I76">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(220*$B$1,0)</f>
         <v/>
       </c>
       <c r="J76">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(179*$B$1,0)</f>
         <v/>
       </c>
       <c r="K76">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(194*$B$1,0)</f>
         <v/>
       </c>
       <c r="L76">
@@ -4454,44 +4454,44 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>207469760</t>
+          <t>207477077</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
         </is>
       </c>
       <c r="D77">
-        <f>ROUND(504*$B$1,0)</f>
+        <f>ROUND(217*$B$1,0)</f>
         <v/>
       </c>
       <c r="E77">
-        <f>ROUND(408*$B$1,0)</f>
+        <f>ROUND(176*$B$1,0)</f>
         <v/>
       </c>
       <c r="F77">
-        <f>ROUND(408*$B$1,0)</f>
+        <f>ROUND(176*$B$1,0)</f>
         <v/>
       </c>
       <c r="G77">
-        <f>ROUND(408*$B$1,0)</f>
+        <f>ROUND(176*$B$1,0)</f>
         <v/>
       </c>
       <c r="H77">
-        <f>ROUND(495*$B$1,0)</f>
+        <f>ROUND(213*$B$1,0)</f>
         <v/>
       </c>
       <c r="I77">
-        <f>ROUND(508*$B$1,0)</f>
+        <f>ROUND(219*$B$1,0)</f>
         <v/>
       </c>
       <c r="J77">
-        <f>ROUND(413*$B$1,0)</f>
+        <f>ROUND(178*$B$1,0)</f>
         <v/>
       </c>
       <c r="K77">
-        <f>ROUND(447*$B$1,0)</f>
+        <f>ROUND(193*$B$1,0)</f>
         <v/>
       </c>
       <c r="L77">
@@ -4507,44 +4507,44 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>207476309</t>
+          <t>212885914</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditi</t>
+          <t xml:space="preserve">FARMSTAY - Collagen Water Full Moist Rolling Eye Serum </t>
         </is>
       </c>
       <c r="D78">
-        <f>ROUND(568*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="E78">
-        <f>ROUND(460*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="F78">
-        <f>ROUND(460*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="G78">
-        <f>ROUND(460*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="H78">
-        <f>ROUND(558*$B$1,0)</f>
+        <f>ROUND(103*$B$1,0)</f>
         <v/>
       </c>
       <c r="I78">
-        <f>ROUND(572*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="J78">
-        <f>ROUND(465*$B$1,0)</f>
+        <f>ROUND(86*$B$1,0)</f>
         <v/>
       </c>
       <c r="K78">
-        <f>ROUND(504*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="L78">
@@ -4560,44 +4560,44 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>208710540</t>
+          <t>207476777</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditi</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
         </is>
       </c>
       <c r="D79">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(101*$B$1,0)</f>
         <v/>
       </c>
       <c r="E79">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="F79">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="G79">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="H79">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(100*$B$1,0)</f>
         <v/>
       </c>
       <c r="I79">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="J79">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="K79">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="L79">
@@ -4613,44 +4613,44 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>168956391</t>
+          <t>208710540</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE</t>
+          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditi</t>
         </is>
       </c>
       <c r="D80">
-        <f>ROUND(2528*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="E80">
-        <f>ROUND(2047*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="F80">
-        <f>ROUND(2047*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="G80">
-        <f>ROUND(2047*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="H80">
-        <f>ROUND(2485*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="I80">
-        <f>ROUND(2549*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="J80">
-        <f>ROUND(2070*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="K80">
-        <f>ROUND(2246*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="L80">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>168958606</t>
+          <t>710417367</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE 1</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] 11</t>
         </is>
       </c>
       <c r="D81">
@@ -4719,44 +4719,44 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>419630142</t>
+          <t>168958606</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
+          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE 1</t>
         </is>
       </c>
       <c r="D82">
-        <f>ROUND(219*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="E82">
-        <f>ROUND(177*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="F82">
-        <f>ROUND(177*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="G82">
-        <f>ROUND(177*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="H82">
-        <f>ROUND(215*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="I82">
-        <f>ROUND(220*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="J82">
-        <f>ROUND(179*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="K82">
-        <f>ROUND(194*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="L82">
@@ -4772,44 +4772,44 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>169076150</t>
+          <t>208708607</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE CREAM</t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [5</t>
         </is>
       </c>
       <c r="D83">
-        <f>ROUND(516*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="E83">
-        <f>ROUND(418*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="F83">
-        <f>ROUND(418*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="G83">
-        <f>ROUND(418*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="H83">
-        <f>ROUND(507*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="I83">
-        <f>ROUND(520*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="J83">
-        <f>ROUND(422*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="K83">
-        <f>ROUND(458*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="L83">
@@ -4825,44 +4825,44 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>207465786</t>
+          <t>207466866</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HEIMISH - All Clean Balm Mandarin [120ml]</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
         </is>
       </c>
       <c r="D84">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(443*$B$1,0)</f>
         <v/>
       </c>
       <c r="E84">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(359*$B$1,0)</f>
         <v/>
       </c>
       <c r="F84">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(359*$B$1,0)</f>
         <v/>
       </c>
       <c r="G84">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(359*$B$1,0)</f>
         <v/>
       </c>
       <c r="H84">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(436*$B$1,0)</f>
         <v/>
       </c>
       <c r="I84">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(447*$B$1,0)</f>
         <v/>
       </c>
       <c r="J84">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(363*$B$1,0)</f>
         <v/>
       </c>
       <c r="K84">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(394*$B$1,0)</f>
         <v/>
       </c>
       <c r="L84">
@@ -4931,44 +4931,44 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>207466866</t>
+          <t>207465786</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
+          <t>HEIMISH - All Clean Balm Mandarin [120ml]</t>
         </is>
       </c>
       <c r="D86">
-        <f>ROUND(443*$B$1,0)</f>
+        <f>ROUND(92*$B$1,0)</f>
         <v/>
       </c>
       <c r="E86">
-        <f>ROUND(359*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="F86">
-        <f>ROUND(359*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="G86">
-        <f>ROUND(359*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="H86">
-        <f>ROUND(436*$B$1,0)</f>
+        <f>ROUND(91*$B$1,0)</f>
         <v/>
       </c>
       <c r="I86">
-        <f>ROUND(447*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="J86">
-        <f>ROUND(363*$B$1,0)</f>
+        <f>ROUND(76*$B$1,0)</f>
         <v/>
       </c>
       <c r="K86">
-        <f>ROUND(394*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="L86">
@@ -5037,44 +5037,44 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>206122859</t>
+          <t>206126372</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>I'm Sorry for My Skin Age Крем Capture Firming Enriched</t>
+          <t>I'm Sorry for My Skin Крем Age Capture Vitalizer</t>
         </is>
       </c>
       <c r="D88">
-        <f>ROUND(65*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="E88">
-        <f>ROUND(52*$B$1,0)</f>
+        <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
       <c r="F88">
-        <f>ROUND(52*$B$1,0)</f>
+        <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
       <c r="G88">
-        <f>ROUND(52*$B$1,0)</f>
+        <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
       <c r="H88">
-        <f>ROUND(64*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="I88">
-        <f>ROUND(65*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="J88">
-        <f>ROUND(53*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="K88">
-        <f>ROUND(58*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="L88">
@@ -5090,44 +5090,44 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>206126372</t>
+          <t>206122859</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>I'm Sorry for My Skin Крем Age Capture Vitalizer</t>
+          <t>I'm Sorry for My Skin Age Крем Capture Firming Enriched</t>
         </is>
       </c>
       <c r="D89">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(65*$B$1,0)</f>
         <v/>
       </c>
       <c r="E89">
-        <f>ROUND(60*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="F89">
-        <f>ROUND(60*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="G89">
-        <f>ROUND(60*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="H89">
-        <f>ROUND(73*$B$1,0)</f>
+        <f>ROUND(64*$B$1,0)</f>
         <v/>
       </c>
       <c r="I89">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(65*$B$1,0)</f>
         <v/>
       </c>
       <c r="J89">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(53*$B$1,0)</f>
         <v/>
       </c>
       <c r="K89">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(58*$B$1,0)</f>
         <v/>
       </c>
       <c r="L89">
@@ -5196,44 +5196,44 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>212883090</t>
+          <t>207482718</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml]</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
         </is>
       </c>
       <c r="D91">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(1453*$B$1,0)</f>
         <v/>
       </c>
       <c r="E91">
-        <f>ROUND(73*$B$1,0)</f>
+        <f>ROUND(1177*$B$1,0)</f>
         <v/>
       </c>
       <c r="F91">
-        <f>ROUND(73*$B$1,0)</f>
+        <f>ROUND(1177*$B$1,0)</f>
         <v/>
       </c>
       <c r="G91">
-        <f>ROUND(73*$B$1,0)</f>
+        <f>ROUND(1177*$B$1,0)</f>
         <v/>
       </c>
       <c r="H91">
-        <f>ROUND(88*$B$1,0)</f>
+        <f>ROUND(1429*$B$1,0)</f>
         <v/>
       </c>
       <c r="I91">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(1465*$B$1,0)</f>
         <v/>
       </c>
       <c r="J91">
-        <f>ROUND(73*$B$1,0)</f>
+        <f>ROUND(1191*$B$1,0)</f>
         <v/>
       </c>
       <c r="K91">
-        <f>ROUND(80*$B$1,0)</f>
+        <f>ROUND(1291*$B$1,0)</f>
         <v/>
       </c>
       <c r="L91">
@@ -5249,44 +5249,44 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>207483780</t>
+          <t>207483179</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
         </is>
       </c>
       <c r="D92">
+        <f>ROUND(218*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E92">
+        <f>ROUND(176*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F92">
+        <f>ROUND(176*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G92">
+        <f>ROUND(176*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H92">
+        <f>ROUND(214*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I92">
+        <f>ROUND(220*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J92">
+        <f>ROUND(178*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K92">
         <f>ROUND(193*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="E92">
-        <f>ROUND(156*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="F92">
-        <f>ROUND(156*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="G92">
-        <f>ROUND(156*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="H92">
-        <f>ROUND(189*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="I92">
-        <f>ROUND(194*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="J92">
-        <f>ROUND(158*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="K92">
-        <f>ROUND(171*$B$1,0)</f>
         <v/>
       </c>
       <c r="L92">
@@ -5302,44 +5302,44 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>212753217</t>
+          <t>207483780</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JIGOTT - Collagen Healing Cream [100ml]</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
         </is>
       </c>
       <c r="D93">
-        <f>ROUND(70*$B$1,0)</f>
+        <f>ROUND(193*$B$1,0)</f>
         <v/>
       </c>
       <c r="E93">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(156*$B$1,0)</f>
         <v/>
       </c>
       <c r="F93">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(156*$B$1,0)</f>
         <v/>
       </c>
       <c r="G93">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(156*$B$1,0)</f>
         <v/>
       </c>
       <c r="H93">
-        <f>ROUND(69*$B$1,0)</f>
+        <f>ROUND(189*$B$1,0)</f>
         <v/>
       </c>
       <c r="I93">
-        <f>ROUND(71*$B$1,0)</f>
+        <f>ROUND(194*$B$1,0)</f>
         <v/>
       </c>
       <c r="J93">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(158*$B$1,0)</f>
         <v/>
       </c>
       <c r="K93">
-        <f>ROUND(62*$B$1,0)</f>
+        <f>ROUND(171*$B$1,0)</f>
         <v/>
       </c>
       <c r="L93">
@@ -5355,44 +5355,44 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>212757456</t>
+          <t>212759698</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
         </is>
       </c>
       <c r="D94">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(166*$B$1,0)</f>
         <v/>
       </c>
       <c r="E94">
-        <f>ROUND(78*$B$1,0)</f>
+        <f>ROUND(134*$B$1,0)</f>
         <v/>
       </c>
       <c r="F94">
-        <f>ROUND(78*$B$1,0)</f>
+        <f>ROUND(134*$B$1,0)</f>
         <v/>
       </c>
       <c r="G94">
-        <f>ROUND(78*$B$1,0)</f>
+        <f>ROUND(134*$B$1,0)</f>
         <v/>
       </c>
       <c r="H94">
-        <f>ROUND(95*$B$1,0)</f>
+        <f>ROUND(163*$B$1,0)</f>
         <v/>
       </c>
       <c r="I94">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(167*$B$1,0)</f>
         <v/>
       </c>
       <c r="J94">
-        <f>ROUND(79*$B$1,0)</f>
+        <f>ROUND(136*$B$1,0)</f>
         <v/>
       </c>
       <c r="K94">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(147*$B$1,0)</f>
         <v/>
       </c>
       <c r="L94">
@@ -5408,44 +5408,44 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>255574453</t>
+          <t>212760119</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JIGOTT - MASK 15</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
         </is>
       </c>
       <c r="D95">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(104*$B$1,0)</f>
         <v/>
       </c>
       <c r="E95">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="F95">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="G95">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="H95">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="I95">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="J95">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="K95">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(92*$B$1,0)</f>
         <v/>
       </c>
       <c r="L95">
@@ -5461,44 +5461,44 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>212759698</t>
+          <t>212757456</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
         </is>
       </c>
       <c r="D96">
-        <f>ROUND(166*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="E96">
-        <f>ROUND(134*$B$1,0)</f>
+        <f>ROUND(78*$B$1,0)</f>
         <v/>
       </c>
       <c r="F96">
-        <f>ROUND(134*$B$1,0)</f>
+        <f>ROUND(78*$B$1,0)</f>
         <v/>
       </c>
       <c r="G96">
-        <f>ROUND(134*$B$1,0)</f>
+        <f>ROUND(78*$B$1,0)</f>
         <v/>
       </c>
       <c r="H96">
-        <f>ROUND(163*$B$1,0)</f>
+        <f>ROUND(95*$B$1,0)</f>
         <v/>
       </c>
       <c r="I96">
-        <f>ROUND(167*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="J96">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(79*$B$1,0)</f>
         <v/>
       </c>
       <c r="K96">
-        <f>ROUND(147*$B$1,0)</f>
+        <f>ROUND(86*$B$1,0)</f>
         <v/>
       </c>
       <c r="L96">
@@ -5514,44 +5514,44 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>207482718</t>
+          <t>212883090</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
+          <t>JIGOTT - Aura Secret Hyaluronec Acid Toner [300ml]</t>
         </is>
       </c>
       <c r="D97">
-        <f>ROUND(1453*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="E97">
-        <f>ROUND(1177*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="F97">
-        <f>ROUND(1177*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="G97">
-        <f>ROUND(1177*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="H97">
-        <f>ROUND(1429*$B$1,0)</f>
+        <f>ROUND(88*$B$1,0)</f>
         <v/>
       </c>
       <c r="I97">
-        <f>ROUND(1465*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="J97">
-        <f>ROUND(1191*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="K97">
-        <f>ROUND(1291*$B$1,0)</f>
+        <f>ROUND(80*$B$1,0)</f>
         <v/>
       </c>
       <c r="L97">
@@ -5567,44 +5567,44 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>207483179</t>
+          <t>212753217</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
+          <t>JIGOTT - Collagen Healing Cream [100ml]</t>
         </is>
       </c>
       <c r="D98">
-        <f>ROUND(218*$B$1,0)</f>
+        <f>ROUND(70*$B$1,0)</f>
         <v/>
       </c>
       <c r="E98">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="F98">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="G98">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="H98">
-        <f>ROUND(214*$B$1,0)</f>
+        <f>ROUND(69*$B$1,0)</f>
         <v/>
       </c>
       <c r="I98">
-        <f>ROUND(220*$B$1,0)</f>
+        <f>ROUND(71*$B$1,0)</f>
         <v/>
       </c>
       <c r="J98">
-        <f>ROUND(178*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="K98">
-        <f>ROUND(193*$B$1,0)</f>
+        <f>ROUND(62*$B$1,0)</f>
         <v/>
       </c>
       <c r="L98">
@@ -5620,44 +5620,44 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>212760119</t>
+          <t>255574453</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
+          <t>JIGOTT - MASK 15</t>
         </is>
       </c>
       <c r="D99">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="E99">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="F99">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="G99">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="H99">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="I99">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="J99">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="K99">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="L99">
@@ -5673,44 +5673,44 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>212713617</t>
+          <t>214964091</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Black Cocoon Home Esthetic Eye Patch [60ea</t>
+          <t>JMSOLUTION - Mask Pack Disney</t>
         </is>
       </c>
       <c r="D100">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(194*$B$1,0)</f>
         <v/>
       </c>
       <c r="E100">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(157*$B$1,0)</f>
         <v/>
       </c>
       <c r="F100">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(157*$B$1,0)</f>
         <v/>
       </c>
       <c r="G100">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(157*$B$1,0)</f>
         <v/>
       </c>
       <c r="H100">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(191*$B$1,0)</f>
         <v/>
       </c>
       <c r="I100">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(196*$B$1,0)</f>
         <v/>
       </c>
       <c r="J100">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="K100">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(172*$B$1,0)</f>
         <v/>
       </c>
       <c r="L100">
@@ -5779,44 +5779,44 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>333259566</t>
+          <t>236825103</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Black [8pcs]</t>
+          <t>JMSOLUTION-Marine Luminous Pearl Deep Moisture Mask Pea</t>
         </is>
       </c>
       <c r="D102">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="E102">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="F102">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="G102">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="H102">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="I102">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="J102">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="K102">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="L102">
@@ -5832,44 +5832,44 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>214964091</t>
+          <t>212717820</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Disney</t>
+          <t>JMSOLUTION - Prime Gold Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D103">
-        <f>ROUND(194*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="E103">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="F103">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="G103">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="H103">
-        <f>ROUND(191*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="I103">
-        <f>ROUND(196*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="J103">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="K103">
-        <f>ROUND(172*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="L103">
@@ -5885,44 +5885,44 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>212717820</t>
+          <t>333259566</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Prime Gold Eye Patch [60ea]</t>
+          <t>JMSOLUTION - Mask Pack Black [8pcs]</t>
         </is>
       </c>
       <c r="D104">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="E104">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F104">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G104">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H104">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="I104">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="J104">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="K104">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="L104">
@@ -5938,44 +5938,44 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>236825103</t>
+          <t>212713617</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>JMSOLUTION-Marine Luminous Pearl Deep Moisture Mask Pea</t>
+          <t>JMSOLUTION - Black Cocoon Home Esthetic Eye Patch [60ea</t>
         </is>
       </c>
       <c r="D105">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="E105">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F105">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G105">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H105">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="I105">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="J105">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="K105">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="L105">
@@ -6044,44 +6044,44 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>207818642</t>
+          <t>238359400</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml]</t>
+          <t>LEBELAGE - High Protection Extreme Sun Cream SPF50+ PA+</t>
         </is>
       </c>
       <c r="D107">
-        <f>ROUND(38*$B$1,0)</f>
+        <f>ROUND(541*$B$1,0)</f>
         <v/>
       </c>
       <c r="E107">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(438*$B$1,0)</f>
         <v/>
       </c>
       <c r="F107">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(438*$B$1,0)</f>
         <v/>
       </c>
       <c r="G107">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(438*$B$1,0)</f>
         <v/>
       </c>
       <c r="H107">
-        <f>ROUND(38*$B$1,0)</f>
+        <f>ROUND(532*$B$1,0)</f>
         <v/>
       </c>
       <c r="I107">
-        <f>ROUND(39*$B$1,0)</f>
+        <f>ROUND(546*$B$1,0)</f>
         <v/>
       </c>
       <c r="J107">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(443*$B$1,0)</f>
         <v/>
       </c>
       <c r="K107">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(481*$B$1,0)</f>
         <v/>
       </c>
       <c r="L107">
@@ -6097,44 +6097,44 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>210575566</t>
+          <t>238359757</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
+          <t>LEBELAGE - High Protection Long Lasting Sun Cream SPF50</t>
         </is>
       </c>
       <c r="D108">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(479*$B$1,0)</f>
         <v/>
       </c>
       <c r="E108">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(388*$B$1,0)</f>
         <v/>
       </c>
       <c r="F108">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(388*$B$1,0)</f>
         <v/>
       </c>
       <c r="G108">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(388*$B$1,0)</f>
         <v/>
       </c>
       <c r="H108">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(471*$B$1,0)</f>
         <v/>
       </c>
       <c r="I108">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(483*$B$1,0)</f>
         <v/>
       </c>
       <c r="J108">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(392*$B$1,0)</f>
         <v/>
       </c>
       <c r="K108">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(425*$B$1,0)</f>
         <v/>
       </c>
       <c r="L108">
@@ -6203,44 +6203,44 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>165008074</t>
+          <t>207818642</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LEBELAGE - High Protection Daily No Sebum Sun Cream SPF</t>
+          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="D110">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="E110">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="F110">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="G110">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="H110">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="I110">
+        <f>ROUND(39*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J110">
+        <f>ROUND(31*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K110">
         <f>ROUND(34*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="J110">
-        <f>ROUND(27*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="K110">
-        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="L110">
@@ -6256,44 +6256,44 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>165008162</t>
+          <t>165008074</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LEBELAGE - High Protection Extreme Sun Cream SPF50+ PA+</t>
+          <t>LEBELAGE - High Protection Daily No Sebum Sun Cream SPF</t>
         </is>
       </c>
       <c r="D111">
-        <f>ROUND(20*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="E111">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="F111">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="G111">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="H111">
-        <f>ROUND(20*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="I111">
-        <f>ROUND(20*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="J111">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="K111">
-        <f>ROUND(18*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="L111">
@@ -6309,44 +6309,44 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>238359400</t>
+          <t>210575566</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>LEBELAGE - High Protection Extreme Sun Cream SPF50+ PA+</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="D112">
-        <f>ROUND(541*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="E112">
-        <f>ROUND(438*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="F112">
-        <f>ROUND(438*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="G112">
-        <f>ROUND(438*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="H112">
-        <f>ROUND(532*$B$1,0)</f>
+        <f>ROUND(32*$B$1,0)</f>
         <v/>
       </c>
       <c r="I112">
-        <f>ROUND(546*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="J112">
-        <f>ROUND(443*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="K112">
-        <f>ROUND(481*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="L112">
@@ -6362,44 +6362,44 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>238359757</t>
+          <t>165008162</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LEBELAGE - High Protection Long Lasting Sun Cream SPF50</t>
+          <t>LEBELAGE - High Protection Extreme Sun Cream SPF50+ PA+</t>
         </is>
       </c>
       <c r="D113">
-        <f>ROUND(479*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="E113">
-        <f>ROUND(388*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="F113">
-        <f>ROUND(388*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="G113">
-        <f>ROUND(388*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="H113">
-        <f>ROUND(471*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="I113">
-        <f>ROUND(483*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="J113">
-        <f>ROUND(392*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="K113">
-        <f>ROUND(425*$B$1,0)</f>
+        <f>ROUND(18*$B$1,0)</f>
         <v/>
       </c>
       <c r="L113">
@@ -6415,44 +6415,44 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>868575374</t>
+          <t>205054338</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
+          <t>manyo_bifida_biome_toner</t>
         </is>
       </c>
       <c r="D114">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(332*$B$1,0)</f>
         <v/>
       </c>
       <c r="E114">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(269*$B$1,0)</f>
         <v/>
       </c>
       <c r="F114">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(269*$B$1,0)</f>
         <v/>
       </c>
       <c r="G114">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(269*$B$1,0)</f>
         <v/>
       </c>
       <c r="H114">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(326*$B$1,0)</f>
         <v/>
       </c>
       <c r="I114">
-        <f>ROUND(42*$B$1,0)</f>
+        <f>ROUND(334*$B$1,0)</f>
         <v/>
       </c>
       <c r="J114">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(272*$B$1,0)</f>
         <v/>
       </c>
       <c r="K114">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(295*$B$1,0)</f>
         <v/>
       </c>
       <c r="L114">
@@ -6468,44 +6468,44 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>868700077</t>
+          <t>198156472</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
+          <t>Manyo_Galac_Vita_Serum</t>
         </is>
       </c>
       <c r="D115">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(261*$B$1,0)</f>
         <v/>
       </c>
       <c r="E115">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(212*$B$1,0)</f>
         <v/>
       </c>
       <c r="F115">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(212*$B$1,0)</f>
         <v/>
       </c>
       <c r="G115">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(212*$B$1,0)</f>
         <v/>
       </c>
       <c r="H115">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(257*$B$1,0)</f>
         <v/>
       </c>
       <c r="I115">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(264*$B$1,0)</f>
         <v/>
       </c>
       <c r="J115">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(214*$B$1,0)</f>
         <v/>
       </c>
       <c r="K115">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(232*$B$1,0)</f>
         <v/>
       </c>
       <c r="L115">
@@ -6521,44 +6521,44 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>198143251</t>
+          <t>198156698</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Manyo_Ampoule_Lotion</t>
+          <t>Manyo_Pure_Cleansing_Oil</t>
         </is>
       </c>
       <c r="D116">
-        <f>ROUND(55*$B$1,0)</f>
+        <f>ROUND(190*$B$1,0)</f>
         <v/>
       </c>
       <c r="E116">
-        <f>ROUND(45*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="F116">
-        <f>ROUND(45*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="G116">
-        <f>ROUND(45*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="H116">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(186*$B$1,0)</f>
         <v/>
       </c>
       <c r="I116">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(191*$B$1,0)</f>
         <v/>
       </c>
       <c r="J116">
-        <f>ROUND(45*$B$1,0)</f>
+        <f>ROUND(155*$B$1,0)</f>
         <v/>
       </c>
       <c r="K116">
-        <f>ROUND(49*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="L116">
@@ -6627,44 +6627,44 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>198156472</t>
+          <t>198143251</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Manyo_Galac_Vita_Serum</t>
+          <t>Manyo_Ampoule_Lotion</t>
         </is>
       </c>
       <c r="D118">
-        <f>ROUND(261*$B$1,0)</f>
+        <f>ROUND(55*$B$1,0)</f>
         <v/>
       </c>
       <c r="E118">
-        <f>ROUND(212*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="F118">
-        <f>ROUND(212*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="G118">
-        <f>ROUND(212*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="H118">
-        <f>ROUND(257*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="I118">
-        <f>ROUND(264*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="J118">
-        <f>ROUND(214*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="K118">
-        <f>ROUND(232*$B$1,0)</f>
+        <f>ROUND(49*$B$1,0)</f>
         <v/>
       </c>
       <c r="L118">
@@ -6680,44 +6680,44 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>198156698</t>
+          <t>868575374</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Manyo_Pure_Cleansing_Oil</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
         </is>
       </c>
       <c r="D119">
-        <f>ROUND(190*$B$1,0)</f>
+        <f>ROUND(41*$B$1,0)</f>
         <v/>
       </c>
       <c r="E119">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="F119">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="G119">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="H119">
-        <f>ROUND(186*$B$1,0)</f>
+        <f>ROUND(41*$B$1,0)</f>
         <v/>
       </c>
       <c r="I119">
-        <f>ROUND(191*$B$1,0)</f>
+        <f>ROUND(42*$B$1,0)</f>
         <v/>
       </c>
       <c r="J119">
-        <f>ROUND(155*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="K119">
-        <f>ROUND(168*$B$1,0)</f>
+        <f>ROUND(37*$B$1,0)</f>
         <v/>
       </c>
       <c r="L119">
@@ -6733,44 +6733,44 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>205054338</t>
+          <t>868700077</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>manyo_bifida_biome_toner</t>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
         </is>
       </c>
       <c r="D120">
-        <f>ROUND(332*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="E120">
-        <f>ROUND(269*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="F120">
-        <f>ROUND(269*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="G120">
-        <f>ROUND(269*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="H120">
-        <f>ROUND(326*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="I120">
-        <f>ROUND(334*$B$1,0)</f>
+        <f>ROUND(37*$B$1,0)</f>
         <v/>
       </c>
       <c r="J120">
-        <f>ROUND(272*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="K120">
-        <f>ROUND(295*$B$1,0)</f>
+        <f>ROUND(32*$B$1,0)</f>
         <v/>
       </c>
       <c r="L120">
@@ -6786,44 +6786,44 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>226115324</t>
+          <t>151175877</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
+          <t>Petitfee Agave Cooling Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="D121">
-        <f>ROUND(190*$B$1,0)</f>
+        <f>ROUND(250*$B$1,0)</f>
         <v/>
       </c>
       <c r="E121">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(202*$B$1,0)</f>
         <v/>
       </c>
       <c r="F121">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(202*$B$1,0)</f>
         <v/>
       </c>
       <c r="G121">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(202*$B$1,0)</f>
         <v/>
       </c>
       <c r="H121">
-        <f>ROUND(187*$B$1,0)</f>
+        <f>ROUND(246*$B$1,0)</f>
         <v/>
       </c>
       <c r="I121">
-        <f>ROUND(192*$B$1,0)</f>
+        <f>ROUND(252*$B$1,0)</f>
         <v/>
       </c>
       <c r="J121">
-        <f>ROUND(156*$B$1,0)</f>
+        <f>ROUND(205*$B$1,0)</f>
         <v/>
       </c>
       <c r="K121">
-        <f>ROUND(169*$B$1,0)</f>
+        <f>ROUND(222*$B$1,0)</f>
         <v/>
       </c>
       <c r="L121">
@@ -6839,44 +6839,44 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>226114831</t>
+          <t>151175880</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
+          <t>Petitfee Black Pearl &amp; Gold hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="D122">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(205*$B$1,0)</f>
         <v/>
       </c>
       <c r="E122">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(166*$B$1,0)</f>
         <v/>
       </c>
       <c r="F122">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(166*$B$1,0)</f>
         <v/>
       </c>
       <c r="G122">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(166*$B$1,0)</f>
         <v/>
       </c>
       <c r="H122">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(201*$B$1,0)</f>
         <v/>
       </c>
       <c r="I122">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(206*$B$1,0)</f>
         <v/>
       </c>
       <c r="J122">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="K122">
-        <f>ROUND(81*$B$1,0)</f>
+        <f>ROUND(182*$B$1,0)</f>
         <v/>
       </c>
       <c r="L122">
@@ -6892,44 +6892,44 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>226115478</t>
+          <t>226115324</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="D123">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(190*$B$1,0)</f>
         <v/>
       </c>
       <c r="E123">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="F123">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="G123">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="H123">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(187*$B$1,0)</f>
         <v/>
       </c>
       <c r="I123">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(192*$B$1,0)</f>
         <v/>
       </c>
       <c r="J123">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(156*$B$1,0)</f>
         <v/>
       </c>
       <c r="K123">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(169*$B$1,0)</f>
         <v/>
       </c>
       <c r="L123">
@@ -6945,44 +6945,44 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>226115248</t>
+          <t>226114935</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="D124">
-        <f>ROUND(123*$B$1,0)</f>
+        <f>ROUND(161*$B$1,0)</f>
         <v/>
       </c>
       <c r="E124">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="F124">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="G124">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="H124">
-        <f>ROUND(121*$B$1,0)</f>
+        <f>ROUND(158*$B$1,0)</f>
         <v/>
       </c>
       <c r="I124">
-        <f>ROUND(124*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="J124">
-        <f>ROUND(101*$B$1,0)</f>
+        <f>ROUND(132*$B$1,0)</f>
         <v/>
       </c>
       <c r="K124">
-        <f>ROUND(109*$B$1,0)</f>
+        <f>ROUND(143*$B$1,0)</f>
         <v/>
       </c>
       <c r="L124">
@@ -6998,44 +6998,44 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>226117746</t>
+          <t>179611278</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Mask Pack [5pc</t>
+          <t>Petitfee Artichoke Soothing Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="D125">
-        <f>ROUND(126*$B$1,0)</f>
+        <f>ROUND(146*$B$1,0)</f>
         <v/>
       </c>
       <c r="E125">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(118*$B$1,0)</f>
         <v/>
       </c>
       <c r="F125">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(118*$B$1,0)</f>
         <v/>
       </c>
       <c r="G125">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(118*$B$1,0)</f>
         <v/>
       </c>
       <c r="H125">
-        <f>ROUND(124*$B$1,0)</f>
+        <f>ROUND(144*$B$1,0)</f>
         <v/>
       </c>
       <c r="I125">
-        <f>ROUND(127*$B$1,0)</f>
+        <f>ROUND(147*$B$1,0)</f>
         <v/>
       </c>
       <c r="J125">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(120*$B$1,0)</f>
         <v/>
       </c>
       <c r="K125">
-        <f>ROUND(112*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="L125">
@@ -7104,44 +7104,44 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>226114935</t>
+          <t>226117746</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Mask Pack [5pc</t>
         </is>
       </c>
       <c r="D127">
-        <f>ROUND(161*$B$1,0)</f>
+        <f>ROUND(126*$B$1,0)</f>
         <v/>
       </c>
       <c r="E127">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="F127">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="G127">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="H127">
-        <f>ROUND(158*$B$1,0)</f>
+        <f>ROUND(124*$B$1,0)</f>
         <v/>
       </c>
       <c r="I127">
-        <f>ROUND(162*$B$1,0)</f>
+        <f>ROUND(127*$B$1,0)</f>
         <v/>
       </c>
       <c r="J127">
-        <f>ROUND(132*$B$1,0)</f>
+        <f>ROUND(103*$B$1,0)</f>
         <v/>
       </c>
       <c r="K127">
-        <f>ROUND(143*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="L127">
@@ -7157,44 +7157,44 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>664171648</t>
+          <t>226115248</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PETITFEE - MASK 5</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="D128">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(123*$B$1,0)</f>
         <v/>
       </c>
       <c r="E128">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(100*$B$1,0)</f>
         <v/>
       </c>
       <c r="F128">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(100*$B$1,0)</f>
         <v/>
       </c>
       <c r="G128">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(100*$B$1,0)</f>
         <v/>
       </c>
       <c r="H128">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(121*$B$1,0)</f>
         <v/>
       </c>
       <c r="I128">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(124*$B$1,0)</f>
         <v/>
       </c>
       <c r="J128">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(101*$B$1,0)</f>
         <v/>
       </c>
       <c r="K128">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(109*$B$1,0)</f>
         <v/>
       </c>
       <c r="L128">
@@ -7210,44 +7210,44 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>664171647</t>
+          <t>179611207</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PETITFEE - MASK 6</t>
+          <t>Petitfee GOLD &amp; SNAIL HYDROGEL EYE PATCH</t>
         </is>
       </c>
       <c r="D129">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(122*$B$1,0)</f>
         <v/>
       </c>
       <c r="E129">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="F129">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="G129">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="H129">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(120*$B$1,0)</f>
         <v/>
       </c>
       <c r="I129">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(123*$B$1,0)</f>
         <v/>
       </c>
       <c r="J129">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(100*$B$1,0)</f>
         <v/>
       </c>
       <c r="K129">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(109*$B$1,0)</f>
         <v/>
       </c>
       <c r="L129">
@@ -7263,44 +7263,44 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>180992464</t>
+          <t>226115478</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PETITFEE Aura Quartz Hydrogel Eye Mask Pure Opal</t>
+          <t>PETITFEE - Black Pearl &amp; Gold Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="D130">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(103*$B$1,0)</f>
         <v/>
       </c>
       <c r="E130">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="F130">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="G130">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="H130">
-        <f>ROUND(23*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="I130">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(104*$B$1,0)</f>
         <v/>
       </c>
       <c r="J130">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="K130">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(92*$B$1,0)</f>
         <v/>
       </c>
       <c r="L130">
@@ -7316,44 +7316,44 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>340752919</t>
+          <t>180988755</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>PETITFEE Black Pearl &amp; Gold Hydrogel Eye Patch/Gold Hyd</t>
+          <t>Petitfee B-Glucan Deep Firming Eye Mask</t>
         </is>
       </c>
       <c r="D131">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="E131">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="F131">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="G131">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="H131">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(92*$B$1,0)</f>
         <v/>
       </c>
       <c r="I131">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(94*$B$1,0)</f>
         <v/>
       </c>
       <c r="J131">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(76*$B$1,0)</f>
         <v/>
       </c>
       <c r="K131">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="L131">
@@ -7369,44 +7369,44 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>179611231</t>
+          <t>226114831</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Petitfee 98% Collagen &amp; CoQ10 Hydro Gel Eye Patch</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="D132">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(91*$B$1,0)</f>
         <v/>
       </c>
       <c r="E132">
-        <f>ROUND(35*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="F132">
-        <f>ROUND(35*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="G132">
-        <f>ROUND(35*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="H132">
-        <f>ROUND(43*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="I132">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(92*$B$1,0)</f>
         <v/>
       </c>
       <c r="J132">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="K132">
-        <f>ROUND(39*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="L132">
@@ -7422,44 +7422,44 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>151175877</t>
+          <t>179611318</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Petitfee Agave Cooling Hydrogel Eye Mask</t>
+          <t>Petitfee Chamomile Lightening Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="D133">
-        <f>ROUND(250*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="E133">
-        <f>ROUND(202*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="F133">
-        <f>ROUND(202*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="G133">
-        <f>ROUND(202*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="H133">
-        <f>ROUND(246*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="I133">
-        <f>ROUND(252*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="J133">
-        <f>ROUND(205*$B$1,0)</f>
+        <f>ROUND(69*$B$1,0)</f>
         <v/>
       </c>
       <c r="K133">
-        <f>ROUND(222*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="L133">
@@ -7475,44 +7475,44 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>179611278</t>
+          <t>180711104</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Petitfee Artichoke Soothing Hydrogel Eye Mask</t>
+          <t>Petitfee GOLD</t>
         </is>
       </c>
       <c r="D134">
-        <f>ROUND(146*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="E134">
-        <f>ROUND(118*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="F134">
-        <f>ROUND(118*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="G134">
-        <f>ROUND(118*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="H134">
-        <f>ROUND(144*$B$1,0)</f>
+        <f>ROUND(80*$B$1,0)</f>
         <v/>
       </c>
       <c r="I134">
-        <f>ROUND(147*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="J134">
-        <f>ROUND(120*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="K134">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(72*$B$1,0)</f>
         <v/>
       </c>
       <c r="L134">
@@ -7528,44 +7528,44 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>180988755</t>
+          <t>179611231</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Petitfee B-Glucan Deep Firming Eye Mask</t>
+          <t>Petitfee 98% Collagen &amp; CoQ10 Hydro Gel Eye Patch</t>
         </is>
       </c>
       <c r="D135">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="E135">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="F135">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="G135">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="H135">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(43*$B$1,0)</f>
         <v/>
       </c>
       <c r="I135">
-        <f>ROUND(94*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="J135">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="K135">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(39*$B$1,0)</f>
         <v/>
       </c>
       <c r="L135">
@@ -7581,44 +7581,44 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>151175880</t>
+          <t>180987509</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Petitfee Black Pearl &amp; Gold hydrogel Eye Patch</t>
+          <t>Petitfee Pink Vita Brightening Eye Mask</t>
         </is>
       </c>
       <c r="D136">
-        <f>ROUND(205*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="E136">
-        <f>ROUND(166*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="F136">
-        <f>ROUND(166*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="G136">
-        <f>ROUND(166*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="H136">
-        <f>ROUND(201*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="I136">
-        <f>ROUND(206*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="J136">
-        <f>ROUND(168*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="K136">
-        <f>ROUND(182*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="L136">
@@ -7634,44 +7634,44 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>179611304</t>
+          <t>180711041</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
+          <t>Petitfee EGF</t>
         </is>
       </c>
       <c r="D137">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="E137">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="F137">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="G137">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="H137">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="I137">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="J137">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="K137">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="L137">
@@ -7687,44 +7687,44 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>179611318</t>
+          <t>180992464</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Petitfee Chamomile Lightening Hydrogel Eye Mask</t>
+          <t>PETITFEE Aura Quartz Hydrogel Eye Mask Pure Opal</t>
         </is>
       </c>
       <c r="D138">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="E138">
-        <f>ROUND(68*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="F138">
-        <f>ROUND(68*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="G138">
-        <f>ROUND(68*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="H138">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="I138">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="J138">
-        <f>ROUND(69*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="K138">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="L138">
@@ -7740,44 +7740,44 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>180711041</t>
+          <t>664171647</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Petitfee EGF</t>
+          <t>PETITFEE - MASK 6</t>
         </is>
       </c>
       <c r="D139">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="E139">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="F139">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="G139">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="H139">
-        <f>ROUND(25*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="I139">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="J139">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="K139">
-        <f>ROUND(23*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="L139">
@@ -7793,44 +7793,44 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>180711104</t>
+          <t>179611304</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Petitfee GOLD</t>
+          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="D140">
-        <f>ROUND(81*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="E140">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="F140">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="G140">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="H140">
-        <f>ROUND(80*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="I140">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="J140">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="K140">
-        <f>ROUND(72*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="L140">
@@ -7846,44 +7846,44 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>179611207</t>
+          <t>664171648</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Petitfee GOLD &amp; SNAIL HYDROGEL EYE PATCH</t>
+          <t>PETITFEE - MASK 5</t>
         </is>
       </c>
       <c r="D141">
-        <f>ROUND(122*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="E141">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="F141">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="G141">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="H141">
-        <f>ROUND(120*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="I141">
-        <f>ROUND(123*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="J141">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="K141">
-        <f>ROUND(109*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="L141">
@@ -7899,44 +7899,44 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>180987509</t>
+          <t>340752919</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Petitfee Pink Vita Brightening Eye Mask</t>
+          <t>PETITFEE Black Pearl &amp; Gold Hydrogel Eye Patch/Gold Hyd</t>
         </is>
       </c>
       <c r="D142">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="E142">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F142">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G142">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H142">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="I142">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="J142">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="K142">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="L142">
@@ -8005,44 +8005,44 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>437203627</t>
+          <t>437231408</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CLEANSER_150ml</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING SUNSCREEN_50ml</t>
         </is>
       </c>
       <c r="D144">
-        <f>ROUND(59*$B$1,0)</f>
+        <f>ROUND(478*$B$1,0)</f>
         <v/>
       </c>
       <c r="E144">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(387*$B$1,0)</f>
         <v/>
       </c>
       <c r="F144">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(387*$B$1,0)</f>
         <v/>
       </c>
       <c r="G144">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(387*$B$1,0)</f>
         <v/>
       </c>
       <c r="H144">
-        <f>ROUND(58*$B$1,0)</f>
+        <f>ROUND(470*$B$1,0)</f>
         <v/>
       </c>
       <c r="I144">
-        <f>ROUND(60*$B$1,0)</f>
+        <f>ROUND(482*$B$1,0)</f>
         <v/>
       </c>
       <c r="J144">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(391*$B$1,0)</f>
         <v/>
       </c>
       <c r="K144">
-        <f>ROUND(52*$B$1,0)</f>
+        <f>ROUND(424*$B$1,0)</f>
         <v/>
       </c>
       <c r="L144">
@@ -8058,44 +8058,44 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>437190353</t>
+          <t>437845041</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
+          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT CREAM 50ml</t>
         </is>
       </c>
       <c r="D145">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="E145">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="F145">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="G145">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="H145">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(109*$B$1,0)</f>
         <v/>
       </c>
       <c r="I145">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="J145">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(91*$B$1,0)</f>
         <v/>
       </c>
       <c r="K145">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(98*$B$1,0)</f>
         <v/>
       </c>
       <c r="L145">
@@ -8111,44 +8111,44 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>437231408</t>
+          <t>437242640</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING SUNSCREEN_50ml</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
         </is>
       </c>
       <c r="D146">
-        <f>ROUND(478*$B$1,0)</f>
+        <f>ROUND(104*$B$1,0)</f>
         <v/>
       </c>
       <c r="E146">
-        <f>ROUND(387*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="F146">
-        <f>ROUND(387*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="G146">
-        <f>ROUND(387*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="H146">
-        <f>ROUND(470*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="I146">
-        <f>ROUND(482*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="J146">
-        <f>ROUND(391*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="K146">
-        <f>ROUND(424*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="L146">
@@ -8164,44 +8164,44 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>437242640</t>
+          <t>437797551</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
+          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT SERUM 30ml</t>
         </is>
       </c>
       <c r="D147">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="E147">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="F147">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="G147">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="H147">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(80*$B$1,0)</f>
         <v/>
       </c>
       <c r="I147">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="J147">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="K147">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(72*$B$1,0)</f>
         <v/>
       </c>
       <c r="L147">
@@ -8217,44 +8217,44 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>437248870</t>
+          <t>437776835</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING SOOTHING GEL_150ml</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
         </is>
       </c>
       <c r="D148">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
       <c r="E148">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(49*$B$1,0)</f>
         <v/>
       </c>
       <c r="F148">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(49*$B$1,0)</f>
         <v/>
       </c>
       <c r="G148">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(49*$B$1,0)</f>
         <v/>
       </c>
       <c r="H148">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(59*$B$1,0)</f>
         <v/>
       </c>
       <c r="I148">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="J148">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(49*$B$1,0)</f>
         <v/>
       </c>
       <c r="K148">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(53*$B$1,0)</f>
         <v/>
       </c>
       <c r="L148">
@@ -8270,44 +8270,44 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>437776835</t>
+          <t>437203627</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CLEANSER_150ml</t>
         </is>
       </c>
       <c r="D149">
+        <f>ROUND(59*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E149">
+        <f>ROUND(48*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F149">
+        <f>ROUND(48*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G149">
+        <f>ROUND(48*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H149">
+        <f>ROUND(58*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I149">
         <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
-      <c r="E149">
-        <f>ROUND(49*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="F149">
-        <f>ROUND(49*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="G149">
-        <f>ROUND(49*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="H149">
-        <f>ROUND(59*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="I149">
-        <f>ROUND(61*$B$1,0)</f>
-        <v/>
-      </c>
       <c r="J149">
-        <f>ROUND(49*$B$1,0)</f>
+        <f>ROUND(48*$B$1,0)</f>
         <v/>
       </c>
       <c r="K149">
-        <f>ROUND(53*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="L149">
@@ -8323,44 +8323,44 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>437850261</t>
+          <t>437248870</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml</t>
+          <t>ROUND LAB MUGWORT CALMING SOOTHING GEL_150ml</t>
         </is>
       </c>
       <c r="D150">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(41*$B$1,0)</f>
         <v/>
       </c>
       <c r="E150">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="F150">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="G150">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="H150">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(40*$B$1,0)</f>
         <v/>
       </c>
       <c r="I150">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(41*$B$1,0)</f>
         <v/>
       </c>
       <c r="J150">
-        <f>ROUND(23*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="K150">
-        <f>ROUND(25*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="L150">
@@ -8376,44 +8376,44 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>437254254</t>
+          <t>437190353</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
         </is>
       </c>
       <c r="D151">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="E151">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="F151">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="G151">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="H151">
+        <f>ROUND(36*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I151">
+        <f>ROUND(37*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J151">
+        <f>ROUND(30*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K151">
         <f>ROUND(32*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="I151">
-        <f>ROUND(33*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="J151">
-        <f>ROUND(27*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="K151">
-        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="L151">
@@ -8429,44 +8429,44 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>437845041</t>
+          <t>437254254</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT CREAM 50ml</t>
+          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml</t>
         </is>
       </c>
       <c r="D152">
-        <f>ROUND(111*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="E152">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="F152">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="G152">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="H152">
-        <f>ROUND(109*$B$1,0)</f>
+        <f>ROUND(32*$B$1,0)</f>
         <v/>
       </c>
       <c r="I152">
-        <f>ROUND(111*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="J152">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="K152">
-        <f>ROUND(98*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="L152">
@@ -8482,44 +8482,44 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>437797551</t>
+          <t>437850261</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT SERUM 30ml</t>
+          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml</t>
         </is>
       </c>
       <c r="D153">
-        <f>ROUND(81*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="E153">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="F153">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="G153">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="H153">
-        <f>ROUND(80*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="I153">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="J153">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="K153">
-        <f>ROUND(72*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="L153">
@@ -8853,44 +8853,44 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>154159632</t>
+          <t>214312837</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Baking Powder BB Deep Cleansing Foam 3в1 30</t>
+          <t>THE SAEM Saemmul Perfect Curling Mascara [8ml]</t>
         </is>
       </c>
       <c r="D160">
-        <f>ROUND(120*$B$1,0)</f>
+        <f>ROUND(172*$B$1,0)</f>
         <v/>
       </c>
       <c r="E160">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(139*$B$1,0)</f>
         <v/>
       </c>
       <c r="F160">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(139*$B$1,0)</f>
         <v/>
       </c>
       <c r="G160">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(139*$B$1,0)</f>
         <v/>
       </c>
       <c r="H160">
-        <f>ROUND(118*$B$1,0)</f>
+        <f>ROUND(169*$B$1,0)</f>
         <v/>
       </c>
       <c r="I160">
-        <f>ROUND(121*$B$1,0)</f>
+        <f>ROUND(173*$B$1,0)</f>
         <v/>
       </c>
       <c r="J160">
-        <f>ROUND(98*$B$1,0)</f>
+        <f>ROUND(141*$B$1,0)</f>
         <v/>
       </c>
       <c r="K160">
-        <f>ROUND(107*$B$1,0)</f>
+        <f>ROUND(153*$B$1,0)</f>
         <v/>
       </c>
       <c r="L160">
@@ -8906,44 +8906,44 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>183030830</t>
+          <t>154159632</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>HairSet/350/8*2</t>
+          <t>Baking Powder BB Deep Cleansing Foam 3в1 30</t>
         </is>
       </c>
       <c r="D161">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(120*$B$1,0)</f>
         <v/>
       </c>
       <c r="E161">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="F161">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="G161">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="H161">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(118*$B$1,0)</f>
         <v/>
       </c>
       <c r="I161">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(121*$B$1,0)</f>
         <v/>
       </c>
       <c r="J161">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(98*$B$1,0)</f>
         <v/>
       </c>
       <c r="K161">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(107*$B$1,0)</f>
         <v/>
       </c>
       <c r="L161">
@@ -8959,44 +8959,44 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>214312837</t>
+          <t>183030830</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>THE SAEM Saemmul Perfect Curling Mascara [8ml]</t>
+          <t>HairSet/350/8*2</t>
         </is>
       </c>
       <c r="D162">
-        <f>ROUND(172*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="E162">
-        <f>ROUND(139*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="F162">
-        <f>ROUND(139*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="G162">
-        <f>ROUND(139*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="H162">
-        <f>ROUND(169*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="I162">
-        <f>ROUND(173*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="J162">
-        <f>ROUND(141*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="K162">
-        <f>ROUND(153*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="L162">

--- a/outputs/plan/plan_prodazh_08.2026-03.2027.xlsx
+++ b/outputs/plan/plan_prodazh_08.2026-03.2027.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -63,11 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -435,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L164"/>
+  <dimension ref="A1:L171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -461,64 +466,69 @@
       <c r="B1" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>База: правильные помесячные Ракета 2026 H1 + сезонность 2024-2025 (осень до среднего). Метрика: продажи-возвраты, шт.</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Бренд</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Артикул</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Авг26</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Сен26</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Окт26</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Ноя26</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Дек26</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Янв27</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Фев27</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Мар27</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Итого 8 мес</t>
         </is>
@@ -541,35 +551,35 @@
         </is>
       </c>
       <c r="D3">
-        <f>ROUND(2499*$B$1,0)</f>
+        <f>ROUND(3878*$B$1,0)</f>
         <v/>
       </c>
       <c r="E3">
-        <f>ROUND(2024*$B$1,0)</f>
+        <f>ROUND(3263*$B$1,0)</f>
         <v/>
       </c>
       <c r="F3">
-        <f>ROUND(2024*$B$1,0)</f>
+        <f>ROUND(3263*$B$1,0)</f>
         <v/>
       </c>
       <c r="G3">
-        <f>ROUND(2024*$B$1,0)</f>
+        <f>ROUND(3263*$B$1,0)</f>
         <v/>
       </c>
       <c r="H3">
-        <f>ROUND(2457*$B$1,0)</f>
+        <f>ROUND(4032*$B$1,0)</f>
         <v/>
       </c>
       <c r="I3">
-        <f>ROUND(2520*$B$1,0)</f>
+        <f>ROUND(4196*$B$1,0)</f>
         <v/>
       </c>
       <c r="J3">
-        <f>ROUND(2047*$B$1,0)</f>
+        <f>ROUND(3180*$B$1,0)</f>
         <v/>
       </c>
       <c r="K3">
-        <f>ROUND(2220*$B$1,0)</f>
+        <f>ROUND(3822*$B$1,0)</f>
         <v/>
       </c>
       <c r="L3">
@@ -594,35 +604,35 @@
         </is>
       </c>
       <c r="D4">
-        <f>ROUND(549*$B$1,0)</f>
+        <f>ROUND(442*$B$1,0)</f>
         <v/>
       </c>
       <c r="E4">
-        <f>ROUND(445*$B$1,0)</f>
+        <f>ROUND(372*$B$1,0)</f>
         <v/>
       </c>
       <c r="F4">
-        <f>ROUND(445*$B$1,0)</f>
+        <f>ROUND(372*$B$1,0)</f>
         <v/>
       </c>
       <c r="G4">
-        <f>ROUND(445*$B$1,0)</f>
+        <f>ROUND(372*$B$1,0)</f>
         <v/>
       </c>
       <c r="H4">
-        <f>ROUND(540*$B$1,0)</f>
+        <f>ROUND(459*$B$1,0)</f>
         <v/>
       </c>
       <c r="I4">
-        <f>ROUND(554*$B$1,0)</f>
+        <f>ROUND(478*$B$1,0)</f>
         <v/>
       </c>
       <c r="J4">
-        <f>ROUND(450*$B$1,0)</f>
+        <f>ROUND(362*$B$1,0)</f>
         <v/>
       </c>
       <c r="K4">
-        <f>ROUND(488*$B$1,0)</f>
+        <f>ROUND(436*$B$1,0)</f>
         <v/>
       </c>
       <c r="L4">
@@ -647,35 +657,35 @@
         </is>
       </c>
       <c r="D5">
-        <f>ROUND(197*$B$1,0)</f>
+        <f>ROUND(132*$B$1,0)</f>
         <v/>
       </c>
       <c r="E5">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="F5">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="G5">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="H5">
-        <f>ROUND(193*$B$1,0)</f>
+        <f>ROUND(138*$B$1,0)</f>
         <v/>
       </c>
       <c r="I5">
-        <f>ROUND(198*$B$1,0)</f>
+        <f>ROUND(143*$B$1,0)</f>
         <v/>
       </c>
       <c r="J5">
-        <f>ROUND(161*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="K5">
-        <f>ROUND(175*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="L5">
@@ -691,44 +701,44 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>551540924</t>
+          <t>551600265</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
+          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30m</t>
         </is>
       </c>
       <c r="D6">
-        <f>ROUND(168*$B$1,0)</f>
+        <f>ROUND(132*$B$1,0)</f>
         <v/>
       </c>
       <c r="E6">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="F6">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="G6">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="H6">
-        <f>ROUND(165*$B$1,0)</f>
+        <f>ROUND(137*$B$1,0)</f>
         <v/>
       </c>
       <c r="I6">
-        <f>ROUND(170*$B$1,0)</f>
+        <f>ROUND(143*$B$1,0)</f>
         <v/>
       </c>
       <c r="J6">
-        <f>ROUND(138*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="K6">
-        <f>ROUND(149*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="L6">
@@ -744,44 +754,44 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>551616449</t>
+          <t>551540924</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING PAD [100ml / 40pads]</t>
         </is>
       </c>
       <c r="D7">
-        <f>ROUND(49*$B$1,0)</f>
+        <f>ROUND(104*$B$1,0)</f>
         <v/>
       </c>
       <c r="E7">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="F7">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="G7">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="H7">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="I7">
-        <f>ROUND(50*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="J7">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="K7">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="L7">
@@ -806,35 +816,35 @@
         </is>
       </c>
       <c r="D8">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="E8">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(55*$B$1,0)</f>
         <v/>
       </c>
       <c r="F8">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(55*$B$1,0)</f>
         <v/>
       </c>
       <c r="G8">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(55*$B$1,0)</f>
         <v/>
       </c>
       <c r="H8">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="I8">
-        <f>ROUND(38*$B$1,0)</f>
+        <f>ROUND(71*$B$1,0)</f>
         <v/>
       </c>
       <c r="J8">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="K8">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(65*$B$1,0)</f>
         <v/>
       </c>
       <c r="L8">
@@ -850,44 +860,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>551490295</t>
+          <t>551616449</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_10ml [10ml]</t>
+          <t>CELIMAX THE REAL NONI STARTER KIT (NEW) [30ml+10ml+10ml</t>
         </is>
       </c>
       <c r="D9">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="E9">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="F9">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="G9">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="H9">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(64*$B$1,0)</f>
         <v/>
       </c>
       <c r="I9">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="J9">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(50*$B$1,0)</f>
         <v/>
       </c>
       <c r="K9">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
       <c r="L9">
@@ -903,44 +913,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>551472457</t>
+          <t>551626041</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]</t>
+          <t>CELIMAX DUAL BARRIER TRIAL KIT [20ml+10ml]</t>
         </is>
       </c>
       <c r="D10">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="E10">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="F10">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="G10">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="H10">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="I10">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="J10">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="K10">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="L10">
@@ -956,44 +966,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>551600265</t>
+          <t>551490295</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CELIMAX JI WOO GAE CICA BHA BLEMISH TONER PAD_10EA [30m</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_10ml [10ml]</t>
         </is>
       </c>
       <c r="D11">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="E11">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="F11">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="G11">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="H11">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="I11">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="J11">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="K11">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="L11">
@@ -1009,44 +1019,44 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>551447345</t>
+          <t>551472457</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
+          <t>CELIMAX THE REAL NONI ENERGY AMPOULE_30ML (NEW) [30ml]</t>
         </is>
       </c>
       <c r="D12">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="E12">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="F12">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="G12">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="H12">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="I12">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="J12">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="K12">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="L12">
@@ -1062,44 +1072,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>551482493</t>
+          <t>551447345</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING CREAM [35ml]</t>
         </is>
       </c>
       <c r="D13">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="E13">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="F13">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="G13">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="H13">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="I13">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="J13">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="K13">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="L13">
@@ -1124,35 +1134,35 @@
         </is>
       </c>
       <c r="D14">
+        <f>ROUND(9*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E14">
         <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
-      <c r="E14">
-        <f>ROUND(6*$B$1,0)</f>
-        <v/>
-      </c>
       <c r="F14">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="G14">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="H14">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="I14">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="J14">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="K14">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="L14">
@@ -1163,49 +1173,49 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COSRX</t>
+          <t>CELIMAX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>207481714</t>
+          <t>551482493</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COSRX AHA/BHA Clarifying Treatment Toner [150ml]</t>
+          <t>CELIMAX PORE+DARK SPOT BRIGHTENING SERUM_30ml [30ml]</t>
         </is>
       </c>
       <c r="D15">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="E15">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F15">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G15">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H15">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="I15">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="J15">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="K15">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="L15">
@@ -1221,44 +1231,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>204258828</t>
+          <t>207481714</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>COSRX_Salicylic_Acid_Cleanser</t>
+          <t>COSRX AHA/BHA Clarifying Treatment Toner [150ml]</t>
         </is>
       </c>
       <c r="D16">
-        <f>ROUND(69*$B$1,0)</f>
+        <f>ROUND(76*$B$1,0)</f>
         <v/>
       </c>
       <c r="E16">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(64*$B$1,0)</f>
         <v/>
       </c>
       <c r="F16">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(64*$B$1,0)</f>
         <v/>
       </c>
       <c r="G16">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(64*$B$1,0)</f>
         <v/>
       </c>
       <c r="H16">
-        <f>ROUND(68*$B$1,0)</f>
+        <f>ROUND(80*$B$1,0)</f>
         <v/>
       </c>
       <c r="I16">
-        <f>ROUND(69*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="J16">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="K16">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="L16">
@@ -1274,44 +1284,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>207481251</t>
+          <t>204250060</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COSRX Advanced Snail 96 Mucin Power Essence [100ml]</t>
+          <t>COSRX_Low_pH_Gel_Cleanser</t>
         </is>
       </c>
       <c r="D17">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(71*$B$1,0)</f>
         <v/>
       </c>
       <c r="E17">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
       <c r="F17">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
       <c r="G17">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
       <c r="H17">
-        <f>ROUND(65*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="I17">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(77*$B$1,0)</f>
         <v/>
       </c>
       <c r="J17">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(58*$B$1,0)</f>
         <v/>
       </c>
       <c r="K17">
-        <f>ROUND(59*$B$1,0)</f>
+        <f>ROUND(70*$B$1,0)</f>
         <v/>
       </c>
       <c r="L17">
@@ -1322,49 +1332,49 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>COSRX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>214305722</t>
+          <t>204258828</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
+          <t>COSRX_Salicylic_Acid_Cleanser</t>
         </is>
       </c>
       <c r="D18">
-        <f>ROUND(161*$B$1,0)</f>
+        <f>ROUND(59*$B$1,0)</f>
         <v/>
       </c>
       <c r="E18">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(50*$B$1,0)</f>
         <v/>
       </c>
       <c r="F18">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(50*$B$1,0)</f>
         <v/>
       </c>
       <c r="G18">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(50*$B$1,0)</f>
         <v/>
       </c>
       <c r="H18">
-        <f>ROUND(158*$B$1,0)</f>
+        <f>ROUND(62*$B$1,0)</f>
         <v/>
       </c>
       <c r="I18">
-        <f>ROUND(162*$B$1,0)</f>
+        <f>ROUND(64*$B$1,0)</f>
         <v/>
       </c>
       <c r="J18">
-        <f>ROUND(132*$B$1,0)</f>
+        <f>ROUND(49*$B$1,0)</f>
         <v/>
       </c>
       <c r="K18">
-        <f>ROUND(143*$B$1,0)</f>
+        <f>ROUND(59*$B$1,0)</f>
         <v/>
       </c>
       <c r="L18">
@@ -1375,49 +1385,49 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DEOPROCE</t>
+          <t>COSRX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>214305705</t>
+          <t>207481251</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - ARGAN SILKY MOISTURE [1000ml]</t>
+          <t>COSRX Advanced Snail 96 Mucin Power Essence [100ml]</t>
         </is>
       </c>
       <c r="D19">
-        <f>ROUND(120*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="E19">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="F19">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="G19">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="H19">
-        <f>ROUND(118*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="I19">
-        <f>ROUND(121*$B$1,0)</f>
+        <f>ROUND(59*$B$1,0)</f>
         <v/>
       </c>
       <c r="J19">
-        <f>ROUND(98*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="K19">
-        <f>ROUND(107*$B$1,0)</f>
+        <f>ROUND(53*$B$1,0)</f>
         <v/>
       </c>
       <c r="L19">
@@ -1433,44 +1443,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>608841921</t>
+          <t>214305722</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[200ml]</t>
+          <t>DEOPROCE SHAMPOO+BALSAM - BLACK GARLIC[2000ml]</t>
         </is>
       </c>
       <c r="D20">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(134*$B$1,0)</f>
         <v/>
       </c>
       <c r="E20">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="F20">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="G20">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="H20">
-        <f>ROUND(81*$B$1,0)</f>
+        <f>ROUND(139*$B$1,0)</f>
         <v/>
       </c>
       <c r="I20">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(145*$B$1,0)</f>
         <v/>
       </c>
       <c r="J20">
-        <f>ROUND(68*$B$1,0)</f>
+        <f>ROUND(110*$B$1,0)</f>
         <v/>
       </c>
       <c r="K20">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(132*$B$1,0)</f>
         <v/>
       </c>
       <c r="L20">
@@ -1486,44 +1496,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>608837066</t>
+          <t>214305705</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] без колпачка</t>
+          <t>DEOPROCE SHAMPOO - ARGAN SILKY MOISTURE [1000ml]</t>
         </is>
       </c>
       <c r="D21">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="E21">
-        <f>ROUND(46*$B$1,0)</f>
+        <f>ROUND(94*$B$1,0)</f>
         <v/>
       </c>
       <c r="F21">
-        <f>ROUND(46*$B$1,0)</f>
+        <f>ROUND(94*$B$1,0)</f>
         <v/>
       </c>
       <c r="G21">
-        <f>ROUND(46*$B$1,0)</f>
+        <f>ROUND(94*$B$1,0)</f>
         <v/>
       </c>
       <c r="H21">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(116*$B$1,0)</f>
         <v/>
       </c>
       <c r="I21">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(121*$B$1,0)</f>
         <v/>
       </c>
       <c r="J21">
-        <f>ROUND(46*$B$1,0)</f>
+        <f>ROUND(92*$B$1,0)</f>
         <v/>
       </c>
       <c r="K21">
-        <f>ROUND(50*$B$1,0)</f>
+        <f>ROUND(110*$B$1,0)</f>
         <v/>
       </c>
       <c r="L21">
@@ -1539,44 +1549,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>608624295</t>
+          <t>608841921</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] с колпачком</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[200ml]</t>
         </is>
       </c>
       <c r="D22">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(64*$B$1,0)</f>
         <v/>
       </c>
       <c r="E22">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="F22">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="G22">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="H22">
-        <f>ROUND(43*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="I22">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(69*$B$1,0)</f>
         <v/>
       </c>
       <c r="J22">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="K22">
-        <f>ROUND(39*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="L22">
@@ -1592,44 +1602,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>214304883</t>
+          <t>608837066</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g]</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] без колпачка</t>
         </is>
       </c>
       <c r="D23">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="E23">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="F23">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="G23">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="H23">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(47*$B$1,0)</f>
         <v/>
       </c>
       <c r="I23">
-        <f>ROUND(35*$B$1,0)</f>
+        <f>ROUND(49*$B$1,0)</f>
         <v/>
       </c>
       <c r="J23">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(37*$B$1,0)</f>
         <v/>
       </c>
       <c r="K23">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="L23">
@@ -1645,44 +1655,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>214304289</t>
+          <t>608624295</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DEOPROCE - REAL FRESH VEGAN CALMING TONER [200ml]</t>
+          <t>DEOPROCE SHAMPOO - BLACK GARLIC[600ml] с колпачком</t>
         </is>
       </c>
       <c r="D24">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="E24">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="F24">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="G24">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="H24">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(37*$B$1,0)</f>
         <v/>
       </c>
       <c r="I24">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="J24">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="K24">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="L24">
@@ -1693,49 +1703,49 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DR. JART</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>199425671</t>
+          <t>214304883</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dr.Jart_Teatreatment_Soothing_Spot</t>
+          <t>DEOPROCE - SNAIL RECOVERY CREAM [100g]</t>
         </is>
       </c>
       <c r="D25">
-        <f>ROUND(71*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="E25">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="F25">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="G25">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="H25">
-        <f>ROUND(70*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="I25">
-        <f>ROUND(71*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="J25">
-        <f>ROUND(58*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="K25">
-        <f>ROUND(63*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="L25">
@@ -1746,49 +1756,49 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DR. JART</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>199367159</t>
+          <t>214304289</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dr.Jart_Dermaclear_Micro_Foam</t>
+          <t>DEOPROCE - REAL FRESH VEGAN CALMING TONER [200ml]</t>
         </is>
       </c>
       <c r="D26">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="E26">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="F26">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="G26">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="H26">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="I26">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="J26">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="K26">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="L26">
@@ -1799,49 +1809,49 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DR. JART</t>
+          <t>DEOPROCE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>212719009</t>
+          <t>214301052</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DR. JART - Cicapair Tiger Grass Color Correcting Treatm</t>
+          <t>DEOPROCE - AC CICA CALMING BOOSTING TONER [150ml]</t>
         </is>
       </c>
       <c r="D27">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="E27">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F27">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G27">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H27">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="I27">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="J27">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="K27">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="L27">
@@ -1852,49 +1862,49 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>EKEL</t>
+          <t>DR. JART</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>207479264</t>
+          <t>199425671</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EKEL Ampoule Cream Collagen [50ml]</t>
+          <t>Dr.Jart_Teatreatment_Soothing_Spot</t>
         </is>
       </c>
       <c r="D28">
-        <f>ROUND(197*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="E28">
-        <f>ROUND(160*$B$1,0)</f>
+        <f>ROUND(48*$B$1,0)</f>
         <v/>
       </c>
       <c r="F28">
-        <f>ROUND(160*$B$1,0)</f>
+        <f>ROUND(48*$B$1,0)</f>
         <v/>
       </c>
       <c r="G28">
-        <f>ROUND(160*$B$1,0)</f>
+        <f>ROUND(48*$B$1,0)</f>
         <v/>
       </c>
       <c r="H28">
-        <f>ROUND(194*$B$1,0)</f>
+        <f>ROUND(59*$B$1,0)</f>
         <v/>
       </c>
       <c r="I28">
-        <f>ROUND(199*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="J28">
-        <f>ROUND(162*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="K28">
-        <f>ROUND(175*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="L28">
@@ -1905,49 +1915,49 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>EKEL</t>
+          <t>DR. JART</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>190160197</t>
+          <t>199427475</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EKEL Ampoule Toner Collagen 150ml</t>
+          <t>Dr.Jart_Teatreatment_Toner</t>
         </is>
       </c>
       <c r="D29">
-        <f>ROUND(168*$B$1,0)</f>
+        <f>ROUND(50*$B$1,0)</f>
         <v/>
       </c>
       <c r="E29">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(42*$B$1,0)</f>
         <v/>
       </c>
       <c r="F29">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(42*$B$1,0)</f>
         <v/>
       </c>
       <c r="G29">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(42*$B$1,0)</f>
         <v/>
       </c>
       <c r="H29">
-        <f>ROUND(165*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="I29">
-        <f>ROUND(169*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="J29">
-        <f>ROUND(137*$B$1,0)</f>
+        <f>ROUND(41*$B$1,0)</f>
         <v/>
       </c>
       <c r="K29">
-        <f>ROUND(149*$B$1,0)</f>
+        <f>ROUND(49*$B$1,0)</f>
         <v/>
       </c>
       <c r="L29">
@@ -1958,49 +1968,49 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EKEL</t>
+          <t>DR. JART</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>208202076</t>
+          <t>199367159</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EKEL Ampule Сream Сollagen [70ml]</t>
+          <t>Dr.Jart_Dermaclear_Micro_Foam</t>
         </is>
       </c>
       <c r="D30">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="E30">
-        <f>ROUND(127*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="F30">
-        <f>ROUND(127*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="G30">
-        <f>ROUND(127*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="H30">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="I30">
-        <f>ROUND(158*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="J30">
-        <f>ROUND(128*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="K30">
-        <f>ROUND(139*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="L30">
@@ -2011,49 +2021,49 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>DR. JART</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>207796439</t>
+          <t>212719009</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Natural 90% Olive Cleansing Oil</t>
+          <t>DR. JART - Cicapair Tiger Grass Color Correcting Treatm</t>
         </is>
       </c>
       <c r="D31">
-        <f>ROUND(196*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="E31">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="F31">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="G31">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="H31">
-        <f>ROUND(192*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="I31">
-        <f>ROUND(197*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="J31">
-        <f>ROUND(160*$B$1,0)</f>
+        <f>ROUND(12*$B$1,0)</f>
         <v/>
       </c>
       <c r="K31">
-        <f>ROUND(174*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="L31">
@@ -2064,49 +2074,49 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>EKEL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>207796563</t>
+          <t>190160197</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream</t>
+          <t>EKEL Ampoule Toner Collagen 150ml</t>
         </is>
       </c>
       <c r="D32">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(193*$B$1,0)</f>
         <v/>
       </c>
       <c r="E32">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="F32">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="G32">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="H32">
-        <f>ROUND(156*$B$1,0)</f>
+        <f>ROUND(201*$B$1,0)</f>
         <v/>
       </c>
       <c r="I32">
-        <f>ROUND(160*$B$1,0)</f>
+        <f>ROUND(209*$B$1,0)</f>
         <v/>
       </c>
       <c r="J32">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(158*$B$1,0)</f>
         <v/>
       </c>
       <c r="K32">
-        <f>ROUND(141*$B$1,0)</f>
+        <f>ROUND(190*$B$1,0)</f>
         <v/>
       </c>
       <c r="L32">
@@ -2117,49 +2127,49 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>EKEL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>154163936</t>
+          <t>207479264</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Elizavecca Hell-Pore Control Hyaluronic Acid 97%</t>
+          <t>EKEL Ampoule Cream Collagen [50ml]</t>
         </is>
       </c>
       <c r="D33">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(156*$B$1,0)</f>
         <v/>
       </c>
       <c r="E33">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(131*$B$1,0)</f>
         <v/>
       </c>
       <c r="F33">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(131*$B$1,0)</f>
         <v/>
       </c>
       <c r="G33">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(131*$B$1,0)</f>
         <v/>
       </c>
       <c r="H33">
-        <f>ROUND(156*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="I33">
-        <f>ROUND(160*$B$1,0)</f>
+        <f>ROUND(169*$B$1,0)</f>
         <v/>
       </c>
       <c r="J33">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(128*$B$1,0)</f>
         <v/>
       </c>
       <c r="K33">
-        <f>ROUND(141*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="L33">
@@ -2170,49 +2180,49 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ELIZAVECCA</t>
+          <t>EKEL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>206057411</t>
+          <t>208202076</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ELIZAVECCA_fruit_toner</t>
+          <t>EKEL Ampule Сream Сollagen [70ml]</t>
         </is>
       </c>
       <c r="D34">
-        <f>ROUND(153*$B$1,0)</f>
+        <f>ROUND(137*$B$1,0)</f>
         <v/>
       </c>
       <c r="E34">
-        <f>ROUND(124*$B$1,0)</f>
+        <f>ROUND(115*$B$1,0)</f>
         <v/>
       </c>
       <c r="F34">
-        <f>ROUND(124*$B$1,0)</f>
+        <f>ROUND(115*$B$1,0)</f>
         <v/>
       </c>
       <c r="G34">
-        <f>ROUND(124*$B$1,0)</f>
+        <f>ROUND(115*$B$1,0)</f>
         <v/>
       </c>
       <c r="H34">
-        <f>ROUND(151*$B$1,0)</f>
+        <f>ROUND(142*$B$1,0)</f>
         <v/>
       </c>
       <c r="I34">
-        <f>ROUND(155*$B$1,0)</f>
+        <f>ROUND(148*$B$1,0)</f>
         <v/>
       </c>
       <c r="J34">
-        <f>ROUND(126*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="K34">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(135*$B$1,0)</f>
         <v/>
       </c>
       <c r="L34">
@@ -2228,44 +2238,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>190159348</t>
+          <t>207796563</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Elizavecca 24k gold snail Cleansing Foam 180ml</t>
+          <t>ELIZAVECCA - Aqua Hyaluronic Acid Water Drop Cream</t>
         </is>
       </c>
       <c r="D35">
-        <f>ROUND(140*$B$1,0)</f>
+        <f>ROUND(151*$B$1,0)</f>
         <v/>
       </c>
       <c r="E35">
-        <f>ROUND(114*$B$1,0)</f>
+        <f>ROUND(127*$B$1,0)</f>
         <v/>
       </c>
       <c r="F35">
-        <f>ROUND(114*$B$1,0)</f>
+        <f>ROUND(127*$B$1,0)</f>
         <v/>
       </c>
       <c r="G35">
-        <f>ROUND(114*$B$1,0)</f>
+        <f>ROUND(127*$B$1,0)</f>
         <v/>
       </c>
       <c r="H35">
-        <f>ROUND(138*$B$1,0)</f>
+        <f>ROUND(157*$B$1,0)</f>
         <v/>
       </c>
       <c r="I35">
-        <f>ROUND(141*$B$1,0)</f>
+        <f>ROUND(163*$B$1,0)</f>
         <v/>
       </c>
       <c r="J35">
-        <f>ROUND(115*$B$1,0)</f>
+        <f>ROUND(124*$B$1,0)</f>
         <v/>
       </c>
       <c r="K35">
-        <f>ROUND(125*$B$1,0)</f>
+        <f>ROUND(149*$B$1,0)</f>
         <v/>
       </c>
       <c r="L35">
@@ -2281,44 +2291,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>207796350</t>
+          <t>154163936</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ELIZAVECCA - CER-100  [100ml]</t>
+          <t>Elizavecca Hell-Pore Control Hyaluronic Acid 97%</t>
         </is>
       </c>
       <c r="D36">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(146*$B$1,0)</f>
         <v/>
       </c>
       <c r="E36">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(122*$B$1,0)</f>
         <v/>
       </c>
       <c r="F36">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(122*$B$1,0)</f>
         <v/>
       </c>
       <c r="G36">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(122*$B$1,0)</f>
         <v/>
       </c>
       <c r="H36">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(151*$B$1,0)</f>
         <v/>
       </c>
       <c r="I36">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(158*$B$1,0)</f>
         <v/>
       </c>
       <c r="J36">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(119*$B$1,0)</f>
         <v/>
       </c>
       <c r="K36">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(143*$B$1,0)</f>
         <v/>
       </c>
       <c r="L36">
@@ -2334,44 +2344,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>307071318</t>
+          <t>206057411</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Elizavecca Milky Piggy Carbonated Bubble Clay Mask N</t>
+          <t>ELIZAVECCA_fruit_toner</t>
         </is>
       </c>
       <c r="D37">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(143*$B$1,0)</f>
         <v/>
       </c>
       <c r="E37">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(120*$B$1,0)</f>
         <v/>
       </c>
       <c r="F37">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(120*$B$1,0)</f>
         <v/>
       </c>
       <c r="G37">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(120*$B$1,0)</f>
         <v/>
       </c>
       <c r="H37">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(148*$B$1,0)</f>
         <v/>
       </c>
       <c r="I37">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="J37">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(117*$B$1,0)</f>
         <v/>
       </c>
       <c r="K37">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(141*$B$1,0)</f>
         <v/>
       </c>
       <c r="L37">
@@ -2387,44 +2397,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>190160008</t>
+          <t>207796439</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Elizavecca Milky Piggy EGF elastic retinol [100ml]</t>
+          <t>ELIZAVECCA - Natural 90% Olive Cleansing Oil</t>
         </is>
       </c>
       <c r="D38">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(129*$B$1,0)</f>
         <v/>
       </c>
       <c r="E38">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="F38">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="G38">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="H38">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(134*$B$1,0)</f>
         <v/>
       </c>
       <c r="I38">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(139*$B$1,0)</f>
         <v/>
       </c>
       <c r="J38">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(106*$B$1,0)</f>
         <v/>
       </c>
       <c r="K38">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(127*$B$1,0)</f>
         <v/>
       </c>
       <c r="L38">
@@ -2435,49 +2445,49 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>238415286</t>
+          <t>190159348</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N</t>
+          <t>Elizavecca 24k gold snail Cleansing Foam 180ml</t>
         </is>
       </c>
       <c r="D39">
-        <f>ROUND(2426*$B$1,0)</f>
+        <f>ROUND(118*$B$1,0)</f>
         <v/>
       </c>
       <c r="E39">
-        <f>ROUND(1965*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="F39">
-        <f>ROUND(1965*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="G39">
-        <f>ROUND(1965*$B$1,0)</f>
+        <f>ROUND(99*$B$1,0)</f>
         <v/>
       </c>
       <c r="H39">
-        <f>ROUND(2385*$B$1,0)</f>
+        <f>ROUND(122*$B$1,0)</f>
         <v/>
       </c>
       <c r="I39">
-        <f>ROUND(2446*$B$1,0)</f>
+        <f>ROUND(127*$B$1,0)</f>
         <v/>
       </c>
       <c r="J39">
-        <f>ROUND(1987*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="K39">
-        <f>ROUND(2155*$B$1,0)</f>
+        <f>ROUND(116*$B$1,0)</f>
         <v/>
       </c>
       <c r="L39">
@@ -2488,49 +2498,49 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>238358954</t>
+          <t>207795785</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen 3in1 Sun Cream SPF50 PA++ [50ml] N</t>
+          <t>ELIZAVECCA - Milky Piggy Hell-Pore Clean Up Enzyme Powd</t>
         </is>
       </c>
       <c r="D40">
-        <f>ROUND(980*$B$1,0)</f>
+        <f>ROUND(107*$B$1,0)</f>
         <v/>
       </c>
       <c r="E40">
-        <f>ROUND(794*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="F40">
-        <f>ROUND(794*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="G40">
-        <f>ROUND(794*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="H40">
-        <f>ROUND(964*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="I40">
-        <f>ROUND(988*$B$1,0)</f>
+        <f>ROUND(116*$B$1,0)</f>
         <v/>
       </c>
       <c r="J40">
-        <f>ROUND(803*$B$1,0)</f>
+        <f>ROUND(88*$B$1,0)</f>
         <v/>
       </c>
       <c r="K40">
-        <f>ROUND(871*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="L40">
@@ -2541,49 +2551,49 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>238358009</t>
+          <t>307071318</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Sun Cream SPF50+ PA++++ [50m</t>
+          <t>Elizavecca Milky Piggy Carbonated Bubble Clay Mask N</t>
         </is>
       </c>
       <c r="D41">
-        <f>ROUND(730*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="E41">
-        <f>ROUND(592*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="F41">
-        <f>ROUND(592*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="G41">
-        <f>ROUND(592*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="H41">
-        <f>ROUND(718*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="I41">
-        <f>ROUND(736*$B$1,0)</f>
+        <f>ROUND(32*$B$1,0)</f>
         <v/>
       </c>
       <c r="J41">
-        <f>ROUND(598*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="K41">
-        <f>ROUND(649*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="L41">
@@ -2594,49 +2604,49 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>207796789</t>
+          <t>207796350</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13]</t>
+          <t>ELIZAVECCA - CER-100  [100ml]</t>
         </is>
       </c>
       <c r="D42">
-        <f>ROUND(442*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="E42">
-        <f>ROUND(358*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="F42">
-        <f>ROUND(358*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="G42">
-        <f>ROUND(358*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="H42">
-        <f>ROUND(435*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="I42">
-        <f>ROUND(446*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="J42">
-        <f>ROUND(362*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="K42">
-        <f>ROUND(393*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="L42">
@@ -2647,49 +2657,49 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENOUGH</t>
+          <t>ELIZAVECCA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>333318356</t>
+          <t>190160008</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Sun Cream SPF50+ PA++++ [50m</t>
+          <t>Elizavecca Milky Piggy EGF elastic retinol [100ml]</t>
         </is>
       </c>
       <c r="D43">
-        <f>ROUND(307*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="E43">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="F43">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="G43">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="H43">
-        <f>ROUND(302*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="I43">
-        <f>ROUND(310*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="J43">
-        <f>ROUND(252*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="K43">
-        <f>ROUND(273*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="L43">
@@ -2705,44 +2715,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>170198835</t>
+          <t>238415286</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Enough Collagen Foundation Cover Up Ultra X10 13 тон</t>
+          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N</t>
         </is>
       </c>
       <c r="D44">
-        <f>ROUND(307*$B$1,0)</f>
+        <f>ROUND(2134*$B$1,0)</f>
         <v/>
       </c>
       <c r="E44">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(1796*$B$1,0)</f>
         <v/>
       </c>
       <c r="F44">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(1796*$B$1,0)</f>
         <v/>
       </c>
       <c r="G44">
-        <f>ROUND(249*$B$1,0)</f>
+        <f>ROUND(1796*$B$1,0)</f>
         <v/>
       </c>
       <c r="H44">
-        <f>ROUND(302*$B$1,0)</f>
+        <f>ROUND(2219*$B$1,0)</f>
         <v/>
       </c>
       <c r="I44">
-        <f>ROUND(310*$B$1,0)</f>
+        <f>ROUND(2309*$B$1,0)</f>
         <v/>
       </c>
       <c r="J44">
-        <f>ROUND(252*$B$1,0)</f>
+        <f>ROUND(1750*$B$1,0)</f>
         <v/>
       </c>
       <c r="K44">
-        <f>ROUND(273*$B$1,0)</f>
+        <f>ROUND(2103*$B$1,0)</f>
         <v/>
       </c>
       <c r="L44">
@@ -2758,44 +2768,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>207796898</t>
+          <t>238358954</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21]</t>
+          <t>ENOUGH - Collagen 3in1 Sun Cream SPF50 PA++ [50ml] N</t>
         </is>
       </c>
       <c r="D45">
-        <f>ROUND(307*$B$1,0)</f>
+        <f>ROUND(722*$B$1,0)</f>
         <v/>
       </c>
       <c r="E45">
-        <f>ROUND(248*$B$1,0)</f>
+        <f>ROUND(607*$B$1,0)</f>
         <v/>
       </c>
       <c r="F45">
-        <f>ROUND(248*$B$1,0)</f>
+        <f>ROUND(607*$B$1,0)</f>
         <v/>
       </c>
       <c r="G45">
-        <f>ROUND(248*$B$1,0)</f>
+        <f>ROUND(607*$B$1,0)</f>
         <v/>
       </c>
       <c r="H45">
-        <f>ROUND(302*$B$1,0)</f>
+        <f>ROUND(750*$B$1,0)</f>
         <v/>
       </c>
       <c r="I45">
-        <f>ROUND(309*$B$1,0)</f>
+        <f>ROUND(781*$B$1,0)</f>
         <v/>
       </c>
       <c r="J45">
-        <f>ROUND(251*$B$1,0)</f>
+        <f>ROUND(592*$B$1,0)</f>
         <v/>
       </c>
       <c r="K45">
-        <f>ROUND(272*$B$1,0)</f>
+        <f>ROUND(711*$B$1,0)</f>
         <v/>
       </c>
       <c r="L45">
@@ -2811,44 +2821,44 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>238416010</t>
+          <t>238358009</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Enough Collagen Whitening Moisture Cream 3in1 50 N</t>
+          <t>ENOUGH - Collagen Moisture Sun Cream SPF50+ PA++++ [50m</t>
         </is>
       </c>
       <c r="D46">
-        <f>ROUND(191*$B$1,0)</f>
+        <f>ROUND(515*$B$1,0)</f>
         <v/>
       </c>
       <c r="E46">
-        <f>ROUND(155*$B$1,0)</f>
+        <f>ROUND(434*$B$1,0)</f>
         <v/>
       </c>
       <c r="F46">
-        <f>ROUND(155*$B$1,0)</f>
+        <f>ROUND(434*$B$1,0)</f>
         <v/>
       </c>
       <c r="G46">
-        <f>ROUND(155*$B$1,0)</f>
+        <f>ROUND(434*$B$1,0)</f>
         <v/>
       </c>
       <c r="H46">
-        <f>ROUND(188*$B$1,0)</f>
+        <f>ROUND(536*$B$1,0)</f>
         <v/>
       </c>
       <c r="I46">
-        <f>ROUND(193*$B$1,0)</f>
+        <f>ROUND(557*$B$1,0)</f>
         <v/>
       </c>
       <c r="J46">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(422*$B$1,0)</f>
         <v/>
       </c>
       <c r="K46">
-        <f>ROUND(170*$B$1,0)</f>
+        <f>ROUND(508*$B$1,0)</f>
         <v/>
       </c>
       <c r="L46">
@@ -2864,44 +2874,44 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>170198180</t>
+          <t>207796789</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Enough Rich Gold Double Wea Radiance Foundation 13 тон</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 13]</t>
         </is>
       </c>
       <c r="D47">
-        <f>ROUND(156*$B$1,0)</f>
+        <f>ROUND(370*$B$1,0)</f>
         <v/>
       </c>
       <c r="E47">
-        <f>ROUND(126*$B$1,0)</f>
+        <f>ROUND(311*$B$1,0)</f>
         <v/>
       </c>
       <c r="F47">
-        <f>ROUND(126*$B$1,0)</f>
+        <f>ROUND(311*$B$1,0)</f>
         <v/>
       </c>
       <c r="G47">
-        <f>ROUND(126*$B$1,0)</f>
+        <f>ROUND(311*$B$1,0)</f>
         <v/>
       </c>
       <c r="H47">
-        <f>ROUND(153*$B$1,0)</f>
+        <f>ROUND(385*$B$1,0)</f>
         <v/>
       </c>
       <c r="I47">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(400*$B$1,0)</f>
         <v/>
       </c>
       <c r="J47">
-        <f>ROUND(128*$B$1,0)</f>
+        <f>ROUND(303*$B$1,0)</f>
         <v/>
       </c>
       <c r="K47">
-        <f>ROUND(139*$B$1,0)</f>
+        <f>ROUND(365*$B$1,0)</f>
         <v/>
       </c>
       <c r="L47">
@@ -2917,44 +2927,44 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>170198876</t>
+          <t>333318356</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Enough Collagen Foundation Cover Up Ultra X10 21 тон</t>
+          <t>ENOUGH - Collagen Moisture Sun Cream SPF50+ PA++++ [50m</t>
         </is>
       </c>
       <c r="D48">
-        <f>ROUND(122*$B$1,0)</f>
+        <f>ROUND(259*$B$1,0)</f>
         <v/>
       </c>
       <c r="E48">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(218*$B$1,0)</f>
         <v/>
       </c>
       <c r="F48">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(218*$B$1,0)</f>
         <v/>
       </c>
       <c r="G48">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(218*$B$1,0)</f>
         <v/>
       </c>
       <c r="H48">
-        <f>ROUND(120*$B$1,0)</f>
+        <f>ROUND(269*$B$1,0)</f>
         <v/>
       </c>
       <c r="I48">
-        <f>ROUND(123*$B$1,0)</f>
+        <f>ROUND(280*$B$1,0)</f>
         <v/>
       </c>
       <c r="J48">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(212*$B$1,0)</f>
         <v/>
       </c>
       <c r="K48">
-        <f>ROUND(108*$B$1,0)</f>
+        <f>ROUND(255*$B$1,0)</f>
         <v/>
       </c>
       <c r="L48">
@@ -2970,44 +2980,44 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>170198738</t>
+          <t>207796898</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide Full Cover Perfect Foundation 13 тон</t>
+          <t>ENOUGH - Gold Snail Moisture Foundation [Tone 21]</t>
         </is>
       </c>
       <c r="D49">
-        <f>ROUND(112*$B$1,0)</f>
+        <f>ROUND(236*$B$1,0)</f>
         <v/>
       </c>
       <c r="E49">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(199*$B$1,0)</f>
         <v/>
       </c>
       <c r="F49">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(199*$B$1,0)</f>
         <v/>
       </c>
       <c r="G49">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(199*$B$1,0)</f>
         <v/>
       </c>
       <c r="H49">
-        <f>ROUND(110*$B$1,0)</f>
+        <f>ROUND(245*$B$1,0)</f>
         <v/>
       </c>
       <c r="I49">
-        <f>ROUND(112*$B$1,0)</f>
+        <f>ROUND(255*$B$1,0)</f>
         <v/>
       </c>
       <c r="J49">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(194*$B$1,0)</f>
         <v/>
       </c>
       <c r="K49">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(233*$B$1,0)</f>
         <v/>
       </c>
       <c r="L49">
@@ -3023,44 +3033,44 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>170198109</t>
+          <t>170198835</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Enough Rich Gold Double Wea Radiance Foundation 21 тон</t>
+          <t>Enough Collagen Foundation Cover Up Ultra X10 13 тон</t>
         </is>
       </c>
       <c r="D50">
-        <f>ROUND(106*$B$1,0)</f>
+        <f>ROUND(193*$B$1,0)</f>
         <v/>
       </c>
       <c r="E50">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="F50">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="G50">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="H50">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(201*$B$1,0)</f>
         <v/>
       </c>
       <c r="I50">
-        <f>ROUND(107*$B$1,0)</f>
+        <f>ROUND(209*$B$1,0)</f>
         <v/>
       </c>
       <c r="J50">
-        <f>ROUND(87*$B$1,0)</f>
+        <f>ROUND(158*$B$1,0)</f>
         <v/>
       </c>
       <c r="K50">
-        <f>ROUND(94*$B$1,0)</f>
+        <f>ROUND(190*$B$1,0)</f>
         <v/>
       </c>
       <c r="L50">
@@ -3076,44 +3086,44 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>170198337</t>
+          <t>238416010</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Enough 8 Peptide Full Cover Perfect Foundation 21 тон</t>
+          <t>Enough Collagen Whitening Moisture Cream 3in1 50 N</t>
         </is>
       </c>
       <c r="D51">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(182*$B$1,0)</f>
         <v/>
       </c>
       <c r="E51">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="F51">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="G51">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(154*$B$1,0)</f>
         <v/>
       </c>
       <c r="H51">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(190*$B$1,0)</f>
         <v/>
       </c>
       <c r="I51">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(197*$B$1,0)</f>
         <v/>
       </c>
       <c r="J51">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(150*$B$1,0)</f>
         <v/>
       </c>
       <c r="K51">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(180*$B$1,0)</f>
         <v/>
       </c>
       <c r="L51">
@@ -3129,44 +3139,44 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>150925322</t>
+          <t>150925321</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Collagen_Enough_Moisture_Foundation_21</t>
+          <t>Collagen_Enough_Moisture_Foundation_13</t>
         </is>
       </c>
       <c r="D52">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(177*$B$1,0)</f>
         <v/>
       </c>
       <c r="E52">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(149*$B$1,0)</f>
         <v/>
       </c>
       <c r="F52">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(149*$B$1,0)</f>
         <v/>
       </c>
       <c r="G52">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(149*$B$1,0)</f>
         <v/>
       </c>
       <c r="H52">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(184*$B$1,0)</f>
         <v/>
       </c>
       <c r="I52">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(192*$B$1,0)</f>
         <v/>
       </c>
       <c r="J52">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(145*$B$1,0)</f>
         <v/>
       </c>
       <c r="K52">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(175*$B$1,0)</f>
         <v/>
       </c>
       <c r="L52">
@@ -3182,44 +3192,44 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>151132051</t>
+          <t>170198180</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ENOUGH COLLAGEN 3IN1 13</t>
+          <t>Enough Rich Gold Double Wea Radiance Foundation 13 тон</t>
         </is>
       </c>
       <c r="D53">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(117*$B$1,0)</f>
         <v/>
       </c>
       <c r="E53">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(98*$B$1,0)</f>
         <v/>
       </c>
       <c r="F53">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(98*$B$1,0)</f>
         <v/>
       </c>
       <c r="G53">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(98*$B$1,0)</f>
         <v/>
       </c>
       <c r="H53">
-        <f>ROUND(101*$B$1,0)</f>
+        <f>ROUND(121*$B$1,0)</f>
         <v/>
       </c>
       <c r="I53">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(126*$B$1,0)</f>
         <v/>
       </c>
       <c r="J53">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="K53">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(115*$B$1,0)</f>
         <v/>
       </c>
       <c r="L53">
@@ -3235,44 +3245,44 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>150925321</t>
+          <t>170198337</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Collagen_Enough_Moisture_Foundation_13</t>
+          <t>Enough 8 Peptide Full Cover Perfect Foundation 21 тон</t>
         </is>
       </c>
       <c r="D54">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(114*$B$1,0)</f>
         <v/>
       </c>
       <c r="E54">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="F54">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="G54">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="H54">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(118*$B$1,0)</f>
         <v/>
       </c>
       <c r="I54">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(123*$B$1,0)</f>
         <v/>
       </c>
       <c r="J54">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="K54">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="L54">
@@ -3288,16 +3298,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>238413828</t>
+          <t>150925322</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ N</t>
+          <t>Collagen_Enough_Moisture_Foundation_21</t>
         </is>
       </c>
       <c r="D55">
-        <f>ROUND(101*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="E55">
@@ -3313,19 +3323,19 @@
         <v/>
       </c>
       <c r="H55">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(101*$B$1,0)</f>
         <v/>
       </c>
       <c r="I55">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="J55">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(80*$B$1,0)</f>
         <v/>
       </c>
       <c r="K55">
-        <f>ROUND(89*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="L55">
@@ -3341,44 +3351,44 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>212889027</t>
+          <t>170198876</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip</t>
+          <t>Enough Collagen Foundation Cover Up Ultra X10 21 тон</t>
         </is>
       </c>
       <c r="D56">
-        <f>ROUND(78*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="E56">
-        <f>ROUND(63*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="F56">
-        <f>ROUND(63*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="G56">
-        <f>ROUND(63*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="H56">
-        <f>ROUND(77*$B$1,0)</f>
+        <f>ROUND(101*$B$1,0)</f>
         <v/>
       </c>
       <c r="I56">
+        <f>ROUND(105*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J56">
         <f>ROUND(79*$B$1,0)</f>
         <v/>
       </c>
-      <c r="J56">
-        <f>ROUND(64*$B$1,0)</f>
-        <v/>
-      </c>
       <c r="K56">
-        <f>ROUND(69*$B$1,0)</f>
+        <f>ROUND(95*$B$1,0)</f>
         <v/>
       </c>
       <c r="L56">
@@ -3394,44 +3404,44 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>212889025</t>
+          <t>170198109</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip01</t>
+          <t>Enough Rich Gold Double Wea Radiance Foundation 21 тон</t>
         </is>
       </c>
       <c r="D57">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(94*$B$1,0)</f>
         <v/>
       </c>
       <c r="E57">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(79*$B$1,0)</f>
         <v/>
       </c>
       <c r="F57">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(79*$B$1,0)</f>
         <v/>
       </c>
       <c r="G57">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(79*$B$1,0)</f>
         <v/>
       </c>
       <c r="H57">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(98*$B$1,0)</f>
         <v/>
       </c>
       <c r="I57">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="J57">
-        <f>ROUND(62*$B$1,0)</f>
+        <f>ROUND(77*$B$1,0)</f>
         <v/>
       </c>
       <c r="K57">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="L57">
@@ -3447,44 +3457,44 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>165002270</t>
+          <t>151132051</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ BB</t>
+          <t xml:space="preserve"> ENOUGH COLLAGEN 3IN1 13</t>
         </is>
       </c>
       <c r="D58">
-        <f>ROUND(70*$B$1,0)</f>
+        <f>ROUND(89*$B$1,0)</f>
         <v/>
       </c>
       <c r="E58">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="F58">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="G58">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="H58">
-        <f>ROUND(68*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="I58">
-        <f>ROUND(70*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="J58">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="K58">
-        <f>ROUND(62*$B$1,0)</f>
+        <f>ROUND(88*$B$1,0)</f>
         <v/>
       </c>
       <c r="L58">
@@ -3500,44 +3510,44 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>212889028</t>
+          <t>170198738</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Enoughcollagenwhiteningcovertip03</t>
+          <t>Enough 8 Peptide Full Cover Perfect Foundation 13 тон</t>
         </is>
       </c>
       <c r="D59">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(86*$B$1,0)</f>
         <v/>
       </c>
       <c r="E59">
-        <f>ROUND(43*$B$1,0)</f>
+        <f>ROUND(72*$B$1,0)</f>
         <v/>
       </c>
       <c r="F59">
-        <f>ROUND(43*$B$1,0)</f>
+        <f>ROUND(72*$B$1,0)</f>
         <v/>
       </c>
       <c r="G59">
-        <f>ROUND(43*$B$1,0)</f>
+        <f>ROUND(72*$B$1,0)</f>
         <v/>
       </c>
       <c r="H59">
-        <f>ROUND(53*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="I59">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="J59">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(71*$B$1,0)</f>
         <v/>
       </c>
       <c r="K59">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="L59">
@@ -3553,44 +3563,44 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>611747838</t>
+          <t>238413828</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Collagen_Enough_Moisture_Foundation_23</t>
+          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ N</t>
         </is>
       </c>
       <c r="D60">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="E60">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(70*$B$1,0)</f>
         <v/>
       </c>
       <c r="F60">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(70*$B$1,0)</f>
         <v/>
       </c>
       <c r="G60">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(70*$B$1,0)</f>
         <v/>
       </c>
       <c r="H60">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="I60">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="J60">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="K60">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="L60">
@@ -3606,44 +3616,44 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>151132052</t>
+          <t>212889025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ENOUGH COLLAGEN 3IN1 21</t>
+          <t>Enoughcollagenwhiteningcovertip01</t>
         </is>
       </c>
       <c r="D61">
-        <f>ROUND(39*$B$1,0)</f>
+        <f>ROUND(69*$B$1,0)</f>
         <v/>
       </c>
       <c r="E61">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(58*$B$1,0)</f>
         <v/>
       </c>
       <c r="F61">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(58*$B$1,0)</f>
         <v/>
       </c>
       <c r="G61">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(58*$B$1,0)</f>
         <v/>
       </c>
       <c r="H61">
-        <f>ROUND(38*$B$1,0)</f>
+        <f>ROUND(71*$B$1,0)</f>
         <v/>
       </c>
       <c r="I61">
-        <f>ROUND(39*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="J61">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="K61">
-        <f>ROUND(35*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="L61">
@@ -3659,44 +3669,44 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>149197341</t>
+          <t>165002270</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ENOUGH - Collagen Moisture Essential Cream [50ml] N 1</t>
+          <t>ENOUGH collagen moisture BB Cream SPF47 PA+++ BB</t>
         </is>
       </c>
       <c r="D62">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="E62">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="F62">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="G62">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="H62">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="I62">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(59*$B$1,0)</f>
         <v/>
       </c>
       <c r="J62">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="K62">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(53*$B$1,0)</f>
         <v/>
       </c>
       <c r="L62">
@@ -3712,44 +3722,44 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>611717011</t>
+          <t>212889027</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #01</t>
+          <t>Enoughcollagenwhiteningcovertip</t>
         </is>
       </c>
       <c r="D63">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="E63">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="F63">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="G63">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="H63">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="I63">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(58*$B$1,0)</f>
         <v/>
       </c>
       <c r="J63">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="K63">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(53*$B$1,0)</f>
         <v/>
       </c>
       <c r="L63">
@@ -3765,44 +3775,44 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>611744611</t>
+          <t>611747838</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ENOUGH Collagen whitening cover tip concealer #02</t>
+          <t>Collagen_Enough_Moisture_Foundation_23</t>
         </is>
       </c>
       <c r="D64">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="E64">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="F64">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="G64">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="H64">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(47*$B$1,0)</f>
         <v/>
       </c>
       <c r="I64">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(49*$B$1,0)</f>
         <v/>
       </c>
       <c r="J64">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(37*$B$1,0)</f>
         <v/>
       </c>
       <c r="K64">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="L64">
@@ -3813,49 +3823,49 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>151313163</t>
+          <t>212889028</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Etude Baking Powder Crunch Pore Scrub</t>
+          <t>Enoughcollagenwhiteningcovertip03</t>
         </is>
       </c>
       <c r="D65">
-        <f>ROUND(1572*$B$1,0)</f>
+        <f>ROUND(37*$B$1,0)</f>
         <v/>
       </c>
       <c r="E65">
-        <f>ROUND(1273*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="F65">
-        <f>ROUND(1273*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="G65">
-        <f>ROUND(1273*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="H65">
-        <f>ROUND(1545*$B$1,0)</f>
+        <f>ROUND(39*$B$1,0)</f>
         <v/>
       </c>
       <c r="I65">
-        <f>ROUND(1585*$B$1,0)</f>
+        <f>ROUND(40*$B$1,0)</f>
         <v/>
       </c>
       <c r="J65">
-        <f>ROUND(1287*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="K65">
-        <f>ROUND(1396*$B$1,0)</f>
+        <f>ROUND(37*$B$1,0)</f>
         <v/>
       </c>
       <c r="L65">
@@ -3866,49 +3876,49 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>169198316</t>
+          <t>151132052</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Etude House Baking Powder Pore Cleansing Foam 160 ml бе</t>
+          <t xml:space="preserve"> ENOUGH COLLAGEN 3IN1 21</t>
         </is>
       </c>
       <c r="D66">
-        <f>ROUND(282*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="E66">
-        <f>ROUND(228*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="F66">
-        <f>ROUND(228*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="G66">
-        <f>ROUND(228*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="H66">
-        <f>ROUND(277*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="I66">
-        <f>ROUND(284*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="J66">
-        <f>ROUND(231*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="K66">
-        <f>ROUND(250*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="L66">
@@ -3919,49 +3929,49 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>307073881</t>
+          <t>611717011</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ETUDE Baking Powder BB Deep Cleansing Foam 160 мл N</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #01</t>
         </is>
       </c>
       <c r="D67">
-        <f>ROUND(242*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="E67">
-        <f>ROUND(196*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F67">
-        <f>ROUND(196*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G67">
-        <f>ROUND(196*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H67">
-        <f>ROUND(237*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="I67">
-        <f>ROUND(244*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="J67">
-        <f>ROUND(198*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="K67">
-        <f>ROUND(215*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="L67">
@@ -3972,49 +3982,49 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ETUDE</t>
+          <t>ENOUGH</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>154160085</t>
+          <t>611744611</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Etude Baking Powder Crunch Pore Scrub треугольники 30</t>
+          <t>ENOUGH Collagen whitening cover tip concealer #02</t>
         </is>
       </c>
       <c r="D68">
-        <f>ROUND(106*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="E68">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(5*$B$1,0)</f>
         <v/>
       </c>
       <c r="F68">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(5*$B$1,0)</f>
         <v/>
       </c>
       <c r="G68">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(5*$B$1,0)</f>
         <v/>
       </c>
       <c r="H68">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="I68">
-        <f>ROUND(107*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="J68">
-        <f>ROUND(87*$B$1,0)</f>
+        <f>ROUND(5*$B$1,0)</f>
         <v/>
       </c>
       <c r="K68">
-        <f>ROUND(94*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="L68">
@@ -4030,44 +4040,44 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>149971127</t>
+          <t>151313163</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Etude Baking Powder Crunch Pore Scrub 1</t>
+          <t>Etude Baking Powder Crunch Pore Scrub</t>
         </is>
       </c>
       <c r="D69">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(1352*$B$1,0)</f>
         <v/>
       </c>
       <c r="E69">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(1137*$B$1,0)</f>
         <v/>
       </c>
       <c r="F69">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(1137*$B$1,0)</f>
         <v/>
       </c>
       <c r="G69">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(1137*$B$1,0)</f>
         <v/>
       </c>
       <c r="H69">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(1406*$B$1,0)</f>
         <v/>
       </c>
       <c r="I69">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(1463*$B$1,0)</f>
         <v/>
       </c>
       <c r="J69">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(1108*$B$1,0)</f>
         <v/>
       </c>
       <c r="K69">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(1332*$B$1,0)</f>
         <v/>
       </c>
       <c r="L69">
@@ -4078,49 +4088,49 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>168956391</t>
+          <t>169198316</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE</t>
+          <t>Etude House Baking Powder Pore Cleansing Foam 160 ml бе</t>
         </is>
       </c>
       <c r="D70">
-        <f>ROUND(2528*$B$1,0)</f>
+        <f>ROUND(231*$B$1,0)</f>
         <v/>
       </c>
       <c r="E70">
-        <f>ROUND(2047*$B$1,0)</f>
+        <f>ROUND(195*$B$1,0)</f>
         <v/>
       </c>
       <c r="F70">
-        <f>ROUND(2047*$B$1,0)</f>
+        <f>ROUND(195*$B$1,0)</f>
         <v/>
       </c>
       <c r="G70">
-        <f>ROUND(2047*$B$1,0)</f>
+        <f>ROUND(195*$B$1,0)</f>
         <v/>
       </c>
       <c r="H70">
-        <f>ROUND(2485*$B$1,0)</f>
+        <f>ROUND(240*$B$1,0)</f>
         <v/>
       </c>
       <c r="I70">
-        <f>ROUND(2549*$B$1,0)</f>
+        <f>ROUND(250*$B$1,0)</f>
         <v/>
       </c>
       <c r="J70">
-        <f>ROUND(2070*$B$1,0)</f>
+        <f>ROUND(190*$B$1,0)</f>
         <v/>
       </c>
       <c r="K70">
-        <f>ROUND(2246*$B$1,0)</f>
+        <f>ROUND(228*$B$1,0)</f>
         <v/>
       </c>
       <c r="L70">
@@ -4131,49 +4141,49 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>207472742</t>
+          <t>307073881</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
+          <t>ETUDE Baking Powder BB Deep Cleansing Foam 160 мл N</t>
         </is>
       </c>
       <c r="D71">
-        <f>ROUND(1789*$B$1,0)</f>
+        <f>ROUND(174*$B$1,0)</f>
         <v/>
       </c>
       <c r="E71">
-        <f>ROUND(1449*$B$1,0)</f>
+        <f>ROUND(146*$B$1,0)</f>
         <v/>
       </c>
       <c r="F71">
-        <f>ROUND(1449*$B$1,0)</f>
+        <f>ROUND(146*$B$1,0)</f>
         <v/>
       </c>
       <c r="G71">
-        <f>ROUND(1449*$B$1,0)</f>
+        <f>ROUND(146*$B$1,0)</f>
         <v/>
       </c>
       <c r="H71">
-        <f>ROUND(1758*$B$1,0)</f>
+        <f>ROUND(180*$B$1,0)</f>
         <v/>
       </c>
       <c r="I71">
-        <f>ROUND(1803*$B$1,0)</f>
+        <f>ROUND(188*$B$1,0)</f>
         <v/>
       </c>
       <c r="J71">
-        <f>ROUND(1465*$B$1,0)</f>
+        <f>ROUND(142*$B$1,0)</f>
         <v/>
       </c>
       <c r="K71">
-        <f>ROUND(1589*$B$1,0)</f>
+        <f>ROUND(171*$B$1,0)</f>
         <v/>
       </c>
       <c r="L71">
@@ -4184,49 +4194,49 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>ETUDE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>207476309</t>
+          <t>154160085</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditi</t>
+          <t>Etude Baking Powder Crunch Pore Scrub треугольники 30</t>
         </is>
       </c>
       <c r="D72">
-        <f>ROUND(568*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="E72">
-        <f>ROUND(460*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="F72">
-        <f>ROUND(460*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="G72">
-        <f>ROUND(460*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="H72">
-        <f>ROUND(558*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="I72">
-        <f>ROUND(572*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="J72">
-        <f>ROUND(465*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="K72">
-        <f>ROUND(504*$B$1,0)</f>
+        <f>ROUND(88*$B$1,0)</f>
         <v/>
       </c>
       <c r="L72">
@@ -4242,44 +4252,44 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>169076150</t>
+          <t>168956391</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE CREAM</t>
+          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE</t>
         </is>
       </c>
       <c r="D73">
-        <f>ROUND(516*$B$1,0)</f>
+        <f>ROUND(2161*$B$1,0)</f>
         <v/>
       </c>
       <c r="E73">
-        <f>ROUND(418*$B$1,0)</f>
+        <f>ROUND(1818*$B$1,0)</f>
         <v/>
       </c>
       <c r="F73">
-        <f>ROUND(418*$B$1,0)</f>
+        <f>ROUND(1818*$B$1,0)</f>
         <v/>
       </c>
       <c r="G73">
-        <f>ROUND(418*$B$1,0)</f>
+        <f>ROUND(1818*$B$1,0)</f>
         <v/>
       </c>
       <c r="H73">
-        <f>ROUND(507*$B$1,0)</f>
+        <f>ROUND(2247*$B$1,0)</f>
         <v/>
       </c>
       <c r="I73">
-        <f>ROUND(520*$B$1,0)</f>
+        <f>ROUND(2338*$B$1,0)</f>
         <v/>
       </c>
       <c r="J73">
-        <f>ROUND(422*$B$1,0)</f>
+        <f>ROUND(1772*$B$1,0)</f>
         <v/>
       </c>
       <c r="K73">
-        <f>ROUND(458*$B$1,0)</f>
+        <f>ROUND(2130*$B$1,0)</f>
         <v/>
       </c>
       <c r="L73">
@@ -4295,44 +4305,44 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>207469760</t>
+          <t>207472742</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
+          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml]</t>
         </is>
       </c>
       <c r="D74">
-        <f>ROUND(504*$B$1,0)</f>
+        <f>ROUND(1557*$B$1,0)</f>
         <v/>
       </c>
       <c r="E74">
-        <f>ROUND(408*$B$1,0)</f>
+        <f>ROUND(1310*$B$1,0)</f>
         <v/>
       </c>
       <c r="F74">
-        <f>ROUND(408*$B$1,0)</f>
+        <f>ROUND(1310*$B$1,0)</f>
         <v/>
       </c>
       <c r="G74">
-        <f>ROUND(408*$B$1,0)</f>
+        <f>ROUND(1310*$B$1,0)</f>
         <v/>
       </c>
       <c r="H74">
-        <f>ROUND(495*$B$1,0)</f>
+        <f>ROUND(1619*$B$1,0)</f>
         <v/>
       </c>
       <c r="I74">
-        <f>ROUND(508*$B$1,0)</f>
+        <f>ROUND(1685*$B$1,0)</f>
         <v/>
       </c>
       <c r="J74">
-        <f>ROUND(413*$B$1,0)</f>
+        <f>ROUND(1277*$B$1,0)</f>
         <v/>
       </c>
       <c r="K74">
-        <f>ROUND(447*$B$1,0)</f>
+        <f>ROUND(1534*$B$1,0)</f>
         <v/>
       </c>
       <c r="L74">
@@ -4348,44 +4358,44 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>207475898</t>
+          <t>169076150</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [5</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE CREAM</t>
         </is>
       </c>
       <c r="D75">
-        <f>ROUND(401*$B$1,0)</f>
+        <f>ROUND(508*$B$1,0)</f>
         <v/>
       </c>
       <c r="E75">
-        <f>ROUND(325*$B$1,0)</f>
+        <f>ROUND(428*$B$1,0)</f>
         <v/>
       </c>
       <c r="F75">
-        <f>ROUND(325*$B$1,0)</f>
+        <f>ROUND(428*$B$1,0)</f>
         <v/>
       </c>
       <c r="G75">
-        <f>ROUND(325*$B$1,0)</f>
+        <f>ROUND(428*$B$1,0)</f>
         <v/>
       </c>
       <c r="H75">
-        <f>ROUND(395*$B$1,0)</f>
+        <f>ROUND(528*$B$1,0)</f>
         <v/>
       </c>
       <c r="I75">
-        <f>ROUND(405*$B$1,0)</f>
+        <f>ROUND(550*$B$1,0)</f>
         <v/>
       </c>
       <c r="J75">
-        <f>ROUND(329*$B$1,0)</f>
+        <f>ROUND(417*$B$1,0)</f>
         <v/>
       </c>
       <c r="K75">
-        <f>ROUND(357*$B$1,0)</f>
+        <f>ROUND(501*$B$1,0)</f>
         <v/>
       </c>
       <c r="L75">
@@ -4401,44 +4411,44 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>419630142</t>
+          <t>207469760</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
+          <t>FARMSTAY - Gold Snail Premium Cream [50ml]</t>
         </is>
       </c>
       <c r="D76">
-        <f>ROUND(219*$B$1,0)</f>
+        <f>ROUND(487*$B$1,0)</f>
         <v/>
       </c>
       <c r="E76">
-        <f>ROUND(177*$B$1,0)</f>
+        <f>ROUND(410*$B$1,0)</f>
         <v/>
       </c>
       <c r="F76">
-        <f>ROUND(177*$B$1,0)</f>
+        <f>ROUND(410*$B$1,0)</f>
         <v/>
       </c>
       <c r="G76">
-        <f>ROUND(177*$B$1,0)</f>
+        <f>ROUND(410*$B$1,0)</f>
         <v/>
       </c>
       <c r="H76">
-        <f>ROUND(215*$B$1,0)</f>
+        <f>ROUND(506*$B$1,0)</f>
         <v/>
       </c>
       <c r="I76">
-        <f>ROUND(220*$B$1,0)</f>
+        <f>ROUND(527*$B$1,0)</f>
         <v/>
       </c>
       <c r="J76">
-        <f>ROUND(179*$B$1,0)</f>
+        <f>ROUND(399*$B$1,0)</f>
         <v/>
       </c>
       <c r="K76">
-        <f>ROUND(194*$B$1,0)</f>
+        <f>ROUND(480*$B$1,0)</f>
         <v/>
       </c>
       <c r="L76">
@@ -4454,44 +4464,44 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>207477077</t>
+          <t>207476309</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
+          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditi</t>
         </is>
       </c>
       <c r="D77">
-        <f>ROUND(217*$B$1,0)</f>
+        <f>ROUND(473*$B$1,0)</f>
         <v/>
       </c>
       <c r="E77">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(398*$B$1,0)</f>
         <v/>
       </c>
       <c r="F77">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(398*$B$1,0)</f>
         <v/>
       </c>
       <c r="G77">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(398*$B$1,0)</f>
         <v/>
       </c>
       <c r="H77">
-        <f>ROUND(213*$B$1,0)</f>
+        <f>ROUND(491*$B$1,0)</f>
         <v/>
       </c>
       <c r="I77">
-        <f>ROUND(219*$B$1,0)</f>
+        <f>ROUND(511*$B$1,0)</f>
         <v/>
       </c>
       <c r="J77">
-        <f>ROUND(178*$B$1,0)</f>
+        <f>ROUND(387*$B$1,0)</f>
         <v/>
       </c>
       <c r="K77">
-        <f>ROUND(193*$B$1,0)</f>
+        <f>ROUND(466*$B$1,0)</f>
         <v/>
       </c>
       <c r="L77">
@@ -4507,44 +4517,44 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>212885914</t>
+          <t>207475898</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">FARMSTAY - Collagen Water Full Moist Rolling Eye Serum </t>
+          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [5</t>
         </is>
       </c>
       <c r="D78">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(354*$B$1,0)</f>
         <v/>
       </c>
       <c r="E78">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(298*$B$1,0)</f>
         <v/>
       </c>
       <c r="F78">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(298*$B$1,0)</f>
         <v/>
       </c>
       <c r="G78">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(298*$B$1,0)</f>
         <v/>
       </c>
       <c r="H78">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(368*$B$1,0)</f>
         <v/>
       </c>
       <c r="I78">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(383*$B$1,0)</f>
         <v/>
       </c>
       <c r="J78">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(290*$B$1,0)</f>
         <v/>
       </c>
       <c r="K78">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(349*$B$1,0)</f>
         <v/>
       </c>
       <c r="L78">
@@ -4560,44 +4570,44 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>207476777</t>
+          <t>207477077</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
+          <t>FARMSTAY - Collagen Water Full Moist Cream [100g]</t>
         </is>
       </c>
       <c r="D79">
-        <f>ROUND(101*$B$1,0)</f>
+        <f>ROUND(200*$B$1,0)</f>
         <v/>
       </c>
       <c r="E79">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="F79">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="G79">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="H79">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(208*$B$1,0)</f>
         <v/>
       </c>
       <c r="I79">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(216*$B$1,0)</f>
         <v/>
       </c>
       <c r="J79">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(164*$B$1,0)</f>
         <v/>
       </c>
       <c r="K79">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(197*$B$1,0)</f>
         <v/>
       </c>
       <c r="L79">
@@ -4613,44 +4623,44 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>208710540</t>
+          <t>419630142</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>FARMSTAY Argan Oil Complete Volume Up Shampoo &amp; Conditi</t>
+          <t>FARMSTAY ESCARGOT NOBLESSE INTENSIVE AMPOULE</t>
         </is>
       </c>
       <c r="D80">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(194*$B$1,0)</f>
         <v/>
       </c>
       <c r="E80">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(163*$B$1,0)</f>
         <v/>
       </c>
       <c r="F80">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(163*$B$1,0)</f>
         <v/>
       </c>
       <c r="G80">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(163*$B$1,0)</f>
         <v/>
       </c>
       <c r="H80">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(202*$B$1,0)</f>
         <v/>
       </c>
       <c r="I80">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(210*$B$1,0)</f>
         <v/>
       </c>
       <c r="J80">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="K80">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(191*$B$1,0)</f>
         <v/>
       </c>
       <c r="L80">
@@ -4666,44 +4676,44 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>710417367</t>
+          <t>212885914</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>FARMSTAY - Black Garlic Nourishing Shampoo [530ml] 11</t>
+          <t xml:space="preserve">FARMSTAY - Collagen Water Full Moist Rolling Eye Serum </t>
         </is>
       </c>
       <c r="D81">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="E81">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(142*$B$1,0)</f>
         <v/>
       </c>
       <c r="F81">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(142*$B$1,0)</f>
         <v/>
       </c>
       <c r="G81">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(142*$B$1,0)</f>
         <v/>
       </c>
       <c r="H81">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(175*$B$1,0)</f>
         <v/>
       </c>
       <c r="I81">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(182*$B$1,0)</f>
         <v/>
       </c>
       <c r="J81">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(138*$B$1,0)</f>
         <v/>
       </c>
       <c r="K81">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(166*$B$1,0)</f>
         <v/>
       </c>
       <c r="L81">
@@ -4719,44 +4729,44 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>168958606</t>
+          <t>207476777</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FARMSTAY COLLAGEN&amp;HYALURONIC ACID ALL-IN ONE AMPOULE 1</t>
+          <t>FARMSTAY - Collagen Pure Cleansing Foam [180ml]</t>
         </is>
       </c>
       <c r="D82">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="E82">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(72*$B$1,0)</f>
         <v/>
       </c>
       <c r="F82">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(72*$B$1,0)</f>
         <v/>
       </c>
       <c r="G82">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(72*$B$1,0)</f>
         <v/>
       </c>
       <c r="H82">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(88*$B$1,0)</f>
         <v/>
       </c>
       <c r="I82">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(92*$B$1,0)</f>
         <v/>
       </c>
       <c r="J82">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(70*$B$1,0)</f>
         <v/>
       </c>
       <c r="K82">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(84*$B$1,0)</f>
         <v/>
       </c>
       <c r="L82">
@@ -4767,49 +4777,49 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FARMSTAY</t>
+          <t>HEIMISH</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>208708607</t>
+          <t>207466866</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FARMSTAY - Collagen Water Full Shampoo &amp; Conditioner [5</t>
+          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
         </is>
       </c>
       <c r="D83">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(344*$B$1,0)</f>
         <v/>
       </c>
       <c r="E83">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(290*$B$1,0)</f>
         <v/>
       </c>
       <c r="F83">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(290*$B$1,0)</f>
         <v/>
       </c>
       <c r="G83">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(290*$B$1,0)</f>
         <v/>
       </c>
       <c r="H83">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(358*$B$1,0)</f>
         <v/>
       </c>
       <c r="I83">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(372*$B$1,0)</f>
         <v/>
       </c>
       <c r="J83">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(282*$B$1,0)</f>
         <v/>
       </c>
       <c r="K83">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(339*$B$1,0)</f>
         <v/>
       </c>
       <c r="L83">
@@ -4825,44 +4835,44 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>207466866</t>
+          <t>207464799</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HEIMISH - Artless Glow Base SPF50+ [40ml]</t>
+          <t>HEIMISH - All Clean Balm [120ml]</t>
         </is>
       </c>
       <c r="D84">
-        <f>ROUND(443*$B$1,0)</f>
+        <f>ROUND(200*$B$1,0)</f>
         <v/>
       </c>
       <c r="E84">
-        <f>ROUND(359*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="F84">
-        <f>ROUND(359*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="G84">
-        <f>ROUND(359*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="H84">
-        <f>ROUND(436*$B$1,0)</f>
+        <f>ROUND(208*$B$1,0)</f>
         <v/>
       </c>
       <c r="I84">
-        <f>ROUND(447*$B$1,0)</f>
+        <f>ROUND(216*$B$1,0)</f>
         <v/>
       </c>
       <c r="J84">
-        <f>ROUND(363*$B$1,0)</f>
+        <f>ROUND(164*$B$1,0)</f>
         <v/>
       </c>
       <c r="K84">
-        <f>ROUND(394*$B$1,0)</f>
+        <f>ROUND(197*$B$1,0)</f>
         <v/>
       </c>
       <c r="L84">
@@ -4878,44 +4888,44 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>207464799</t>
+          <t>207465786</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HEIMISH - All Clean Balm [120ml]</t>
+          <t>HEIMISH - All Clean Balm Mandarin [120ml]</t>
         </is>
       </c>
       <c r="D85">
-        <f>ROUND(301*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="E85">
-        <f>ROUND(244*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="F85">
-        <f>ROUND(244*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="G85">
-        <f>ROUND(244*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="H85">
-        <f>ROUND(296*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="I85">
-        <f>ROUND(303*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="J85">
-        <f>ROUND(246*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="K85">
-        <f>ROUND(267*$B$1,0)</f>
+        <f>ROUND(88*$B$1,0)</f>
         <v/>
       </c>
       <c r="L85">
@@ -4926,49 +4936,49 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HEIMISH</t>
+          <t>I'M SORRY FOR MY SKIN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>207465786</t>
+          <t>206122859</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HEIMISH - All Clean Balm Mandarin [120ml]</t>
+          <t>I'm Sorry for My Skin Age Крем Capture Firming Enriched</t>
         </is>
       </c>
       <c r="D86">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(101*$B$1,0)</f>
         <v/>
       </c>
       <c r="E86">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="F86">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="G86">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="H86">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="I86">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(110*$B$1,0)</f>
         <v/>
       </c>
       <c r="J86">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="K86">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(100*$B$1,0)</f>
         <v/>
       </c>
       <c r="L86">
@@ -4993,35 +5003,35 @@
         </is>
       </c>
       <c r="D87">
-        <f>ROUND(131*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="E87">
-        <f>ROUND(106*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="F87">
-        <f>ROUND(106*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="G87">
-        <f>ROUND(106*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="H87">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(101*$B$1,0)</f>
         <v/>
       </c>
       <c r="I87">
-        <f>ROUND(132*$B$1,0)</f>
+        <f>ROUND(105*$B$1,0)</f>
         <v/>
       </c>
       <c r="J87">
-        <f>ROUND(107*$B$1,0)</f>
+        <f>ROUND(80*$B$1,0)</f>
         <v/>
       </c>
       <c r="K87">
-        <f>ROUND(116*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="L87">
@@ -5046,35 +5056,35 @@
         </is>
       </c>
       <c r="D88">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="E88">
+        <f>ROUND(48*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F88">
+        <f>ROUND(48*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G88">
+        <f>ROUND(48*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H88">
         <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
-      <c r="F88">
-        <f>ROUND(60*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="G88">
-        <f>ROUND(60*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="H88">
-        <f>ROUND(73*$B$1,0)</f>
-        <v/>
-      </c>
       <c r="I88">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(62*$B$1,0)</f>
         <v/>
       </c>
       <c r="J88">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(47*$B$1,0)</f>
         <v/>
       </c>
       <c r="K88">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="L88">
@@ -5085,49 +5095,49 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>I'M SORRY FOR MY SKIN</t>
+          <t>ISNTREE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>206122859</t>
+          <t>207818000</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>I'm Sorry for My Skin Age Крем Capture Firming Enriched</t>
+          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml]</t>
         </is>
       </c>
       <c r="D89">
-        <f>ROUND(65*$B$1,0)</f>
+        <f>ROUND(18*$B$1,0)</f>
         <v/>
       </c>
       <c r="E89">
-        <f>ROUND(52*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="F89">
-        <f>ROUND(52*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="G89">
-        <f>ROUND(52*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="H89">
-        <f>ROUND(64*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="I89">
-        <f>ROUND(65*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="J89">
-        <f>ROUND(53*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="K89">
-        <f>ROUND(58*$B$1,0)</f>
+        <f>ROUND(18*$B$1,0)</f>
         <v/>
       </c>
       <c r="L89">
@@ -5138,49 +5148,49 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ISNTREE</t>
+          <t>JIGOTT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>207818000</t>
+          <t>207482718</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ISNTREE - Chestnut AHA 8% Clear Essence Sample [20ml]</t>
+          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
         </is>
       </c>
       <c r="D90">
-        <f>ROUND(25*$B$1,0)</f>
+        <f>ROUND(1378*$B$1,0)</f>
         <v/>
       </c>
       <c r="E90">
-        <f>ROUND(20*$B$1,0)</f>
+        <f>ROUND(1159*$B$1,0)</f>
         <v/>
       </c>
       <c r="F90">
-        <f>ROUND(20*$B$1,0)</f>
+        <f>ROUND(1159*$B$1,0)</f>
         <v/>
       </c>
       <c r="G90">
-        <f>ROUND(20*$B$1,0)</f>
+        <f>ROUND(1159*$B$1,0)</f>
         <v/>
       </c>
       <c r="H90">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(1432*$B$1,0)</f>
         <v/>
       </c>
       <c r="I90">
-        <f>ROUND(25*$B$1,0)</f>
+        <f>ROUND(1491*$B$1,0)</f>
         <v/>
       </c>
       <c r="J90">
-        <f>ROUND(20*$B$1,0)</f>
+        <f>ROUND(1130*$B$1,0)</f>
         <v/>
       </c>
       <c r="K90">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(1358*$B$1,0)</f>
         <v/>
       </c>
       <c r="L90">
@@ -5196,44 +5206,44 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>207482718</t>
+          <t>207483179</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Lifting Cream [70ml]</t>
+          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
         </is>
       </c>
       <c r="D91">
-        <f>ROUND(1453*$B$1,0)</f>
+        <f>ROUND(300*$B$1,0)</f>
         <v/>
       </c>
       <c r="E91">
-        <f>ROUND(1177*$B$1,0)</f>
+        <f>ROUND(252*$B$1,0)</f>
         <v/>
       </c>
       <c r="F91">
-        <f>ROUND(1177*$B$1,0)</f>
+        <f>ROUND(252*$B$1,0)</f>
         <v/>
       </c>
       <c r="G91">
-        <f>ROUND(1177*$B$1,0)</f>
+        <f>ROUND(252*$B$1,0)</f>
         <v/>
       </c>
       <c r="H91">
-        <f>ROUND(1429*$B$1,0)</f>
+        <f>ROUND(312*$B$1,0)</f>
         <v/>
       </c>
       <c r="I91">
-        <f>ROUND(1465*$B$1,0)</f>
+        <f>ROUND(325*$B$1,0)</f>
         <v/>
       </c>
       <c r="J91">
-        <f>ROUND(1191*$B$1,0)</f>
+        <f>ROUND(246*$B$1,0)</f>
         <v/>
       </c>
       <c r="K91">
-        <f>ROUND(1291*$B$1,0)</f>
+        <f>ROUND(296*$B$1,0)</f>
         <v/>
       </c>
       <c r="L91">
@@ -5249,44 +5259,44 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>207483179</t>
+          <t>207483780</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>JIGOTT - Snail Reparing Cream [100ml]</t>
+          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
         </is>
       </c>
       <c r="D92">
-        <f>ROUND(218*$B$1,0)</f>
+        <f>ROUND(263*$B$1,0)</f>
         <v/>
       </c>
       <c r="E92">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(221*$B$1,0)</f>
         <v/>
       </c>
       <c r="F92">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(221*$B$1,0)</f>
         <v/>
       </c>
       <c r="G92">
-        <f>ROUND(176*$B$1,0)</f>
+        <f>ROUND(221*$B$1,0)</f>
         <v/>
       </c>
       <c r="H92">
-        <f>ROUND(214*$B$1,0)</f>
+        <f>ROUND(273*$B$1,0)</f>
         <v/>
       </c>
       <c r="I92">
-        <f>ROUND(220*$B$1,0)</f>
+        <f>ROUND(284*$B$1,0)</f>
         <v/>
       </c>
       <c r="J92">
-        <f>ROUND(178*$B$1,0)</f>
+        <f>ROUND(216*$B$1,0)</f>
         <v/>
       </c>
       <c r="K92">
-        <f>ROUND(193*$B$1,0)</f>
+        <f>ROUND(259*$B$1,0)</f>
         <v/>
       </c>
       <c r="L92">
@@ -5302,44 +5312,44 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>207483780</t>
+          <t>212757456</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JIGOTT - Birds Nest Firming Cream [70ml]</t>
+          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
         </is>
       </c>
       <c r="D93">
-        <f>ROUND(193*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="E93">
-        <f>ROUND(156*$B$1,0)</f>
+        <f>ROUND(134*$B$1,0)</f>
         <v/>
       </c>
       <c r="F93">
-        <f>ROUND(156*$B$1,0)</f>
+        <f>ROUND(134*$B$1,0)</f>
         <v/>
       </c>
       <c r="G93">
-        <f>ROUND(156*$B$1,0)</f>
+        <f>ROUND(134*$B$1,0)</f>
         <v/>
       </c>
       <c r="H93">
-        <f>ROUND(189*$B$1,0)</f>
+        <f>ROUND(165*$B$1,0)</f>
         <v/>
       </c>
       <c r="I93">
-        <f>ROUND(194*$B$1,0)</f>
+        <f>ROUND(172*$B$1,0)</f>
         <v/>
       </c>
       <c r="J93">
-        <f>ROUND(158*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="K93">
-        <f>ROUND(171*$B$1,0)</f>
+        <f>ROUND(157*$B$1,0)</f>
         <v/>
       </c>
       <c r="L93">
@@ -5355,44 +5365,44 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>212759698</t>
+          <t>212760119</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
+          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
         </is>
       </c>
       <c r="D94">
-        <f>ROUND(166*$B$1,0)</f>
+        <f>ROUND(153*$B$1,0)</f>
         <v/>
       </c>
       <c r="E94">
-        <f>ROUND(134*$B$1,0)</f>
+        <f>ROUND(128*$B$1,0)</f>
         <v/>
       </c>
       <c r="F94">
-        <f>ROUND(134*$B$1,0)</f>
+        <f>ROUND(128*$B$1,0)</f>
         <v/>
       </c>
       <c r="G94">
-        <f>ROUND(134*$B$1,0)</f>
+        <f>ROUND(128*$B$1,0)</f>
         <v/>
       </c>
       <c r="H94">
-        <f>ROUND(163*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="I94">
-        <f>ROUND(167*$B$1,0)</f>
+        <f>ROUND(165*$B$1,0)</f>
         <v/>
       </c>
       <c r="J94">
-        <f>ROUND(136*$B$1,0)</f>
+        <f>ROUND(125*$B$1,0)</f>
         <v/>
       </c>
       <c r="K94">
-        <f>ROUND(147*$B$1,0)</f>
+        <f>ROUND(150*$B$1,0)</f>
         <v/>
       </c>
       <c r="L94">
@@ -5408,44 +5418,44 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>212760119</t>
+          <t>212759698</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JIGOTT - Ultimate Real Collagen Toner [300ml]</t>
+          <t>JIGOTT - Moisture Real Aloe Vera Toner [300ml]</t>
         </is>
       </c>
       <c r="D95">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(147*$B$1,0)</f>
         <v/>
       </c>
       <c r="E95">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(124*$B$1,0)</f>
         <v/>
       </c>
       <c r="F95">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(124*$B$1,0)</f>
         <v/>
       </c>
       <c r="G95">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(124*$B$1,0)</f>
         <v/>
       </c>
       <c r="H95">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(153*$B$1,0)</f>
         <v/>
       </c>
       <c r="I95">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(160*$B$1,0)</f>
         <v/>
       </c>
       <c r="J95">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(121*$B$1,0)</f>
         <v/>
       </c>
       <c r="K95">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(145*$B$1,0)</f>
         <v/>
       </c>
       <c r="L95">
@@ -5461,44 +5471,44 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>212757456</t>
+          <t>255574453</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JIGOTT - Daily Real Cica Toner [300ml]</t>
+          <t>JIGOTT - MASK 15</t>
         </is>
       </c>
       <c r="D96">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(109*$B$1,0)</f>
         <v/>
       </c>
       <c r="E96">
-        <f>ROUND(78*$B$1,0)</f>
+        <f>ROUND(92*$B$1,0)</f>
         <v/>
       </c>
       <c r="F96">
-        <f>ROUND(78*$B$1,0)</f>
+        <f>ROUND(92*$B$1,0)</f>
         <v/>
       </c>
       <c r="G96">
-        <f>ROUND(78*$B$1,0)</f>
+        <f>ROUND(92*$B$1,0)</f>
         <v/>
       </c>
       <c r="H96">
-        <f>ROUND(95*$B$1,0)</f>
+        <f>ROUND(113*$B$1,0)</f>
         <v/>
       </c>
       <c r="I96">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(118*$B$1,0)</f>
         <v/>
       </c>
       <c r="J96">
-        <f>ROUND(79*$B$1,0)</f>
+        <f>ROUND(89*$B$1,0)</f>
         <v/>
       </c>
       <c r="K96">
-        <f>ROUND(86*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="L96">
@@ -5523,35 +5533,35 @@
         </is>
       </c>
       <c r="D97">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(98*$B$1,0)</f>
         <v/>
       </c>
       <c r="E97">
-        <f>ROUND(73*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="F97">
-        <f>ROUND(73*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="G97">
-        <f>ROUND(73*$B$1,0)</f>
+        <f>ROUND(82*$B$1,0)</f>
         <v/>
       </c>
       <c r="H97">
-        <f>ROUND(88*$B$1,0)</f>
+        <f>ROUND(101*$B$1,0)</f>
         <v/>
       </c>
       <c r="I97">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(106*$B$1,0)</f>
         <v/>
       </c>
       <c r="J97">
-        <f>ROUND(73*$B$1,0)</f>
+        <f>ROUND(80*$B$1,0)</f>
         <v/>
       </c>
       <c r="K97">
-        <f>ROUND(80*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="L97">
@@ -5576,7 +5586,7 @@
         </is>
       </c>
       <c r="D98">
-        <f>ROUND(70*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="E98">
@@ -5592,19 +5602,19 @@
         <v/>
       </c>
       <c r="H98">
-        <f>ROUND(69*$B$1,0)</f>
+        <f>ROUND(70*$B$1,0)</f>
         <v/>
       </c>
       <c r="I98">
-        <f>ROUND(71*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="J98">
-        <f>ROUND(57*$B$1,0)</f>
+        <f>ROUND(55*$B$1,0)</f>
         <v/>
       </c>
       <c r="K98">
-        <f>ROUND(62*$B$1,0)</f>
+        <f>ROUND(66*$B$1,0)</f>
         <v/>
       </c>
       <c r="L98">
@@ -5615,49 +5625,49 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>JIGOTT</t>
+          <t>JMSOLUTION</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>255574453</t>
+          <t>214964091</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>JIGOTT - MASK 15</t>
+          <t>JMSOLUTION - Mask Pack Disney</t>
         </is>
       </c>
       <c r="D99">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(206*$B$1,0)</f>
         <v/>
       </c>
       <c r="E99">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(174*$B$1,0)</f>
         <v/>
       </c>
       <c r="F99">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(174*$B$1,0)</f>
         <v/>
       </c>
       <c r="G99">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(174*$B$1,0)</f>
         <v/>
       </c>
       <c r="H99">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(215*$B$1,0)</f>
         <v/>
       </c>
       <c r="I99">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(223*$B$1,0)</f>
         <v/>
       </c>
       <c r="J99">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(169*$B$1,0)</f>
         <v/>
       </c>
       <c r="K99">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(203*$B$1,0)</f>
         <v/>
       </c>
       <c r="L99">
@@ -5673,44 +5683,44 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>214964091</t>
+          <t>214977901</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Disney</t>
+          <t>JMSOLUTION - Mask Pack Black</t>
         </is>
       </c>
       <c r="D100">
-        <f>ROUND(194*$B$1,0)</f>
+        <f>ROUND(113*$B$1,0)</f>
         <v/>
       </c>
       <c r="E100">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(95*$B$1,0)</f>
         <v/>
       </c>
       <c r="F100">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(95*$B$1,0)</f>
         <v/>
       </c>
       <c r="G100">
-        <f>ROUND(157*$B$1,0)</f>
+        <f>ROUND(95*$B$1,0)</f>
         <v/>
       </c>
       <c r="H100">
-        <f>ROUND(191*$B$1,0)</f>
+        <f>ROUND(117*$B$1,0)</f>
         <v/>
       </c>
       <c r="I100">
-        <f>ROUND(196*$B$1,0)</f>
+        <f>ROUND(122*$B$1,0)</f>
         <v/>
       </c>
       <c r="J100">
-        <f>ROUND(159*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="K100">
-        <f>ROUND(172*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="L100">
@@ -5726,44 +5736,44 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>214977901</t>
+          <t>333259566</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Black</t>
+          <t>JMSOLUTION - Mask Pack Black [8pcs]</t>
         </is>
       </c>
       <c r="D101">
-        <f>ROUND(115*$B$1,0)</f>
+        <f>ROUND(41*$B$1,0)</f>
         <v/>
       </c>
       <c r="E101">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="F101">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="G101">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="H101">
-        <f>ROUND(113*$B$1,0)</f>
+        <f>ROUND(42*$B$1,0)</f>
         <v/>
       </c>
       <c r="I101">
-        <f>ROUND(116*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="J101">
-        <f>ROUND(94*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="K101">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(40*$B$1,0)</f>
         <v/>
       </c>
       <c r="L101">
@@ -5779,44 +5789,44 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>236825103</t>
+          <t>212717820</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>JMSOLUTION-Marine Luminous Pearl Deep Moisture Mask Pea</t>
+          <t>JMSOLUTION - Prime Gold Eye Patch [60ea]</t>
         </is>
       </c>
       <c r="D102">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="E102">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="F102">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="G102">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="H102">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="I102">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
       <c r="J102">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="K102">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="L102">
@@ -5832,44 +5842,44 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>212717820</t>
+          <t>212713617</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Prime Gold Eye Patch [60ea]</t>
+          <t>JMSOLUTION - Black Cocoon Home Esthetic Eye Patch [60ea</t>
         </is>
       </c>
       <c r="D103">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="E103">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="F103">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="G103">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="H103">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="I103">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="J103">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="K103">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="L103">
@@ -5885,44 +5895,44 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>333259566</t>
+          <t>236825103</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Black [8pcs]</t>
+          <t>JMSOLUTION-Marine Luminous Pearl Deep Moisture Mask Pea</t>
         </is>
       </c>
       <c r="D104">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="E104">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="F104">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="G104">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="H104">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="I104">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="J104">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="K104">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="L104">
@@ -5933,49 +5943,49 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JMSOLUTION</t>
+          <t>LANEIGE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>212713617</t>
+          <t>868761530</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Black Cocoon Home Esthetic Eye Patch [60ea</t>
+          <t>LANEIGE LIP SLEEPING MASK-BERRY [3g]</t>
         </is>
       </c>
       <c r="D105">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(170*$B$1,0)</f>
         <v/>
       </c>
       <c r="E105">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(143*$B$1,0)</f>
         <v/>
       </c>
       <c r="F105">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(143*$B$1,0)</f>
         <v/>
       </c>
       <c r="G105">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(143*$B$1,0)</f>
         <v/>
       </c>
       <c r="H105">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(177*$B$1,0)</f>
         <v/>
       </c>
       <c r="I105">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(184*$B$1,0)</f>
         <v/>
       </c>
       <c r="J105">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(139*$B$1,0)</f>
         <v/>
       </c>
       <c r="K105">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="L105">
@@ -5986,49 +5996,49 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LANEIGE</t>
+          <t>LEBELAGE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>868761530</t>
+          <t>238359400</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LANEIGE LIP SLEEPING MASK-BERRY [3g]</t>
+          <t>LEBELAGE - High Protection Extreme Sun Cream SPF50+ PA+</t>
         </is>
       </c>
       <c r="D106">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(333*$B$1,0)</f>
         <v/>
       </c>
       <c r="E106">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(280*$B$1,0)</f>
         <v/>
       </c>
       <c r="F106">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(280*$B$1,0)</f>
         <v/>
       </c>
       <c r="G106">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(280*$B$1,0)</f>
         <v/>
       </c>
       <c r="H106">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(346*$B$1,0)</f>
         <v/>
       </c>
       <c r="I106">
-        <f>ROUND(94*$B$1,0)</f>
+        <f>ROUND(360*$B$1,0)</f>
         <v/>
       </c>
       <c r="J106">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(273*$B$1,0)</f>
         <v/>
       </c>
       <c r="K106">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(328*$B$1,0)</f>
         <v/>
       </c>
       <c r="L106">
@@ -6044,44 +6054,44 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>238359400</t>
+          <t>238359757</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LEBELAGE - High Protection Extreme Sun Cream SPF50+ PA+</t>
+          <t>LEBELAGE - High Protection Long Lasting Sun Cream SPF50</t>
         </is>
       </c>
       <c r="D107">
-        <f>ROUND(541*$B$1,0)</f>
+        <f>ROUND(285*$B$1,0)</f>
         <v/>
       </c>
       <c r="E107">
-        <f>ROUND(438*$B$1,0)</f>
+        <f>ROUND(240*$B$1,0)</f>
         <v/>
       </c>
       <c r="F107">
-        <f>ROUND(438*$B$1,0)</f>
+        <f>ROUND(240*$B$1,0)</f>
         <v/>
       </c>
       <c r="G107">
-        <f>ROUND(438*$B$1,0)</f>
+        <f>ROUND(240*$B$1,0)</f>
         <v/>
       </c>
       <c r="H107">
-        <f>ROUND(532*$B$1,0)</f>
+        <f>ROUND(297*$B$1,0)</f>
         <v/>
       </c>
       <c r="I107">
-        <f>ROUND(546*$B$1,0)</f>
+        <f>ROUND(309*$B$1,0)</f>
         <v/>
       </c>
       <c r="J107">
-        <f>ROUND(443*$B$1,0)</f>
+        <f>ROUND(234*$B$1,0)</f>
         <v/>
       </c>
       <c r="K107">
-        <f>ROUND(481*$B$1,0)</f>
+        <f>ROUND(281*$B$1,0)</f>
         <v/>
       </c>
       <c r="L107">
@@ -6097,44 +6107,44 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>238359757</t>
+          <t>210579932</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LEBELAGE - High Protection Long Lasting Sun Cream SPF50</t>
+          <t>LEBELAGE - Dr. Snail Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="D108">
-        <f>ROUND(479*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="E108">
-        <f>ROUND(388*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="F108">
-        <f>ROUND(388*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="G108">
-        <f>ROUND(388*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="H108">
-        <f>ROUND(471*$B$1,0)</f>
+        <f>ROUND(71*$B$1,0)</f>
         <v/>
       </c>
       <c r="I108">
-        <f>ROUND(483*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="J108">
-        <f>ROUND(392*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="K108">
-        <f>ROUND(425*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="L108">
@@ -6150,44 +6160,44 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>210579932</t>
+          <t>207818642</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Snail Derma Eye Cream [40ml]</t>
+          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="D109">
-        <f>ROUND(89*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="E109">
-        <f>ROUND(72*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="F109">
-        <f>ROUND(72*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="G109">
-        <f>ROUND(72*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="H109">
-        <f>ROUND(88*$B$1,0)</f>
+        <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
       <c r="I109">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(32*$B$1,0)</f>
         <v/>
       </c>
       <c r="J109">
-        <f>ROUND(73*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="K109">
-        <f>ROUND(79*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="L109">
@@ -6203,44 +6213,44 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>207818642</t>
+          <t>210575566</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Hyaluronic Derma Eye Cream [40ml]</t>
+          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
         </is>
       </c>
       <c r="D110">
-        <f>ROUND(38*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="E110">
+        <f>ROUND(24*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F110">
+        <f>ROUND(24*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G110">
+        <f>ROUND(24*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H110">
+        <f>ROUND(30*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I110">
         <f>ROUND(31*$B$1,0)</f>
         <v/>
       </c>
-      <c r="F110">
-        <f>ROUND(31*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="G110">
-        <f>ROUND(31*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="H110">
-        <f>ROUND(38*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="I110">
-        <f>ROUND(39*$B$1,0)</f>
-        <v/>
-      </c>
       <c r="J110">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="K110">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(29*$B$1,0)</f>
         <v/>
       </c>
       <c r="L110">
@@ -6256,44 +6266,44 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>165008074</t>
+          <t>165008162</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LEBELAGE - High Protection Daily No Sebum Sun Cream SPF</t>
+          <t>LEBELAGE - High Protection Extreme Sun Cream SPF50+ PA+</t>
         </is>
       </c>
       <c r="D111">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(28*$B$1,0)</f>
         <v/>
       </c>
       <c r="E111">
+        <f>ROUND(23*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F111">
+        <f>ROUND(23*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G111">
+        <f>ROUND(23*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H111">
+        <f>ROUND(29*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I111">
+        <f>ROUND(30*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J111">
+        <f>ROUND(23*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K111">
         <f>ROUND(27*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="F111">
-        <f>ROUND(27*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="G111">
-        <f>ROUND(27*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="H111">
-        <f>ROUND(33*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="I111">
-        <f>ROUND(34*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="J111">
-        <f>ROUND(27*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="K111">
-        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="L111">
@@ -6309,44 +6319,44 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>210575566</t>
+          <t>165008074</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>LEBELAGE - Dr. Peptide Derma Eye Cream [40ml]</t>
+          <t>LEBELAGE - High Protection Daily No Sebum Sun Cream SPF</t>
         </is>
       </c>
       <c r="D112">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="E112">
+        <f>ROUND(21*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F112">
+        <f>ROUND(21*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G112">
+        <f>ROUND(21*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H112">
+        <f>ROUND(26*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I112">
         <f>ROUND(27*$B$1,0)</f>
         <v/>
       </c>
-      <c r="F112">
-        <f>ROUND(27*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="G112">
-        <f>ROUND(27*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="H112">
-        <f>ROUND(32*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="I112">
-        <f>ROUND(33*$B$1,0)</f>
-        <v/>
-      </c>
       <c r="J112">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="K112">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="L112">
@@ -6357,49 +6367,49 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LEBELAGE</t>
+          <t>MANYO</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>165008162</t>
+          <t>205054338</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LEBELAGE - High Protection Extreme Sun Cream SPF50+ PA+</t>
+          <t>manyo_bifida_biome_toner</t>
         </is>
       </c>
       <c r="D113">
-        <f>ROUND(20*$B$1,0)</f>
+        <f>ROUND(205*$B$1,0)</f>
         <v/>
       </c>
       <c r="E113">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(173*$B$1,0)</f>
         <v/>
       </c>
       <c r="F113">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(173*$B$1,0)</f>
         <v/>
       </c>
       <c r="G113">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(173*$B$1,0)</f>
         <v/>
       </c>
       <c r="H113">
-        <f>ROUND(20*$B$1,0)</f>
+        <f>ROUND(213*$B$1,0)</f>
         <v/>
       </c>
       <c r="I113">
-        <f>ROUND(20*$B$1,0)</f>
+        <f>ROUND(222*$B$1,0)</f>
         <v/>
       </c>
       <c r="J113">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="K113">
-        <f>ROUND(18*$B$1,0)</f>
+        <f>ROUND(202*$B$1,0)</f>
         <v/>
       </c>
       <c r="L113">
@@ -6415,44 +6425,44 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>205054338</t>
+          <t>198147185</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>manyo_bifida_biome_toner</t>
+          <t>Manyo_Complex_Ampoule</t>
         </is>
       </c>
       <c r="D114">
-        <f>ROUND(332*$B$1,0)</f>
+        <f>ROUND(192*$B$1,0)</f>
         <v/>
       </c>
       <c r="E114">
-        <f>ROUND(269*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="F114">
-        <f>ROUND(269*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="G114">
-        <f>ROUND(269*$B$1,0)</f>
+        <f>ROUND(162*$B$1,0)</f>
         <v/>
       </c>
       <c r="H114">
-        <f>ROUND(326*$B$1,0)</f>
+        <f>ROUND(200*$B$1,0)</f>
         <v/>
       </c>
       <c r="I114">
-        <f>ROUND(334*$B$1,0)</f>
+        <f>ROUND(208*$B$1,0)</f>
         <v/>
       </c>
       <c r="J114">
-        <f>ROUND(272*$B$1,0)</f>
+        <f>ROUND(157*$B$1,0)</f>
         <v/>
       </c>
       <c r="K114">
-        <f>ROUND(295*$B$1,0)</f>
+        <f>ROUND(189*$B$1,0)</f>
         <v/>
       </c>
       <c r="L114">
@@ -6477,35 +6487,35 @@
         </is>
       </c>
       <c r="D115">
-        <f>ROUND(261*$B$1,0)</f>
+        <f>ROUND(179*$B$1,0)</f>
         <v/>
       </c>
       <c r="E115">
-        <f>ROUND(212*$B$1,0)</f>
+        <f>ROUND(151*$B$1,0)</f>
         <v/>
       </c>
       <c r="F115">
-        <f>ROUND(212*$B$1,0)</f>
+        <f>ROUND(151*$B$1,0)</f>
         <v/>
       </c>
       <c r="G115">
-        <f>ROUND(212*$B$1,0)</f>
+        <f>ROUND(151*$B$1,0)</f>
         <v/>
       </c>
       <c r="H115">
-        <f>ROUND(257*$B$1,0)</f>
+        <f>ROUND(186*$B$1,0)</f>
         <v/>
       </c>
       <c r="I115">
-        <f>ROUND(264*$B$1,0)</f>
+        <f>ROUND(194*$B$1,0)</f>
         <v/>
       </c>
       <c r="J115">
-        <f>ROUND(214*$B$1,0)</f>
+        <f>ROUND(147*$B$1,0)</f>
         <v/>
       </c>
       <c r="K115">
-        <f>ROUND(232*$B$1,0)</f>
+        <f>ROUND(176*$B$1,0)</f>
         <v/>
       </c>
       <c r="L115">
@@ -6530,35 +6540,35 @@
         </is>
       </c>
       <c r="D116">
-        <f>ROUND(190*$B$1,0)</f>
+        <f>ROUND(155*$B$1,0)</f>
         <v/>
       </c>
       <c r="E116">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="F116">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="G116">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="H116">
-        <f>ROUND(186*$B$1,0)</f>
+        <f>ROUND(161*$B$1,0)</f>
         <v/>
       </c>
       <c r="I116">
-        <f>ROUND(191*$B$1,0)</f>
+        <f>ROUND(168*$B$1,0)</f>
         <v/>
       </c>
       <c r="J116">
-        <f>ROUND(155*$B$1,0)</f>
+        <f>ROUND(127*$B$1,0)</f>
         <v/>
       </c>
       <c r="K116">
-        <f>ROUND(168*$B$1,0)</f>
+        <f>ROUND(153*$B$1,0)</f>
         <v/>
       </c>
       <c r="L116">
@@ -6574,44 +6584,44 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>198147185</t>
+          <t>198143251</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Manyo_Complex_Ampoule</t>
+          <t>Manyo_Ampoule_Lotion</t>
         </is>
       </c>
       <c r="D117">
-        <f>ROUND(180*$B$1,0)</f>
+        <f>ROUND(104*$B$1,0)</f>
         <v/>
       </c>
       <c r="E117">
-        <f>ROUND(146*$B$1,0)</f>
+        <f>ROUND(88*$B$1,0)</f>
         <v/>
       </c>
       <c r="F117">
-        <f>ROUND(146*$B$1,0)</f>
+        <f>ROUND(88*$B$1,0)</f>
         <v/>
       </c>
       <c r="G117">
-        <f>ROUND(146*$B$1,0)</f>
+        <f>ROUND(88*$B$1,0)</f>
         <v/>
       </c>
       <c r="H117">
-        <f>ROUND(177*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="I117">
-        <f>ROUND(182*$B$1,0)</f>
+        <f>ROUND(113*$B$1,0)</f>
         <v/>
       </c>
       <c r="J117">
-        <f>ROUND(148*$B$1,0)</f>
+        <f>ROUND(86*$B$1,0)</f>
         <v/>
       </c>
       <c r="K117">
-        <f>ROUND(160*$B$1,0)</f>
+        <f>ROUND(103*$B$1,0)</f>
         <v/>
       </c>
       <c r="L117">
@@ -6627,44 +6637,44 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>198143251</t>
+          <t>868575374</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Manyo_Ampoule_Lotion</t>
+          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
         </is>
       </c>
       <c r="D118">
-        <f>ROUND(55*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="E118">
-        <f>ROUND(45*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="F118">
-        <f>ROUND(45*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="G118">
-        <f>ROUND(45*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="H118">
-        <f>ROUND(54*$B$1,0)</f>
+        <f>ROUND(77*$B$1,0)</f>
         <v/>
       </c>
       <c r="I118">
-        <f>ROUND(56*$B$1,0)</f>
+        <f>ROUND(80*$B$1,0)</f>
         <v/>
       </c>
       <c r="J118">
-        <f>ROUND(45*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="K118">
-        <f>ROUND(49*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="L118">
@@ -6680,32 +6690,32 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>868575374</t>
+          <t>868700077</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA COMPLEX AMPOULE GEL CLEANSER [400ml]</t>
+          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
         </is>
       </c>
       <c r="D119">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(39*$B$1,0)</f>
         <v/>
       </c>
       <c r="E119">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="F119">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="G119">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(33*$B$1,0)</f>
         <v/>
       </c>
       <c r="H119">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(40*$B$1,0)</f>
         <v/>
       </c>
       <c r="I119">
@@ -6713,11 +6723,11 @@
         <v/>
       </c>
       <c r="J119">
-        <f>ROUND(34*$B$1,0)</f>
+        <f>ROUND(32*$B$1,0)</f>
         <v/>
       </c>
       <c r="K119">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(38*$B$1,0)</f>
         <v/>
       </c>
       <c r="L119">
@@ -6733,12 +6743,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>868700077</t>
+          <t>198148122</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MANYO BIFIDA INFUSION SHOT AMPOULE 1DX [50ml]</t>
+          <t>Manyo_Concentrate_Cream</t>
         </is>
       </c>
       <c r="D120">
@@ -6746,23 +6756,23 @@
         <v/>
       </c>
       <c r="E120">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="F120">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="G120">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(30*$B$1,0)</f>
         <v/>
       </c>
       <c r="H120">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(37*$B$1,0)</f>
         <v/>
       </c>
       <c r="I120">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(39*$B$1,0)</f>
         <v/>
       </c>
       <c r="J120">
@@ -6770,7 +6780,7 @@
         <v/>
       </c>
       <c r="K120">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(36*$B$1,0)</f>
         <v/>
       </c>
       <c r="L120">
@@ -6781,49 +6791,49 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PETITFEE</t>
+          <t>MISSHA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>151175877</t>
+          <t>212825852</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Petitfee Agave Cooling Hydrogel Eye Mask</t>
+          <t>MISSHA - M Perfect Cover BB Cream SPF42+ PA+++ (Tone 21</t>
         </is>
       </c>
       <c r="D121">
-        <f>ROUND(250*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="E121">
-        <f>ROUND(202*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="F121">
-        <f>ROUND(202*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="G121">
-        <f>ROUND(202*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="H121">
-        <f>ROUND(246*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="I121">
-        <f>ROUND(252*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="J121">
-        <f>ROUND(205*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="K121">
-        <f>ROUND(222*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="L121">
@@ -6839,44 +6849,44 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>151175880</t>
+          <t>151175877</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Petitfee Black Pearl &amp; Gold hydrogel Eye Patch</t>
+          <t>Petitfee Agave Cooling Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="D122">
-        <f>ROUND(205*$B$1,0)</f>
+        <f>ROUND(233*$B$1,0)</f>
         <v/>
       </c>
       <c r="E122">
-        <f>ROUND(166*$B$1,0)</f>
+        <f>ROUND(196*$B$1,0)</f>
         <v/>
       </c>
       <c r="F122">
-        <f>ROUND(166*$B$1,0)</f>
+        <f>ROUND(196*$B$1,0)</f>
         <v/>
       </c>
       <c r="G122">
-        <f>ROUND(166*$B$1,0)</f>
+        <f>ROUND(196*$B$1,0)</f>
         <v/>
       </c>
       <c r="H122">
-        <f>ROUND(201*$B$1,0)</f>
+        <f>ROUND(242*$B$1,0)</f>
         <v/>
       </c>
       <c r="I122">
-        <f>ROUND(206*$B$1,0)</f>
+        <f>ROUND(252*$B$1,0)</f>
         <v/>
       </c>
       <c r="J122">
-        <f>ROUND(168*$B$1,0)</f>
+        <f>ROUND(191*$B$1,0)</f>
         <v/>
       </c>
       <c r="K122">
-        <f>ROUND(182*$B$1,0)</f>
+        <f>ROUND(230*$B$1,0)</f>
         <v/>
       </c>
       <c r="L122">
@@ -6892,44 +6902,44 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>226115324</t>
+          <t>151175880</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
+          <t>Petitfee Black Pearl &amp; Gold hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="D123">
-        <f>ROUND(190*$B$1,0)</f>
+        <f>ROUND(228*$B$1,0)</f>
         <v/>
       </c>
       <c r="E123">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(192*$B$1,0)</f>
         <v/>
       </c>
       <c r="F123">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(192*$B$1,0)</f>
         <v/>
       </c>
       <c r="G123">
-        <f>ROUND(154*$B$1,0)</f>
+        <f>ROUND(192*$B$1,0)</f>
         <v/>
       </c>
       <c r="H123">
+        <f>ROUND(237*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I123">
+        <f>ROUND(247*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J123">
         <f>ROUND(187*$B$1,0)</f>
         <v/>
       </c>
-      <c r="I123">
-        <f>ROUND(192*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="J123">
-        <f>ROUND(156*$B$1,0)</f>
-        <v/>
-      </c>
       <c r="K123">
-        <f>ROUND(169*$B$1,0)</f>
+        <f>ROUND(225*$B$1,0)</f>
         <v/>
       </c>
       <c r="L123">
@@ -6945,44 +6955,44 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>226114935</t>
+          <t>226115324</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
+          <t>PETITFEE - Agave Cooling Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="D124">
-        <f>ROUND(161*$B$1,0)</f>
+        <f>ROUND(157*$B$1,0)</f>
         <v/>
       </c>
       <c r="E124">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(132*$B$1,0)</f>
         <v/>
       </c>
       <c r="F124">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(132*$B$1,0)</f>
         <v/>
       </c>
       <c r="G124">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(132*$B$1,0)</f>
         <v/>
       </c>
       <c r="H124">
-        <f>ROUND(158*$B$1,0)</f>
+        <f>ROUND(164*$B$1,0)</f>
         <v/>
       </c>
       <c r="I124">
-        <f>ROUND(162*$B$1,0)</f>
+        <f>ROUND(170*$B$1,0)</f>
         <v/>
       </c>
       <c r="J124">
-        <f>ROUND(132*$B$1,0)</f>
+        <f>ROUND(129*$B$1,0)</f>
         <v/>
       </c>
       <c r="K124">
-        <f>ROUND(143*$B$1,0)</f>
+        <f>ROUND(155*$B$1,0)</f>
         <v/>
       </c>
       <c r="L124">
@@ -6998,36 +7008,36 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>179611278</t>
+          <t>226114831</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Petitfee Artichoke Soothing Hydrogel Eye Mask</t>
+          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
         </is>
       </c>
       <c r="D125">
-        <f>ROUND(146*$B$1,0)</f>
+        <f>ROUND(147*$B$1,0)</f>
         <v/>
       </c>
       <c r="E125">
-        <f>ROUND(118*$B$1,0)</f>
+        <f>ROUND(124*$B$1,0)</f>
         <v/>
       </c>
       <c r="F125">
-        <f>ROUND(118*$B$1,0)</f>
+        <f>ROUND(124*$B$1,0)</f>
         <v/>
       </c>
       <c r="G125">
-        <f>ROUND(118*$B$1,0)</f>
+        <f>ROUND(124*$B$1,0)</f>
         <v/>
       </c>
       <c r="H125">
-        <f>ROUND(144*$B$1,0)</f>
+        <f>ROUND(153*$B$1,0)</f>
         <v/>
       </c>
       <c r="I125">
-        <f>ROUND(147*$B$1,0)</f>
+        <f>ROUND(159*$B$1,0)</f>
         <v/>
       </c>
       <c r="J125">
@@ -7035,7 +7045,7 @@
         <v/>
       </c>
       <c r="K125">
-        <f>ROUND(130*$B$1,0)</f>
+        <f>ROUND(145*$B$1,0)</f>
         <v/>
       </c>
       <c r="L125">
@@ -7051,16 +7061,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>226115141</t>
+          <t>226114935</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs]</t>
+          <t>PETITFEE - Gold Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="D126">
-        <f>ROUND(145*$B$1,0)</f>
+        <f>ROUND(140*$B$1,0)</f>
         <v/>
       </c>
       <c r="E126">
@@ -7076,19 +7086,19 @@
         <v/>
       </c>
       <c r="H126">
-        <f>ROUND(143*$B$1,0)</f>
+        <f>ROUND(145*$B$1,0)</f>
         <v/>
       </c>
       <c r="I126">
-        <f>ROUND(147*$B$1,0)</f>
+        <f>ROUND(151*$B$1,0)</f>
         <v/>
       </c>
       <c r="J126">
-        <f>ROUND(119*$B$1,0)</f>
+        <f>ROUND(115*$B$1,0)</f>
         <v/>
       </c>
       <c r="K126">
-        <f>ROUND(129*$B$1,0)</f>
+        <f>ROUND(138*$B$1,0)</f>
         <v/>
       </c>
       <c r="L126">
@@ -7104,44 +7114,44 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>226117746</t>
+          <t>226115248</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PETITFEE - Chamomile Lightening Hydrogel Mask Pack [5pc</t>
+          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="D127">
-        <f>ROUND(126*$B$1,0)</f>
+        <f>ROUND(132*$B$1,0)</f>
         <v/>
       </c>
       <c r="E127">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="F127">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="G127">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="H127">
-        <f>ROUND(124*$B$1,0)</f>
+        <f>ROUND(137*$B$1,0)</f>
         <v/>
       </c>
       <c r="I127">
-        <f>ROUND(127*$B$1,0)</f>
+        <f>ROUND(143*$B$1,0)</f>
         <v/>
       </c>
       <c r="J127">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="K127">
-        <f>ROUND(112*$B$1,0)</f>
+        <f>ROUND(130*$B$1,0)</f>
         <v/>
       </c>
       <c r="L127">
@@ -7157,44 +7167,44 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>226115248</t>
+          <t>179611278</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PETITFEE - Cacao Energizing Hydrogel Mask Pack [5pcs]</t>
+          <t>Petitfee Artichoke Soothing Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="D128">
-        <f>ROUND(123*$B$1,0)</f>
+        <f>ROUND(126*$B$1,0)</f>
         <v/>
       </c>
       <c r="E128">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(106*$B$1,0)</f>
         <v/>
       </c>
       <c r="F128">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(106*$B$1,0)</f>
         <v/>
       </c>
       <c r="G128">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(106*$B$1,0)</f>
         <v/>
       </c>
       <c r="H128">
-        <f>ROUND(121*$B$1,0)</f>
+        <f>ROUND(131*$B$1,0)</f>
         <v/>
       </c>
       <c r="I128">
+        <f>ROUND(136*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J128">
+        <f>ROUND(103*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K128">
         <f>ROUND(124*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="J128">
-        <f>ROUND(101*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="K128">
-        <f>ROUND(109*$B$1,0)</f>
         <v/>
       </c>
       <c r="L128">
@@ -7210,32 +7220,32 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>179611207</t>
+          <t>226115141</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Petitfee GOLD &amp; SNAIL HYDROGEL EYE PATCH</t>
+          <t>PETITFEE - Gold &amp; Snail Hydrogel Mask Pack [5pcs]</t>
         </is>
       </c>
       <c r="D129">
-        <f>ROUND(122*$B$1,0)</f>
+        <f>ROUND(114*$B$1,0)</f>
         <v/>
       </c>
       <c r="E129">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="F129">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="G129">
-        <f>ROUND(99*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="H129">
-        <f>ROUND(120*$B$1,0)</f>
+        <f>ROUND(118*$B$1,0)</f>
         <v/>
       </c>
       <c r="I129">
@@ -7243,11 +7253,11 @@
         <v/>
       </c>
       <c r="J129">
-        <f>ROUND(100*$B$1,0)</f>
+        <f>ROUND(93*$B$1,0)</f>
         <v/>
       </c>
       <c r="K129">
-        <f>ROUND(109*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="L129">
@@ -7272,27 +7282,27 @@
         </is>
       </c>
       <c r="D130">
-        <f>ROUND(103*$B$1,0)</f>
+        <f>ROUND(104*$B$1,0)</f>
         <v/>
       </c>
       <c r="E130">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="F130">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="G130">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="H130">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(108*$B$1,0)</f>
         <v/>
       </c>
       <c r="I130">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="J130">
@@ -7300,7 +7310,7 @@
         <v/>
       </c>
       <c r="K130">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="L130">
@@ -7316,44 +7326,44 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>180988755</t>
+          <t>179611207</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Petitfee B-Glucan Deep Firming Eye Mask</t>
+          <t>Petitfee GOLD &amp; SNAIL HYDROGEL EYE PATCH</t>
         </is>
       </c>
       <c r="D131">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(103*$B$1,0)</f>
         <v/>
       </c>
       <c r="E131">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="F131">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="G131">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="H131">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(107*$B$1,0)</f>
         <v/>
       </c>
       <c r="I131">
-        <f>ROUND(94*$B$1,0)</f>
+        <f>ROUND(112*$B$1,0)</f>
         <v/>
       </c>
       <c r="J131">
-        <f>ROUND(76*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="K131">
-        <f>ROUND(83*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="L131">
@@ -7369,44 +7379,44 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>226114831</t>
+          <t>226117746</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PETITFEE - Artichoke Soothing Hydrogel Face Mask [5pcs]</t>
+          <t>PETITFEE - Chamomile Lightening Hydrogel Mask Pack [5pc</t>
         </is>
       </c>
       <c r="D132">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(98*$B$1,0)</f>
         <v/>
       </c>
       <c r="E132">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="F132">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="G132">
-        <f>ROUND(74*$B$1,0)</f>
+        <f>ROUND(83*$B$1,0)</f>
         <v/>
       </c>
       <c r="H132">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(102*$B$1,0)</f>
         <v/>
       </c>
       <c r="I132">
-        <f>ROUND(92*$B$1,0)</f>
+        <f>ROUND(107*$B$1,0)</f>
         <v/>
       </c>
       <c r="J132">
-        <f>ROUND(75*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="K132">
-        <f>ROUND(81*$B$1,0)</f>
+        <f>ROUND(97*$B$1,0)</f>
         <v/>
       </c>
       <c r="L132">
@@ -7422,44 +7432,44 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>179611318</t>
+          <t>180988755</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Petitfee Chamomile Lightening Hydrogel Eye Mask</t>
+          <t>Petitfee B-Glucan Deep Firming Eye Mask</t>
         </is>
       </c>
       <c r="D133">
+        <f>ROUND(85*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E133">
+        <f>ROUND(72*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F133">
+        <f>ROUND(72*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G133">
+        <f>ROUND(72*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H133">
+        <f>ROUND(89*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I133">
+        <f>ROUND(92*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J133">
+        <f>ROUND(70*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K133">
         <f>ROUND(84*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="E133">
-        <f>ROUND(68*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="F133">
-        <f>ROUND(68*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="G133">
-        <f>ROUND(68*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="H133">
-        <f>ROUND(83*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="I133">
-        <f>ROUND(85*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="J133">
-        <f>ROUND(69*$B$1,0)</f>
-        <v/>
-      </c>
-      <c r="K133">
-        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="L133">
@@ -7484,35 +7494,35 @@
         </is>
       </c>
       <c r="D134">
-        <f>ROUND(81*$B$1,0)</f>
+        <f>ROUND(65*$B$1,0)</f>
         <v/>
       </c>
       <c r="E134">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(55*$B$1,0)</f>
         <v/>
       </c>
       <c r="F134">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(55*$B$1,0)</f>
         <v/>
       </c>
       <c r="G134">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(55*$B$1,0)</f>
         <v/>
       </c>
       <c r="H134">
-        <f>ROUND(80*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="I134">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(71*$B$1,0)</f>
         <v/>
       </c>
       <c r="J134">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="K134">
-        <f>ROUND(72*$B$1,0)</f>
+        <f>ROUND(65*$B$1,0)</f>
         <v/>
       </c>
       <c r="L134">
@@ -7528,44 +7538,44 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>179611231</t>
+          <t>179611318</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Petitfee 98% Collagen &amp; CoQ10 Hydro Gel Eye Patch</t>
+          <t>Petitfee Chamomile Lightening Hydrogel Eye Mask</t>
         </is>
       </c>
       <c r="D135">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(64*$B$1,0)</f>
         <v/>
       </c>
       <c r="E135">
-        <f>ROUND(35*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="F135">
-        <f>ROUND(35*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="G135">
-        <f>ROUND(35*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="H135">
-        <f>ROUND(43*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="I135">
-        <f>ROUND(44*$B$1,0)</f>
+        <f>ROUND(69*$B$1,0)</f>
         <v/>
       </c>
       <c r="J135">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="K135">
-        <f>ROUND(39*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="L135">
@@ -7581,44 +7591,44 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>180987509</t>
+          <t>179611231</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Petitfee Pink Vita Brightening Eye Mask</t>
+          <t>Petitfee 98% Collagen &amp; CoQ10 Hydro Gel Eye Patch</t>
         </is>
       </c>
       <c r="D136">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(55*$B$1,0)</f>
         <v/>
       </c>
       <c r="E136">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="F136">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="G136">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(46*$B$1,0)</f>
         <v/>
       </c>
       <c r="H136">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="I136">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
       <c r="J136">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="K136">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="L136">
@@ -7634,44 +7644,44 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>180711041</t>
+          <t>664171648</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Petitfee EGF</t>
+          <t>PETITFEE - MASK 5</t>
         </is>
       </c>
       <c r="D137">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="E137">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="F137">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="G137">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="H137">
-        <f>ROUND(25*$B$1,0)</f>
+        <f>ROUND(56*$B$1,0)</f>
         <v/>
       </c>
       <c r="I137">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(58*$B$1,0)</f>
         <v/>
       </c>
       <c r="J137">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="K137">
-        <f>ROUND(23*$B$1,0)</f>
+        <f>ROUND(53*$B$1,0)</f>
         <v/>
       </c>
       <c r="L137">
@@ -7687,44 +7697,44 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>180992464</t>
+          <t>664171647</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PETITFEE Aura Quartz Hydrogel Eye Mask Pure Opal</t>
+          <t>PETITFEE - MASK 6</t>
         </is>
       </c>
       <c r="D138">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="E138">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="F138">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="G138">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(44*$B$1,0)</f>
         <v/>
       </c>
       <c r="H138">
-        <f>ROUND(23*$B$1,0)</f>
+        <f>ROUND(54*$B$1,0)</f>
         <v/>
       </c>
       <c r="I138">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(57*$B$1,0)</f>
         <v/>
       </c>
       <c r="J138">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(43*$B$1,0)</f>
         <v/>
       </c>
       <c r="K138">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(51*$B$1,0)</f>
         <v/>
       </c>
       <c r="L138">
@@ -7740,44 +7750,44 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>664171647</t>
+          <t>180987509</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PETITFEE - MASK 6</t>
+          <t>Petitfee Pink Vita Brightening Eye Mask</t>
         </is>
       </c>
       <c r="D139">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="E139">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="F139">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="G139">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="H139">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="I139">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="J139">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="K139">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="L139">
@@ -7793,44 +7803,44 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>179611304</t>
+          <t>180992464</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
+          <t>PETITFEE Aura Quartz Hydrogel Eye Mask Pure Opal</t>
         </is>
       </c>
       <c r="D140">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="E140">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="F140">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="G140">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="H140">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="I140">
-        <f>ROUND(16*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="J140">
-        <f>ROUND(13*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="K140">
-        <f>ROUND(15*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="L140">
@@ -7846,44 +7856,44 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>664171648</t>
+          <t>180711041</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PETITFEE - MASK 5</t>
+          <t>Petitfee EGF</t>
         </is>
       </c>
       <c r="D141">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="E141">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="F141">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="G141">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="H141">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="I141">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="J141">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(18*$B$1,0)</f>
         <v/>
       </c>
       <c r="K141">
-        <f>ROUND(10*$B$1,0)</f>
+        <f>ROUND(22*$B$1,0)</f>
         <v/>
       </c>
       <c r="L141">
@@ -7899,44 +7909,44 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>340752919</t>
+          <t>179611304</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PETITFEE Black Pearl &amp; Gold Hydrogel Eye Patch/Gold Hyd</t>
+          <t>Petitfee Cacao Energizing Hydrogel Eye Patch</t>
         </is>
       </c>
       <c r="D142">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="E142">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="F142">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="G142">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="H142">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="I142">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(21*$B$1,0)</f>
         <v/>
       </c>
       <c r="J142">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="K142">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="L142">
@@ -7947,49 +7957,49 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>437154709</t>
+          <t>1175175447</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
+          <t>PETITFEE MASK 6</t>
         </is>
       </c>
       <c r="D143">
-        <f>ROUND(2508*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="E143">
-        <f>ROUND(2031*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="F143">
-        <f>ROUND(2031*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="G143">
-        <f>ROUND(2031*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="H143">
-        <f>ROUND(2466*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="I143">
-        <f>ROUND(2529*$B$1,0)</f>
+        <f>ROUND(11*$B$1,0)</f>
         <v/>
       </c>
       <c r="J143">
-        <f>ROUND(2054*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="K143">
-        <f>ROUND(2228*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="L143">
@@ -8000,49 +8010,49 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ROUND LAB</t>
+          <t>PETITFEE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>437231408</t>
+          <t>340752919</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING SUNSCREEN_50ml</t>
+          <t>PETITFEE Black Pearl &amp; Gold Hydrogel Eye Patch/Gold Hyd</t>
         </is>
       </c>
       <c r="D144">
-        <f>ROUND(478*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="E144">
-        <f>ROUND(387*$B$1,0)</f>
+        <f>ROUND(5*$B$1,0)</f>
         <v/>
       </c>
       <c r="F144">
-        <f>ROUND(387*$B$1,0)</f>
+        <f>ROUND(5*$B$1,0)</f>
         <v/>
       </c>
       <c r="G144">
-        <f>ROUND(387*$B$1,0)</f>
+        <f>ROUND(5*$B$1,0)</f>
         <v/>
       </c>
       <c r="H144">
-        <f>ROUND(470*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="I144">
-        <f>ROUND(482*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="J144">
-        <f>ROUND(391*$B$1,0)</f>
+        <f>ROUND(5*$B$1,0)</f>
         <v/>
       </c>
       <c r="K144">
-        <f>ROUND(424*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="L144">
@@ -8058,44 +8068,44 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>437845041</t>
+          <t>437154709</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT CREAM 50ml</t>
+          <t>ROUND LAB 1025 DOKDO CLEANSER_150ml</t>
         </is>
       </c>
       <c r="D145">
-        <f>ROUND(111*$B$1,0)</f>
+        <f>ROUND(2516*$B$1,0)</f>
         <v/>
       </c>
       <c r="E145">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(2117*$B$1,0)</f>
         <v/>
       </c>
       <c r="F145">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(2117*$B$1,0)</f>
         <v/>
       </c>
       <c r="G145">
-        <f>ROUND(90*$B$1,0)</f>
+        <f>ROUND(2117*$B$1,0)</f>
         <v/>
       </c>
       <c r="H145">
-        <f>ROUND(109*$B$1,0)</f>
+        <f>ROUND(2615*$B$1,0)</f>
         <v/>
       </c>
       <c r="I145">
-        <f>ROUND(111*$B$1,0)</f>
+        <f>ROUND(2722*$B$1,0)</f>
         <v/>
       </c>
       <c r="J145">
-        <f>ROUND(91*$B$1,0)</f>
+        <f>ROUND(2062*$B$1,0)</f>
         <v/>
       </c>
       <c r="K145">
-        <f>ROUND(98*$B$1,0)</f>
+        <f>ROUND(2479*$B$1,0)</f>
         <v/>
       </c>
       <c r="L145">
@@ -8111,44 +8121,44 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>437242640</t>
+          <t>437231408</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING SUNSCREEN_50ml</t>
         </is>
       </c>
       <c r="D146">
-        <f>ROUND(104*$B$1,0)</f>
+        <f>ROUND(534*$B$1,0)</f>
         <v/>
       </c>
       <c r="E146">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(449*$B$1,0)</f>
         <v/>
       </c>
       <c r="F146">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(449*$B$1,0)</f>
         <v/>
       </c>
       <c r="G146">
-        <f>ROUND(84*$B$1,0)</f>
+        <f>ROUND(449*$B$1,0)</f>
         <v/>
       </c>
       <c r="H146">
-        <f>ROUND(102*$B$1,0)</f>
+        <f>ROUND(555*$B$1,0)</f>
         <v/>
       </c>
       <c r="I146">
-        <f>ROUND(105*$B$1,0)</f>
+        <f>ROUND(578*$B$1,0)</f>
         <v/>
       </c>
       <c r="J146">
-        <f>ROUND(85*$B$1,0)</f>
+        <f>ROUND(438*$B$1,0)</f>
         <v/>
       </c>
       <c r="K146">
-        <f>ROUND(93*$B$1,0)</f>
+        <f>ROUND(526*$B$1,0)</f>
         <v/>
       </c>
       <c r="L146">
@@ -8164,44 +8174,44 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>437797551</t>
+          <t>437203627</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT SERUM 30ml</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CLEANSER_150ml</t>
         </is>
       </c>
       <c r="D147">
-        <f>ROUND(81*$B$1,0)</f>
+        <f>ROUND(160*$B$1,0)</f>
         <v/>
       </c>
       <c r="E147">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(135*$B$1,0)</f>
         <v/>
       </c>
       <c r="F147">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(135*$B$1,0)</f>
         <v/>
       </c>
       <c r="G147">
-        <f>ROUND(66*$B$1,0)</f>
+        <f>ROUND(135*$B$1,0)</f>
         <v/>
       </c>
       <c r="H147">
-        <f>ROUND(80*$B$1,0)</f>
+        <f>ROUND(167*$B$1,0)</f>
         <v/>
       </c>
       <c r="I147">
-        <f>ROUND(82*$B$1,0)</f>
+        <f>ROUND(173*$B$1,0)</f>
         <v/>
       </c>
       <c r="J147">
-        <f>ROUND(67*$B$1,0)</f>
+        <f>ROUND(131*$B$1,0)</f>
         <v/>
       </c>
       <c r="K147">
-        <f>ROUND(72*$B$1,0)</f>
+        <f>ROUND(158*$B$1,0)</f>
         <v/>
       </c>
       <c r="L147">
@@ -8217,44 +8227,44 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>437776835</t>
+          <t>437242640</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
+          <t>ROUND LAB MUGWORT CALMING CLEANSER_150ml</t>
         </is>
       </c>
       <c r="D148">
-        <f>ROUND(60*$B$1,0)</f>
+        <f>ROUND(136*$B$1,0)</f>
         <v/>
       </c>
       <c r="E148">
-        <f>ROUND(49*$B$1,0)</f>
+        <f>ROUND(114*$B$1,0)</f>
         <v/>
       </c>
       <c r="F148">
-        <f>ROUND(49*$B$1,0)</f>
+        <f>ROUND(114*$B$1,0)</f>
         <v/>
       </c>
       <c r="G148">
-        <f>ROUND(49*$B$1,0)</f>
+        <f>ROUND(114*$B$1,0)</f>
         <v/>
       </c>
       <c r="H148">
-        <f>ROUND(59*$B$1,0)</f>
+        <f>ROUND(141*$B$1,0)</f>
         <v/>
       </c>
       <c r="I148">
-        <f>ROUND(61*$B$1,0)</f>
+        <f>ROUND(147*$B$1,0)</f>
         <v/>
       </c>
       <c r="J148">
-        <f>ROUND(49*$B$1,0)</f>
+        <f>ROUND(111*$B$1,0)</f>
         <v/>
       </c>
       <c r="K148">
-        <f>ROUND(53*$B$1,0)</f>
+        <f>ROUND(134*$B$1,0)</f>
         <v/>
       </c>
       <c r="L148">
@@ -8270,44 +8280,44 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>437203627</t>
+          <t>437248870</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CLEANSER_150ml</t>
+          <t>ROUND LAB MUGWORT CALMING SOOTHING GEL_150ml</t>
         </is>
       </c>
       <c r="D149">
-        <f>ROUND(59*$B$1,0)</f>
+        <f>ROUND(96*$B$1,0)</f>
         <v/>
       </c>
       <c r="E149">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="F149">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="G149">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="H149">
-        <f>ROUND(58*$B$1,0)</f>
+        <f>ROUND(100*$B$1,0)</f>
         <v/>
       </c>
       <c r="I149">
-        <f>ROUND(60*$B$1,0)</f>
+        <f>ROUND(104*$B$1,0)</f>
         <v/>
       </c>
       <c r="J149">
-        <f>ROUND(48*$B$1,0)</f>
+        <f>ROUND(79*$B$1,0)</f>
         <v/>
       </c>
       <c r="K149">
-        <f>ROUND(52*$B$1,0)</f>
+        <f>ROUND(94*$B$1,0)</f>
         <v/>
       </c>
       <c r="L149">
@@ -8323,44 +8333,44 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>437248870</t>
+          <t>437797551</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ROUND LAB MUGWORT CALMING SOOTHING GEL_150ml</t>
+          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT SERUM 30ml</t>
         </is>
       </c>
       <c r="D150">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(87*$B$1,0)</f>
         <v/>
       </c>
       <c r="E150">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="F150">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="G150">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="H150">
-        <f>ROUND(40*$B$1,0)</f>
+        <f>ROUND(90*$B$1,0)</f>
         <v/>
       </c>
       <c r="I150">
-        <f>ROUND(41*$B$1,0)</f>
+        <f>ROUND(94*$B$1,0)</f>
         <v/>
       </c>
       <c r="J150">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(71*$B$1,0)</f>
         <v/>
       </c>
       <c r="K150">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(85*$B$1,0)</f>
         <v/>
       </c>
       <c r="L150">
@@ -8376,44 +8386,44 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>437190353</t>
+          <t>437254254</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
+          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml</t>
         </is>
       </c>
       <c r="D151">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(75*$B$1,0)</f>
         <v/>
       </c>
       <c r="E151">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="F151">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="G151">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(63*$B$1,0)</f>
         <v/>
       </c>
       <c r="H151">
-        <f>ROUND(36*$B$1,0)</f>
+        <f>ROUND(78*$B$1,0)</f>
         <v/>
       </c>
       <c r="I151">
-        <f>ROUND(37*$B$1,0)</f>
+        <f>ROUND(81*$B$1,0)</f>
         <v/>
       </c>
       <c r="J151">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(62*$B$1,0)</f>
         <v/>
       </c>
       <c r="K151">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(74*$B$1,0)</f>
         <v/>
       </c>
       <c r="L151">
@@ -8429,44 +8439,44 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>437254254</t>
+          <t>437845041</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ROUND LAB SOYBEAN PANTHENOL CREAM_80ml</t>
+          <t>ROUND LAB VITA NIACINAMIDE DARK SPOT CREAM 50ml</t>
         </is>
       </c>
       <c r="D152">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(73*$B$1,0)</f>
         <v/>
       </c>
       <c r="E152">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="F152">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="G152">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="H152">
-        <f>ROUND(32*$B$1,0)</f>
+        <f>ROUND(76*$B$1,0)</f>
         <v/>
       </c>
       <c r="I152">
-        <f>ROUND(33*$B$1,0)</f>
+        <f>ROUND(79*$B$1,0)</f>
         <v/>
       </c>
       <c r="J152">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(60*$B$1,0)</f>
         <v/>
       </c>
       <c r="K152">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(72*$B$1,0)</f>
         <v/>
       </c>
       <c r="L152">
@@ -8482,44 +8492,44 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>437850261</t>
+          <t>437776835</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml</t>
+          <t>ROUND LAB PINE CALMING CICA AMPOULE_30ml</t>
         </is>
       </c>
       <c r="D153">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(62*$B$1,0)</f>
         <v/>
       </c>
       <c r="E153">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(53*$B$1,0)</f>
         <v/>
       </c>
       <c r="F153">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(53*$B$1,0)</f>
         <v/>
       </c>
       <c r="G153">
-        <f>ROUND(22*$B$1,0)</f>
+        <f>ROUND(53*$B$1,0)</f>
         <v/>
       </c>
       <c r="H153">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(65*$B$1,0)</f>
         <v/>
       </c>
       <c r="I153">
-        <f>ROUND(28*$B$1,0)</f>
+        <f>ROUND(68*$B$1,0)</f>
         <v/>
       </c>
       <c r="J153">
-        <f>ROUND(23*$B$1,0)</f>
+        <f>ROUND(51*$B$1,0)</f>
         <v/>
       </c>
       <c r="K153">
-        <f>ROUND(25*$B$1,0)</f>
+        <f>ROUND(62*$B$1,0)</f>
         <v/>
       </c>
       <c r="L153">
@@ -8530,49 +8540,49 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>214311963</t>
+          <t>437190353</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
+          <t>ROUND LAB BIRCH JUICE MOISTURIZING CREAM_80ml</t>
         </is>
       </c>
       <c r="D154">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(62*$B$1,0)</f>
         <v/>
       </c>
       <c r="E154">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="F154">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="G154">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(52*$B$1,0)</f>
         <v/>
       </c>
       <c r="H154">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(64*$B$1,0)</f>
         <v/>
       </c>
       <c r="I154">
-        <f>ROUND(21*$B$1,0)</f>
+        <f>ROUND(67*$B$1,0)</f>
         <v/>
       </c>
       <c r="J154">
-        <f>ROUND(17*$B$1,0)</f>
+        <f>ROUND(51*$B$1,0)</f>
         <v/>
       </c>
       <c r="K154">
-        <f>ROUND(19*$B$1,0)</f>
+        <f>ROUND(61*$B$1,0)</f>
         <v/>
       </c>
       <c r="L154">
@@ -8583,49 +8593,49 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SKIN1004</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>214312149</t>
+          <t>437238521</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack</t>
+          <t>ROUND LAB MUGWORT CALMING TONER_300ml</t>
         </is>
       </c>
       <c r="D155">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(41*$B$1,0)</f>
         <v/>
       </c>
       <c r="E155">
-        <f>ROUND(5*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="F155">
-        <f>ROUND(5*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="G155">
-        <f>ROUND(5*$B$1,0)</f>
+        <f>ROUND(35*$B$1,0)</f>
         <v/>
       </c>
       <c r="H155">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(43*$B$1,0)</f>
         <v/>
       </c>
       <c r="I155">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(45*$B$1,0)</f>
         <v/>
       </c>
       <c r="J155">
-        <f>ROUND(5*$B$1,0)</f>
+        <f>ROUND(34*$B$1,0)</f>
         <v/>
       </c>
       <c r="K155">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(41*$B$1,0)</f>
         <v/>
       </c>
       <c r="L155">
@@ -8636,49 +8646,49 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>ROUND LAB</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>248928555</t>
+          <t>437850261</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Acne Clear Bod</t>
+          <t>ROUND LAB SOYBEAN CLEANSING OIL_200ml</t>
         </is>
       </c>
       <c r="D156">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="E156">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="F156">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="G156">
-        <f>ROUND(11*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="H156">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="I156">
-        <f>ROUND(14*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="J156">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="K156">
-        <f>ROUND(12*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="L156">
@@ -8689,49 +8699,49 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SOME BY MI</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>248929125</t>
+          <t>214311963</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
+          <t>SKIN1004 - Madagascar Centella Ampoule [30ml]</t>
         </is>
       </c>
       <c r="D157">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="E157">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="F157">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="G157">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="H157">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="I157">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="J157">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="K157">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(15*$B$1,0)</f>
         <v/>
       </c>
       <c r="L157">
@@ -8742,49 +8752,49 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>THE ORDINARY</t>
+          <t>SKIN1004</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>214312385</t>
+          <t>214312149</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Argireline Solution 10% [30ml]</t>
+          <t>SKIN1004 - Madagascar Centella Hyalu-Cica Sleeping Pack</t>
         </is>
       </c>
       <c r="D158">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="E158">
-        <f>ROUND(25*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F158">
-        <f>ROUND(25*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G158">
-        <f>ROUND(25*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H158">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="I158">
-        <f>ROUND(31*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="J158">
-        <f>ROUND(25*$B$1,0)</f>
+        <f>ROUND(5*$B$1,0)</f>
         <v/>
       </c>
       <c r="K158">
-        <f>ROUND(27*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="L158">
@@ -8795,49 +8805,49 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>THE ORDINARY</t>
+          <t>SOME BY MI</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>247275092</t>
+          <t>248928555</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution[KOR] [2</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Acne Clear Bod</t>
         </is>
       </c>
       <c r="D159">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="E159">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="F159">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="G159">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(14*$B$1,0)</f>
         <v/>
       </c>
       <c r="H159">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(17*$B$1,0)</f>
         <v/>
       </c>
       <c r="I159">
-        <f>ROUND(9*$B$1,0)</f>
+        <f>ROUND(18*$B$1,0)</f>
         <v/>
       </c>
       <c r="J159">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(13*$B$1,0)</f>
         <v/>
       </c>
       <c r="K159">
-        <f>ROUND(8*$B$1,0)</f>
+        <f>ROUND(16*$B$1,0)</f>
         <v/>
       </c>
       <c r="L159">
@@ -8848,49 +8858,49 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ПРОЧЕЕ</t>
+          <t>SOME BY MI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>214312837</t>
+          <t>248929125</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>THE SAEM Saemmul Perfect Curling Mascara [8ml]</t>
+          <t>SOME BY MI - AHA-BHA-PHA 30 Days Miracle Cream [60g]</t>
         </is>
       </c>
       <c r="D160">
-        <f>ROUND(172*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="E160">
-        <f>ROUND(139*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="F160">
-        <f>ROUND(139*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="G160">
-        <f>ROUND(139*$B$1,0)</f>
+        <f>ROUND(8*$B$1,0)</f>
         <v/>
       </c>
       <c r="H160">
-        <f>ROUND(169*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="I160">
-        <f>ROUND(173*$B$1,0)</f>
+        <f>ROUND(10*$B$1,0)</f>
         <v/>
       </c>
       <c r="J160">
-        <f>ROUND(141*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="K160">
-        <f>ROUND(153*$B$1,0)</f>
+        <f>ROUND(9*$B$1,0)</f>
         <v/>
       </c>
       <c r="L160">
@@ -8901,49 +8911,49 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ПРОЧЕЕ</t>
+          <t>THE ORDINARY</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>154159632</t>
+          <t>214312385</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Baking Powder BB Deep Cleansing Foam 3в1 30</t>
+          <t>THE ORDINARY - Argireline Solution 10% [30ml]</t>
         </is>
       </c>
       <c r="D161">
-        <f>ROUND(120*$B$1,0)</f>
+        <f>ROUND(24*$B$1,0)</f>
         <v/>
       </c>
       <c r="E161">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="F161">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="G161">
-        <f>ROUND(97*$B$1,0)</f>
+        <f>ROUND(20*$B$1,0)</f>
         <v/>
       </c>
       <c r="H161">
-        <f>ROUND(118*$B$1,0)</f>
+        <f>ROUND(25*$B$1,0)</f>
         <v/>
       </c>
       <c r="I161">
-        <f>ROUND(121*$B$1,0)</f>
+        <f>ROUND(26*$B$1,0)</f>
         <v/>
       </c>
       <c r="J161">
-        <f>ROUND(98*$B$1,0)</f>
+        <f>ROUND(19*$B$1,0)</f>
         <v/>
       </c>
       <c r="K161">
-        <f>ROUND(107*$B$1,0)</f>
+        <f>ROUND(23*$B$1,0)</f>
         <v/>
       </c>
       <c r="L161">
@@ -8954,49 +8964,49 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПРОЧЕЕ</t>
+          <t>THE ORDINARY</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>183030830</t>
+          <t>247275092</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>HairSet/350/8*2</t>
+          <t>THE ORDINARY - Glycolic Acid 7% Toning Solution[KOR] [2</t>
         </is>
       </c>
       <c r="D162">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="E162">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="F162">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="G162">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="H162">
-        <f>ROUND(29*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="I162">
-        <f>ROUND(30*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="J162">
-        <f>ROUND(24*$B$1,0)</f>
+        <f>ROUND(6*$B$1,0)</f>
         <v/>
       </c>
       <c r="K162">
-        <f>ROUND(26*$B$1,0)</f>
+        <f>ROUND(7*$B$1,0)</f>
         <v/>
       </c>
       <c r="L162">
@@ -9012,44 +9022,44 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>663654300</t>
+          <t>214312837</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>videokamera4gneww</t>
+          <t>THE SAEM Saemmul Perfect Curling Mascara [8ml]</t>
         </is>
       </c>
       <c r="D163">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(249*$B$1,0)</f>
         <v/>
       </c>
       <c r="E163">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(209*$B$1,0)</f>
         <v/>
       </c>
       <c r="F163">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(209*$B$1,0)</f>
         <v/>
       </c>
       <c r="G163">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(209*$B$1,0)</f>
         <v/>
       </c>
       <c r="H163">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(259*$B$1,0)</f>
         <v/>
       </c>
       <c r="I163">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(269*$B$1,0)</f>
         <v/>
       </c>
       <c r="J163">
-        <f>ROUND(6*$B$1,0)</f>
+        <f>ROUND(204*$B$1,0)</f>
         <v/>
       </c>
       <c r="K163">
-        <f>ROUND(7*$B$1,0)</f>
+        <f>ROUND(245*$B$1,0)</f>
         <v/>
       </c>
       <c r="L163">
@@ -9058,45 +9068,416 @@
       </c>
     </row>
     <row r="164">
-      <c r="C164" s="1" t="inlineStr">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ПРОЧЕЕ</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>190314124</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>СГ-Белая с узорами</t>
+        </is>
+      </c>
+      <c r="D164">
+        <f>ROUND(99*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E164">
+        <f>ROUND(83*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F164">
+        <f>ROUND(83*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G164">
+        <f>ROUND(83*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H164">
+        <f>ROUND(103*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I164">
+        <f>ROUND(107*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J164">
+        <f>ROUND(81*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K164">
+        <f>ROUND(98*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="L164">
+        <f>SUM(D164:K164)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ПРОЧЕЕ</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>154159632</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Baking Powder BB Deep Cleansing Foam 3в1 30</t>
+        </is>
+      </c>
+      <c r="D165">
+        <f>ROUND(79*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E165">
+        <f>ROUND(67*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F165">
+        <f>ROUND(67*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G165">
+        <f>ROUND(67*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H165">
+        <f>ROUND(82*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I165">
+        <f>ROUND(86*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J165">
+        <f>ROUND(65*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K165">
+        <f>ROUND(78*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="L165">
+        <f>SUM(D165:K165)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ПРОЧЕЕ</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>183030830</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>HairSet/350/8*2</t>
+        </is>
+      </c>
+      <c r="D166">
+        <f>ROUND(21*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E166">
+        <f>ROUND(18*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F166">
+        <f>ROUND(18*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G166">
+        <f>ROUND(18*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H166">
+        <f>ROUND(22*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I166">
+        <f>ROUND(23*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J166">
+        <f>ROUND(17*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K166">
+        <f>ROUND(21*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="L166">
+        <f>SUM(D166:K166)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>ПРОЧЕЕ</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>180709801</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Koelf Royal Jelly</t>
+        </is>
+      </c>
+      <c r="D167">
+        <f>ROUND(16*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E167">
+        <f>ROUND(13*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F167">
+        <f>ROUND(13*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G167">
+        <f>ROUND(13*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H167">
+        <f>ROUND(16*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I167">
+        <f>ROUND(17*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J167">
+        <f>ROUND(13*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K167">
+        <f>ROUND(15*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="L167">
+        <f>SUM(D167:K167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>ПРОЧЕЕ</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>190314349</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>СГ-Красная</t>
+        </is>
+      </c>
+      <c r="D168">
+        <f>ROUND(11*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E168">
+        <f>ROUND(9*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F168">
+        <f>ROUND(9*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G168">
+        <f>ROUND(9*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H168">
+        <f>ROUND(12*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I168">
+        <f>ROUND(12*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J168">
+        <f>ROUND(9*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K168">
+        <f>ROUND(11*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="L168">
+        <f>SUM(D168:K168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>ПРОЧЕЕ</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>179611284</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Koelf Pearl &amp; Shea Butter Hydrogel Eye Patch</t>
+        </is>
+      </c>
+      <c r="D169">
+        <f>ROUND(10*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E169">
+        <f>ROUND(9*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F169">
+        <f>ROUND(9*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G169">
+        <f>ROUND(9*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H169">
+        <f>ROUND(11*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I169">
+        <f>ROUND(11*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J169">
+        <f>ROUND(8*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K169">
+        <f>ROUND(10*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="L169">
+        <f>SUM(D169:K169)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>ПРОЧЕЕ</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>663654300</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>videokamera4gneww</t>
+        </is>
+      </c>
+      <c r="D170">
+        <f>ROUND(7*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="E170">
+        <f>ROUND(6*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="F170">
+        <f>ROUND(6*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="G170">
+        <f>ROUND(6*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="H170">
+        <f>ROUND(8*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="I170">
+        <f>ROUND(8*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="J170">
+        <f>ROUND(6*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="K170">
+        <f>ROUND(7*$B$1,0)</f>
+        <v/>
+      </c>
+      <c r="L170">
+        <f>SUM(D170:K170)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="C171" s="1" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="D164" s="1">
-        <f>SUM(D3:D163)</f>
-        <v/>
-      </c>
-      <c r="E164" s="1">
-        <f>SUM(E3:E163)</f>
-        <v/>
-      </c>
-      <c r="F164" s="1">
-        <f>SUM(F3:F163)</f>
-        <v/>
-      </c>
-      <c r="G164" s="1">
-        <f>SUM(G3:G163)</f>
-        <v/>
-      </c>
-      <c r="H164" s="1">
-        <f>SUM(H3:H163)</f>
-        <v/>
-      </c>
-      <c r="I164" s="1">
-        <f>SUM(I3:I163)</f>
-        <v/>
-      </c>
-      <c r="J164" s="1">
-        <f>SUM(J3:J163)</f>
-        <v/>
-      </c>
-      <c r="K164" s="1">
-        <f>SUM(K3:K163)</f>
-        <v/>
-      </c>
-      <c r="L164" s="1">
-        <f>SUM(L3:L163)</f>
+      <c r="D171" s="1">
+        <f>SUM(D3:D170)</f>
+        <v/>
+      </c>
+      <c r="E171" s="1">
+        <f>SUM(E3:E170)</f>
+        <v/>
+      </c>
+      <c r="F171" s="1">
+        <f>SUM(F3:F170)</f>
+        <v/>
+      </c>
+      <c r="G171" s="1">
+        <f>SUM(G3:G170)</f>
+        <v/>
+      </c>
+      <c r="H171" s="1">
+        <f>SUM(H3:H170)</f>
+        <v/>
+      </c>
+      <c r="I171" s="1">
+        <f>SUM(I3:I170)</f>
+        <v/>
+      </c>
+      <c r="J171" s="1">
+        <f>SUM(J3:J170)</f>
+        <v/>
+      </c>
+      <c r="K171" s="1">
+        <f>SUM(K3:K170)</f>
+        <v/>
+      </c>
+      <c r="L171" s="1">
+        <f>SUM(L3:L170)</f>
         <v/>
       </c>
     </row>
